--- a/output/screener_output.xlsx
+++ b/output/screener_output.xlsx
@@ -646,10 +646,10 @@
           <t>Mar 2024</t>
         </is>
       </c>
-      <c r="D2" s="2" t="n">
+      <c r="D2" t="n">
         <v>11.85</v>
       </c>
-      <c r="E2" s="2" t="n">
+      <c r="E2" t="n">
         <v>76.3</v>
       </c>
       <c r="F2" s="2" t="n">
@@ -664,28 +664,28 @@
       <c r="I2" s="2" t="n">
         <v>22.61</v>
       </c>
-      <c r="J2" s="2" t="n">
+      <c r="J2" t="n">
         <v>56.39</v>
       </c>
       <c r="K2" s="2" t="n">
         <v>9424</v>
       </c>
-      <c r="L2" s="2" t="n">
+      <c r="L2" t="n">
         <v>17.07</v>
       </c>
-      <c r="M2" s="2" t="n">
+      <c r="M2" t="n">
         <v>212</v>
       </c>
-      <c r="N2" s="2" t="n">
+      <c r="N2" t="n">
         <v>19.06</v>
       </c>
-      <c r="O2" s="2" t="n">
+      <c r="O2" t="n">
         <v>0</v>
       </c>
-      <c r="P2" s="2" t="n">
+      <c r="P2" t="n">
         <v>17</v>
       </c>
-      <c r="Q2" s="2" t="n">
+      <c r="Q2" t="n">
         <v>21183</v>
       </c>
       <c r="R2" s="2" t="n">
@@ -694,25 +694,25 @@
       <c r="S2" s="2" t="n">
         <v>120.69</v>
       </c>
-      <c r="T2" s="2" t="n">
+      <c r="T2" t="n">
         <v>121.24</v>
       </c>
-      <c r="U2" s="2" t="n">
+      <c r="U2" t="n">
         <v>67.58</v>
       </c>
-      <c r="V2" s="2" t="n">
+      <c r="V2" t="n">
         <v>0</v>
       </c>
-      <c r="W2" s="2" t="n">
+      <c r="W2" t="n">
         <v>5</v>
       </c>
-      <c r="X2" s="2" t="n">
+      <c r="X2" s="3" t="n">
         <v>28.1</v>
       </c>
-      <c r="Y2" s="2" t="n">
+      <c r="Y2" s="3" t="n">
         <v>312.51</v>
       </c>
-      <c r="Z2" s="2" t="n">
+      <c r="Z2" t="n">
         <v>0</v>
       </c>
       <c r="AA2" t="inlineStr">
@@ -720,7 +720,7 @@
           <t>Consumer Discretionary</t>
         </is>
       </c>
-      <c r="AB2" s="2" t="n">
+      <c r="AB2" t="n">
         <v>68904</v>
       </c>
       <c r="AC2" s="2" t="n">
@@ -746,10 +746,10 @@
           <t>Mar 2024</t>
         </is>
       </c>
-      <c r="D3" s="2" t="n">
+      <c r="D3" t="n">
         <v>19.14</v>
       </c>
-      <c r="E3" s="2" t="n">
+      <c r="E3" t="n">
         <v>26.69</v>
       </c>
       <c r="F3" s="2" t="n">
@@ -764,55 +764,55 @@
       <c r="I3" s="2" t="n">
         <v>87.09999999999999</v>
       </c>
-      <c r="J3" s="2" t="n">
+      <c r="J3" t="n">
         <v>1.66</v>
       </c>
       <c r="K3" s="2" t="n">
         <v>50429</v>
       </c>
-      <c r="L3" s="2" t="n">
+      <c r="L3" t="n">
         <v>2.53</v>
       </c>
-      <c r="M3" s="2" t="n">
+      <c r="M3" t="n">
         <v>127</v>
       </c>
-      <c r="N3" s="2" t="n">
+      <c r="N3" t="n">
         <v>249.97</v>
       </c>
-      <c r="O3" s="2" t="n">
+      <c r="O3" t="n">
         <v>58</v>
       </c>
-      <c r="P3" s="2" t="n">
+      <c r="P3" t="n">
         <v>8021</v>
       </c>
-      <c r="Q3" s="2" t="n">
+      <c r="Q3" t="n">
         <v>44338</v>
       </c>
-      <c r="R3" s="2" t="n">
+      <c r="R3" s="3" t="n">
         <v>10.46</v>
       </c>
-      <c r="S3" s="2" t="n">
+      <c r="S3" s="3" t="n">
         <v>7.87</v>
       </c>
-      <c r="T3" s="2" t="n">
+      <c r="T3" t="n">
         <v>8.619999999999999</v>
       </c>
-      <c r="U3" s="2" t="n">
+      <c r="U3" t="n">
         <v>13.63</v>
       </c>
-      <c r="V3" s="2" t="n">
+      <c r="V3" t="n">
         <v>0</v>
       </c>
-      <c r="W3" s="2" t="n">
+      <c r="W3" t="n">
         <v>5</v>
       </c>
-      <c r="X3" s="2" t="n">
+      <c r="X3" s="3" t="n">
         <v>39.72</v>
       </c>
-      <c r="Y3" s="2" t="n">
+      <c r="Y3" s="3" t="n">
         <v>20.18</v>
       </c>
-      <c r="Z3" s="2" t="n">
+      <c r="Z3" t="n">
         <v>1.15</v>
       </c>
       <c r="AA3" t="inlineStr">
@@ -820,7 +820,7 @@
           <t>Information Technology</t>
         </is>
       </c>
-      <c r="AB3" s="2" t="n">
+      <c r="AB3" t="n">
         <v>240893</v>
       </c>
       <c r="AC3" s="2" t="n">
@@ -846,10 +846,10 @@
           <t>Mar 2024</t>
         </is>
       </c>
-      <c r="D4" s="2" t="n">
+      <c r="D4" t="n">
         <v>7.03</v>
       </c>
-      <c r="E4" s="2" t="n">
+      <c r="E4" t="n">
         <v>13.51</v>
       </c>
       <c r="F4" s="2" t="n">
@@ -861,58 +861,58 @@
       <c r="H4" s="2" t="n">
         <v>0.1</v>
       </c>
-      <c r="I4" s="2" t="n">
+      <c r="I4" s="3" t="n">
         <v>3.54</v>
       </c>
-      <c r="J4" s="2" t="n">
+      <c r="J4" t="n">
         <v>8.029999999999999</v>
       </c>
       <c r="K4" s="2" t="n">
         <v>20445</v>
       </c>
-      <c r="L4" s="2" t="n">
+      <c r="L4" t="n">
         <v>0.99</v>
       </c>
-      <c r="M4" s="2" t="n">
+      <c r="M4" t="n">
         <v>95</v>
       </c>
-      <c r="N4" s="2" t="n">
+      <c r="N4" t="n">
         <v>667.27</v>
       </c>
-      <c r="O4" s="2" t="n">
+      <c r="O4" t="n">
         <v>36</v>
       </c>
-      <c r="P4" s="2" t="n">
+      <c r="P4" t="n">
         <v>2071</v>
       </c>
-      <c r="Q4" s="2" t="n">
+      <c r="Q4" t="n">
         <v>18266</v>
       </c>
-      <c r="R4" s="2" t="n">
+      <c r="R4" s="3" t="n">
         <v>10.34</v>
       </c>
-      <c r="S4" s="2" t="n">
+      <c r="S4" s="3" t="n">
         <v>8.76</v>
       </c>
-      <c r="T4" s="2" t="n">
+      <c r="T4" t="n">
         <v>8.56</v>
       </c>
-      <c r="U4" s="2" t="n">
+      <c r="U4" t="n">
         <v>17.59</v>
       </c>
-      <c r="V4" s="2" t="n">
+      <c r="V4" t="n">
         <v>0</v>
       </c>
-      <c r="W4" s="2" t="n">
+      <c r="W4" t="n">
         <v>4</v>
       </c>
-      <c r="X4" s="2" t="n">
+      <c r="X4" s="3" t="n">
         <v>30.16</v>
       </c>
-      <c r="Y4" s="2" t="n">
+      <c r="Y4" s="3" t="n">
         <v>4.29</v>
       </c>
-      <c r="Z4" s="2" t="n">
+      <c r="Z4" t="n">
         <v>1.26</v>
       </c>
       <c r="AA4" t="inlineStr">
@@ -920,7 +920,7 @@
           <t>Industrials</t>
         </is>
       </c>
-      <c r="AB4" s="2" t="n">
+      <c r="AB4" t="n">
         <v>221113</v>
       </c>
       <c r="AC4" s="2" t="n">
@@ -946,10 +946,10 @@
           <t>Mar 2024</t>
         </is>
       </c>
-      <c r="D5" s="2" t="n">
+      <c r="D5" t="n">
         <v>41.37</v>
       </c>
-      <c r="E5" s="2" t="n">
+      <c r="E5" t="n">
         <v>36.2</v>
       </c>
       <c r="F5" s="2" t="n">
@@ -961,31 +961,31 @@
       <c r="H5" s="2" t="n">
         <v>0.8</v>
       </c>
-      <c r="I5" s="2" t="n">
+      <c r="I5" s="3" t="n">
         <v>8.300000000000001</v>
       </c>
-      <c r="J5" s="2" t="n">
+      <c r="J5" t="n">
         <v>0.55</v>
       </c>
       <c r="K5" s="2" t="n">
         <v>17651</v>
       </c>
-      <c r="L5" s="2" t="n">
+      <c r="L5" t="n">
         <v>6.91</v>
       </c>
-      <c r="M5" s="2" t="n">
+      <c r="M5" t="n">
         <v>54</v>
       </c>
-      <c r="N5" s="2" t="n">
+      <c r="N5" t="n">
         <v>11.19</v>
       </c>
-      <c r="O5" s="2" t="n">
+      <c r="O5" t="n">
         <v>0</v>
       </c>
-      <c r="P5" s="2" t="n">
+      <c r="P5" t="n">
         <v>34616</v>
       </c>
-      <c r="Q5" s="2" t="n">
+      <c r="Q5" t="n">
         <v>14170</v>
       </c>
       <c r="R5" s="2" t="n">
@@ -994,25 +994,25 @@
       <c r="S5" s="3" t="n">
         <v/>
       </c>
-      <c r="T5" s="3" t="n">
+      <c r="T5" t="n">
         <v/>
       </c>
-      <c r="U5" s="2" t="n">
+      <c r="U5" t="n">
         <v>24.29</v>
       </c>
-      <c r="V5" s="2" t="n">
+      <c r="V5" t="n">
         <v>1</v>
       </c>
-      <c r="W5" s="2" t="n">
+      <c r="W5" t="n">
         <v>4</v>
       </c>
-      <c r="X5" s="2" t="n">
+      <c r="X5" s="3" t="n">
         <v>46.05</v>
       </c>
-      <c r="Y5" s="2" t="n">
+      <c r="Y5" s="3" t="n">
         <v>222.2</v>
       </c>
-      <c r="Z5" s="2" t="n">
+      <c r="Z5" t="n">
         <v>0</v>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1020,7 +1020,7 @@
           <t>Energy</t>
         </is>
       </c>
-      <c r="AB5" s="2" t="n">
+      <c r="AB5" t="n">
         <v>50351</v>
       </c>
       <c r="AC5" s="2" t="n">
@@ -1046,10 +1046,10 @@
           <t>Mar 2024</t>
         </is>
       </c>
-      <c r="D6" s="2" t="n">
+      <c r="D6" t="n">
         <v>16.12</v>
       </c>
-      <c r="E6" s="2" t="n">
+      <c r="E6" t="n">
         <v>23.83</v>
       </c>
       <c r="F6" s="2" t="n">
@@ -1064,55 +1064,55 @@
       <c r="I6" s="2" t="n">
         <v>41.19</v>
       </c>
-      <c r="J6" s="2" t="n">
+      <c r="J6" t="n">
         <v>2.32</v>
       </c>
       <c r="K6" s="2" t="n">
         <v>2938</v>
       </c>
-      <c r="L6" s="2" t="n">
+      <c r="L6" t="n">
         <v>5.07</v>
       </c>
-      <c r="M6" s="2" t="n">
+      <c r="M6" t="n">
         <v>41</v>
       </c>
-      <c r="N6" s="2" t="n">
+      <c r="N6" t="n">
         <v>34.79</v>
       </c>
-      <c r="O6" s="2" t="n">
+      <c r="O6" t="n">
         <v>79</v>
       </c>
-      <c r="P6" s="2" t="n">
+      <c r="P6" t="n">
         <v>345</v>
       </c>
-      <c r="Q6" s="2" t="n">
+      <c r="Q6" t="n">
         <v>4175</v>
       </c>
-      <c r="R6" s="2" t="n">
+      <c r="R6" s="3" t="n">
         <v>14.55</v>
       </c>
-      <c r="S6" s="2" t="n">
+      <c r="S6" s="3" t="n">
         <v>14.85</v>
       </c>
-      <c r="T6" s="2" t="n">
+      <c r="T6" t="n">
         <v>15.44</v>
       </c>
-      <c r="U6" s="2" t="n">
+      <c r="U6" t="n">
         <v>18.28</v>
       </c>
-      <c r="V6" s="2" t="n">
+      <c r="V6" t="n">
         <v>0</v>
       </c>
-      <c r="W6" s="2" t="n">
+      <c r="W6" t="n">
         <v>5</v>
       </c>
-      <c r="X6" s="2" t="n">
+      <c r="X6" s="3" t="n">
         <v>25.17</v>
       </c>
-      <c r="Y6" s="2" t="n">
+      <c r="Y6" s="3" t="n">
         <v>29.66</v>
       </c>
-      <c r="Z6" s="2" t="n">
+      <c r="Z6" t="n">
         <v>7.66</v>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1120,7 +1120,7 @@
           <t>Consumer Staples</t>
         </is>
       </c>
-      <c r="AB6" s="2" t="n">
+      <c r="AB6" t="n">
         <v>24394</v>
       </c>
       <c r="AC6" s="2" t="n">
@@ -1146,10 +1146,10 @@
           <t>Mar 2024</t>
         </is>
       </c>
-      <c r="D7" s="2" t="n">
+      <c r="D7" t="n">
         <v>26.02</v>
       </c>
-      <c r="E7" s="2" t="n">
+      <c r="E7" t="n">
         <v>34.33</v>
       </c>
       <c r="F7" s="2" t="n">
@@ -1164,28 +1164,28 @@
       <c r="I7" s="2" t="n">
         <v>82.73999999999999</v>
       </c>
-      <c r="J7" s="2" t="n">
+      <c r="J7" t="n">
         <v>0.7</v>
       </c>
       <c r="K7" s="2" t="n">
         <v>667</v>
       </c>
-      <c r="L7" s="2" t="n">
+      <c r="L7" t="n">
         <v>5.04</v>
       </c>
-      <c r="M7" s="2" t="n">
+      <c r="M7" t="n">
         <v>14</v>
       </c>
-      <c r="N7" s="2" t="n">
+      <c r="N7" t="n">
         <v>20.19</v>
       </c>
-      <c r="O7" s="2" t="n">
+      <c r="O7" t="n">
         <v>47</v>
       </c>
-      <c r="P7" s="2" t="n">
+      <c r="P7" t="n">
         <v>60</v>
       </c>
-      <c r="Q7" s="2" t="n">
+      <c r="Q7" t="n">
         <v>882</v>
       </c>
       <c r="R7" s="2" t="n">
@@ -1194,25 +1194,25 @@
       <c r="S7" s="2" t="n">
         <v>29.17</v>
       </c>
-      <c r="T7" s="2" t="n">
+      <c r="T7" t="n">
         <v>28.47</v>
       </c>
-      <c r="U7" s="2" t="n">
+      <c r="U7" t="n">
         <v>76.47</v>
       </c>
-      <c r="V7" s="2" t="n">
+      <c r="V7" t="n">
         <v>1</v>
       </c>
-      <c r="W7" s="2" t="n">
+      <c r="W7" t="n">
         <v>4</v>
       </c>
-      <c r="X7" s="2" t="n">
+      <c r="X7" s="3" t="n">
         <v>799.9299999999999</v>
       </c>
-      <c r="Y7" s="2" t="n">
+      <c r="Y7" s="3" t="n">
         <v>554.6799999999999</v>
       </c>
-      <c r="Z7" s="2" t="n">
+      <c r="Z7" t="n">
         <v>0.42</v>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1220,7 +1220,7 @@
           <t>Consumer Discretionary</t>
         </is>
       </c>
-      <c r="AB7" s="2" t="n">
+      <c r="AB7" t="n">
         <v>4270</v>
       </c>
       <c r="AC7" s="2" t="n">
@@ -1246,10 +1246,10 @@
           <t>Mar 2024</t>
         </is>
       </c>
-      <c r="D8" s="2" t="n">
+      <c r="D8" t="n">
         <v>17.08</v>
       </c>
-      <c r="E8" s="2" t="n">
+      <c r="E8" t="n">
         <v>23.7</v>
       </c>
       <c r="F8" s="2" t="n">
@@ -1264,55 +1264,55 @@
       <c r="I8" s="2" t="n">
         <v>87.52</v>
       </c>
-      <c r="J8" s="2" t="n">
+      <c r="J8" t="n">
         <v>1.13</v>
       </c>
       <c r="K8" s="2" t="n">
         <v>20117</v>
       </c>
-      <c r="L8" s="2" t="n">
+      <c r="L8" t="n">
         <v>3.31</v>
       </c>
-      <c r="M8" s="2" t="n">
+      <c r="M8" t="n">
         <v>63</v>
       </c>
-      <c r="N8" s="2" t="n">
+      <c r="N8" t="n">
         <v>42.55</v>
       </c>
-      <c r="O8" s="3" t="n">
+      <c r="O8" t="n">
         <v/>
       </c>
-      <c r="P8" s="2" t="n">
+      <c r="P8" t="n">
         <v>8359</v>
       </c>
-      <c r="Q8" s="2" t="n">
+      <c r="Q8" t="n">
         <v>25210</v>
       </c>
-      <c r="R8" s="2" t="n">
+      <c r="R8" s="3" t="n">
         <v>13.2</v>
       </c>
-      <c r="S8" s="2" t="n">
+      <c r="S8" s="3" t="n">
         <v>11.24</v>
       </c>
-      <c r="T8" s="2" t="n">
+      <c r="T8" t="n">
         <v>12.47</v>
       </c>
-      <c r="U8" s="2" t="n">
+      <c r="U8" t="n">
         <v>15.22</v>
       </c>
-      <c r="V8" s="2" t="n">
+      <c r="V8" t="n">
         <v>0</v>
       </c>
-      <c r="W8" s="2" t="n">
+      <c r="W8" t="n">
         <v>5</v>
       </c>
-      <c r="X8" s="2" t="n">
+      <c r="X8" s="3" t="n">
         <v>100.32</v>
       </c>
-      <c r="Y8" s="2" t="n">
+      <c r="Y8" s="3" t="n">
         <v>148.53</v>
       </c>
-      <c r="Z8" s="3" t="n">
+      <c r="Z8" t="n">
         <v/>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1320,7 +1320,7 @@
           <t>Information Technology</t>
         </is>
       </c>
-      <c r="AB8" s="2" t="n">
+      <c r="AB8" t="n">
         <v>153670</v>
       </c>
       <c r="AC8" s="2" t="n">
@@ -1346,10 +1346,10 @@
           <t>Mar 2024</t>
         </is>
       </c>
-      <c r="D9" s="2" t="n">
+      <c r="D9" t="n">
         <v>11.94</v>
       </c>
-      <c r="E9" s="2" t="n">
+      <c r="E9" t="n">
         <v>15.93</v>
       </c>
       <c r="F9" s="2" t="n">
@@ -1361,31 +1361,31 @@
       <c r="H9" s="2" t="n">
         <v>0.43</v>
       </c>
-      <c r="I9" s="2" t="n">
+      <c r="I9" s="3" t="n">
         <v>8.039999999999999</v>
       </c>
-      <c r="J9" s="2" t="n">
+      <c r="J9" t="n">
         <v>1.73</v>
       </c>
       <c r="K9" s="2" t="n">
         <v>841</v>
       </c>
-      <c r="L9" s="2" t="n">
+      <c r="L9" t="n">
         <v>4.11</v>
       </c>
-      <c r="M9" s="2" t="n">
+      <c r="M9" t="n">
         <v>42</v>
       </c>
-      <c r="N9" s="2" t="n">
+      <c r="N9" t="n">
         <v>113</v>
       </c>
-      <c r="O9" s="2" t="n">
+      <c r="O9" t="n">
         <v>8</v>
       </c>
-      <c r="P9" s="2" t="n">
+      <c r="P9" t="n">
         <v>1753</v>
       </c>
-      <c r="Q9" s="2" t="n">
+      <c r="Q9" t="n">
         <v>1349</v>
       </c>
       <c r="R9" s="2" t="n">
@@ -1394,25 +1394,25 @@
       <c r="S9" s="2" t="n">
         <v>73.11</v>
       </c>
-      <c r="T9" s="2" t="n">
+      <c r="T9" t="n">
         <v>69.52</v>
       </c>
-      <c r="U9" s="2" t="n">
+      <c r="U9" t="n">
         <v>68.36</v>
       </c>
-      <c r="V9" s="2" t="n">
+      <c r="V9" t="n">
         <v>1</v>
       </c>
-      <c r="W9" s="2" t="n">
+      <c r="W9" t="n">
         <v>5</v>
       </c>
-      <c r="X9" s="2" t="n">
+      <c r="X9" s="3" t="n">
         <v>19.88</v>
       </c>
-      <c r="Y9" s="2" t="n">
+      <c r="Y9" s="3" t="n">
         <v>7.39</v>
       </c>
-      <c r="Z9" s="2" t="n">
+      <c r="Z9" t="n">
         <v>0.96</v>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1420,7 +1420,7 @@
           <t>Consumer Discretionary</t>
         </is>
       </c>
-      <c r="AB9" s="2" t="n">
+      <c r="AB9" t="n">
         <v>12375</v>
       </c>
       <c r="AC9" s="2" t="n">
@@ -1446,46 +1446,46 @@
           <t>Mar 2024</t>
         </is>
       </c>
-      <c r="D10" s="2" t="n">
+      <c r="D10" t="n">
         <v>28.89</v>
       </c>
-      <c r="E10" s="2" t="n">
+      <c r="E10" t="n">
         <v>62.41</v>
       </c>
       <c r="F10" s="2" t="n">
         <v>17.99</v>
       </c>
-      <c r="G10" s="2" t="n">
+      <c r="G10" s="3" t="n">
         <v>5.22</v>
       </c>
-      <c r="H10" s="2" t="n">
+      <c r="H10" s="3" t="n">
         <v>6.45</v>
       </c>
-      <c r="I10" s="2" t="n">
+      <c r="I10" s="3" t="n">
         <v>1.3</v>
       </c>
-      <c r="J10" s="2" t="n">
+      <c r="J10" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="K10" s="2" t="n">
         <v>12547</v>
       </c>
-      <c r="L10" s="2" t="n">
+      <c r="L10" t="n">
         <v>90.73999999999999</v>
       </c>
-      <c r="M10" s="2" t="n">
+      <c r="M10" t="n">
         <v>63</v>
       </c>
-      <c r="N10" s="2" t="n">
+      <c r="N10" t="n">
         <v>182.31</v>
       </c>
-      <c r="O10" s="2" t="n">
+      <c r="O10" t="n">
         <v>16</v>
       </c>
-      <c r="P10" s="2" t="n">
+      <c r="P10" t="n">
         <v>1651008</v>
       </c>
-      <c r="Q10" s="2" t="n">
+      <c r="Q10" t="n">
         <v>157284</v>
       </c>
       <c r="R10" s="2" t="n">
@@ -1494,25 +1494,25 @@
       <c r="S10" s="2" t="n">
         <v>51.95</v>
       </c>
-      <c r="T10" s="2" t="n">
+      <c r="T10" t="n">
         <v>55.18</v>
       </c>
-      <c r="U10" s="2" t="n">
+      <c r="U10" t="n">
         <v>21.4</v>
       </c>
-      <c r="V10" s="2" t="n">
+      <c r="V10" t="n">
         <v>0</v>
       </c>
-      <c r="W10" s="2" t="n">
+      <c r="W10" t="n">
         <v>2</v>
       </c>
-      <c r="X10" s="2" t="n">
+      <c r="X10" s="3" t="n">
         <v>115.62</v>
       </c>
-      <c r="Y10" s="2" t="n">
+      <c r="Y10" s="3" t="n">
         <v>39.95</v>
       </c>
-      <c r="Z10" s="2" t="n">
+      <c r="Z10" t="n">
         <v>0.22</v>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1520,7 +1520,7 @@
           <t>Financials</t>
         </is>
       </c>
-      <c r="AB10" s="2" t="n">
+      <c r="AB10" t="n">
         <v>159516</v>
       </c>
       <c r="AC10" s="2" t="n">
@@ -1546,10 +1546,10 @@
           <t>Mar 2024</t>
         </is>
       </c>
-      <c r="D11" s="2" t="n">
+      <c r="D11" t="n">
         <v>30.34</v>
       </c>
-      <c r="E11" s="2" t="n">
+      <c r="E11" t="n">
         <v>58.36</v>
       </c>
       <c r="F11" s="2" t="n">
@@ -1561,58 +1561,58 @@
       <c r="H11" s="2" t="n">
         <v>0.9399999999999999</v>
       </c>
-      <c r="I11" s="2" t="n">
+      <c r="I11" s="3" t="n">
         <v>5.95</v>
       </c>
-      <c r="J11" s="2" t="n">
+      <c r="J11" t="n">
         <v>0.23</v>
       </c>
       <c r="K11" s="2" t="n">
         <v>8250</v>
       </c>
-      <c r="L11" s="2" t="n">
+      <c r="L11" t="n">
         <v>25.34</v>
       </c>
-      <c r="M11" s="2" t="n">
+      <c r="M11" t="n">
         <v>38</v>
       </c>
-      <c r="N11" s="2" t="n">
+      <c r="N11" t="n">
         <v>122.17</v>
       </c>
-      <c r="O11" s="2" t="n">
+      <c r="O11" t="n">
         <v>16</v>
       </c>
-      <c r="P11" s="2" t="n">
+      <c r="P11" t="n">
         <v>49470</v>
       </c>
-      <c r="Q11" s="2" t="n">
+      <c r="Q11" t="n">
         <v>15018</v>
       </c>
       <c r="R11" s="2" t="n">
         <v>19.58</v>
       </c>
-      <c r="S11" s="2" t="n">
+      <c r="S11" s="3" t="n">
         <v>14.91</v>
       </c>
-      <c r="T11" s="2" t="n">
+      <c r="T11" t="n">
         <v>14.87</v>
       </c>
-      <c r="U11" s="2" t="n">
+      <c r="U11" t="n">
         <v>28.63</v>
       </c>
-      <c r="V11" s="2" t="n">
+      <c r="V11" t="n">
         <v>1</v>
       </c>
-      <c r="W11" s="2" t="n">
+      <c r="W11" t="n">
         <v>4</v>
       </c>
-      <c r="X11" s="2" t="n">
+      <c r="X11" s="3" t="n">
         <v>35.34</v>
       </c>
-      <c r="Y11" s="2" t="n">
+      <c r="Y11" s="3" t="n">
         <v>10.99</v>
       </c>
-      <c r="Z11" s="2" t="n">
+      <c r="Z11" t="n">
         <v>1.19</v>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1620,7 +1620,7 @@
           <t>Industrials</t>
         </is>
       </c>
-      <c r="AB11" s="2" t="n">
+      <c r="AB11" t="n">
         <v>26711</v>
       </c>
       <c r="AC11" s="2" t="n">
@@ -1646,10 +1646,10 @@
           <t>Mar 2024</t>
         </is>
       </c>
-      <c r="D12" s="2" t="n">
+      <c r="D12" t="n">
         <v>14.29</v>
       </c>
-      <c r="E12" s="2" t="n">
+      <c r="E12" t="n">
         <v>22.02</v>
       </c>
       <c r="F12" s="2" t="n">
@@ -1664,55 +1664,55 @@
       <c r="I12" s="2" t="n">
         <v>46.46</v>
       </c>
-      <c r="J12" s="2" t="n">
+      <c r="J12" t="n">
         <v>1.11</v>
       </c>
       <c r="K12" s="2" t="n">
         <v>15840</v>
       </c>
-      <c r="L12" s="2" t="n">
+      <c r="L12" t="n">
         <v>6.01</v>
       </c>
-      <c r="M12" s="2" t="n">
+      <c r="M12" t="n">
         <v>58</v>
       </c>
-      <c r="N12" s="2" t="n">
+      <c r="N12" t="n">
         <v>125.71</v>
       </c>
-      <c r="O12" s="2" t="n">
+      <c r="O12" t="n">
         <v>90</v>
       </c>
-      <c r="P12" s="2" t="n">
+      <c r="P12" t="n">
         <v>5758</v>
       </c>
-      <c r="Q12" s="2" t="n">
+      <c r="Q12" t="n">
         <v>22448</v>
       </c>
-      <c r="R12" s="2" t="n">
+      <c r="R12" s="3" t="n">
         <v>12.71</v>
       </c>
-      <c r="S12" s="2" t="n">
+      <c r="S12" s="3" t="n">
         <v>9.19</v>
       </c>
-      <c r="T12" s="2" t="n">
+      <c r="T12" t="n">
         <v>9.41</v>
       </c>
-      <c r="U12" s="2" t="n">
+      <c r="U12" t="n">
         <v>13.4</v>
       </c>
-      <c r="V12" s="2" t="n">
+      <c r="V12" t="n">
         <v>0</v>
       </c>
-      <c r="W12" s="2" t="n">
+      <c r="W12" t="n">
         <v>5</v>
       </c>
-      <c r="X12" s="2" t="n">
+      <c r="X12" s="3" t="n">
         <v>16.63</v>
       </c>
-      <c r="Y12" s="2" t="n">
+      <c r="Y12" s="3" t="n">
         <v>7.67</v>
       </c>
-      <c r="Z12" s="2" t="n">
+      <c r="Z12" t="n">
         <v>9.33</v>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1720,7 +1720,7 @@
           <t>Information Technology</t>
         </is>
       </c>
-      <c r="AB12" s="2" t="n">
+      <c r="AB12" t="n">
         <v>109913</v>
       </c>
       <c r="AC12" s="2" t="n">
@@ -1746,10 +1746,10 @@
           <t>Mar 2024</t>
         </is>
       </c>
-      <c r="D13" s="2" t="n">
+      <c r="D13" t="n">
         <v>12.91</v>
       </c>
-      <c r="E13" s="2" t="n">
+      <c r="E13" t="n">
         <v>17.98</v>
       </c>
       <c r="F13" s="2" t="n">
@@ -1764,28 +1764,28 @@
       <c r="I13" s="2" t="n">
         <v>31.93</v>
       </c>
-      <c r="J13" s="2" t="n">
+      <c r="J13" t="n">
         <v>1.29</v>
       </c>
       <c r="K13" s="2" t="n">
         <v>1752</v>
       </c>
-      <c r="L13" s="2" t="n">
+      <c r="L13" t="n">
         <v>11.03</v>
       </c>
-      <c r="M13" s="2" t="n">
+      <c r="M13" t="n">
         <v>155</v>
       </c>
-      <c r="N13" s="2" t="n">
+      <c r="N13" t="n">
         <v>667.27</v>
       </c>
-      <c r="O13" s="2" t="n">
+      <c r="O13" t="n">
         <v>42</v>
       </c>
-      <c r="P13" s="2" t="n">
+      <c r="P13" t="n">
         <v>2071</v>
       </c>
-      <c r="Q13" s="2" t="n">
+      <c r="Q13" t="n">
         <v>5670</v>
       </c>
       <c r="R13" s="2" t="n">
@@ -1794,25 +1794,25 @@
       <c r="S13" s="2" t="n">
         <v>24.78</v>
       </c>
-      <c r="T13" s="2" t="n">
+      <c r="T13" t="n">
         <v>12.24</v>
       </c>
-      <c r="U13" s="2" t="n">
+      <c r="U13" t="n">
         <v>42.13</v>
       </c>
-      <c r="V13" s="2" t="n">
+      <c r="V13" t="n">
         <v>0</v>
       </c>
-      <c r="W13" s="2" t="n">
+      <c r="W13" t="n">
         <v>5</v>
       </c>
-      <c r="X13" s="2" t="n">
+      <c r="X13" s="3" t="n">
         <v>14.13</v>
       </c>
-      <c r="Y13" s="2" t="n">
+      <c r="Y13" s="3" t="n">
         <v>3.28</v>
       </c>
-      <c r="Z13" s="2" t="n">
+      <c r="Z13" t="n">
         <v>1.92</v>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1820,7 +1820,7 @@
           <t>Information Technology</t>
         </is>
       </c>
-      <c r="AB13" s="2" t="n">
+      <c r="AB13" t="n">
         <v>35517</v>
       </c>
       <c r="AC13" s="2" t="n">
@@ -1846,10 +1846,10 @@
           <t>Mar 2024</t>
         </is>
       </c>
-      <c r="D14" s="2" t="n">
+      <c r="D14" t="n">
         <v>15.66</v>
       </c>
-      <c r="E14" s="2" t="n">
+      <c r="E14" t="n">
         <v>21.37</v>
       </c>
       <c r="F14" s="2" t="n">
@@ -1864,55 +1864,55 @@
       <c r="I14" s="2" t="n">
         <v>41</v>
       </c>
-      <c r="J14" s="2" t="n">
+      <c r="J14" t="n">
         <v>1.19</v>
       </c>
       <c r="K14" s="2" t="n">
         <v>3556</v>
       </c>
-      <c r="L14" s="2" t="n">
+      <c r="L14" t="n">
         <v>7.18</v>
       </c>
-      <c r="M14" s="2" t="n">
+      <c r="M14" t="n">
         <v>57</v>
       </c>
-      <c r="N14" s="2" t="n">
+      <c r="N14" t="n">
         <v>195.08</v>
       </c>
-      <c r="O14" s="2" t="n">
+      <c r="O14" t="n">
         <v>58</v>
       </c>
-      <c r="P14" s="2" t="n">
+      <c r="P14" t="n">
         <v>2474</v>
       </c>
-      <c r="Q14" s="2" t="n">
+      <c r="Q14" t="n">
         <v>6104</v>
       </c>
-      <c r="R14" s="2" t="n">
+      <c r="R14" s="3" t="n">
         <v>13.03</v>
       </c>
       <c r="S14" s="2" t="n">
         <v>20.28</v>
       </c>
-      <c r="T14" s="2" t="n">
+      <c r="T14" t="n">
         <v>20.97</v>
       </c>
-      <c r="U14" s="2" t="n">
+      <c r="U14" t="n">
         <v>17.8</v>
       </c>
-      <c r="V14" s="2" t="n">
+      <c r="V14" t="n">
         <v>0</v>
       </c>
-      <c r="W14" s="2" t="n">
+      <c r="W14" t="n">
         <v>5</v>
       </c>
-      <c r="X14" s="2" t="n">
+      <c r="X14" s="3" t="n">
         <v>59.65</v>
       </c>
-      <c r="Y14" s="2" t="n">
+      <c r="Y14" s="3" t="n">
         <v>17.43</v>
       </c>
-      <c r="Z14" s="2" t="n">
+      <c r="Z14" t="n">
         <v>1.71</v>
       </c>
       <c r="AA14" t="inlineStr">
@@ -1920,7 +1920,7 @@
           <t>Materials</t>
         </is>
       </c>
-      <c r="AB14" s="2" t="n">
+      <c r="AB14" t="n">
         <v>35495</v>
       </c>
       <c r="AC14" s="2" t="n">
@@ -1946,10 +1946,10 @@
           <t>Mar 2024</t>
         </is>
       </c>
-      <c r="D15" s="2" t="n">
+      <c r="D15" t="n">
         <v>19.82</v>
       </c>
-      <c r="E15" s="2" t="n">
+      <c r="E15" t="n">
         <v>26.84</v>
       </c>
       <c r="F15" s="2" t="n">
@@ -1964,55 +1964,55 @@
       <c r="I15" s="2" t="n">
         <v>58.33</v>
       </c>
-      <c r="J15" s="2" t="n">
+      <c r="J15" t="n">
         <v>0.57</v>
       </c>
       <c r="K15" s="2" t="n">
         <v>11372</v>
       </c>
-      <c r="L15" s="2" t="n">
+      <c r="L15" t="n">
         <v>1.57</v>
       </c>
-      <c r="M15" s="2" t="n">
+      <c r="M15" t="n">
         <v>40</v>
       </c>
-      <c r="N15" s="2" t="n">
+      <c r="N15" t="n">
         <v>265.28</v>
       </c>
-      <c r="O15" s="2" t="n">
+      <c r="O15" t="n">
         <v>34</v>
       </c>
-      <c r="P15" s="2" t="n">
+      <c r="P15" t="n">
         <v>3274</v>
       </c>
-      <c r="Q15" s="2" t="n">
+      <c r="Q15" t="n">
         <v>12135</v>
       </c>
-      <c r="R15" s="2" t="n">
+      <c r="R15" s="3" t="n">
         <v>10.78</v>
       </c>
       <c r="S15" s="2" t="n">
         <v>24.54</v>
       </c>
-      <c r="T15" s="2" t="n">
+      <c r="T15" t="n">
         <v>29.46</v>
       </c>
-      <c r="U15" s="2" t="n">
+      <c r="U15" t="n">
         <v>13.13</v>
       </c>
-      <c r="V15" s="2" t="n">
+      <c r="V15" t="n">
         <v>1</v>
       </c>
-      <c r="W15" s="2" t="n">
+      <c r="W15" t="n">
         <v>4</v>
       </c>
-      <c r="X15" s="2" t="n">
+      <c r="X15" s="3" t="n">
         <v>113.17</v>
       </c>
-      <c r="Y15" s="2" t="n">
+      <c r="Y15" s="3" t="n">
         <v>17.06</v>
       </c>
-      <c r="Z15" s="2" t="n">
+      <c r="Z15" t="n">
         <v>0.75</v>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2020,7 +2020,7 @@
           <t>Healthcare</t>
         </is>
       </c>
-      <c r="AB15" s="2" t="n">
+      <c r="AB15" t="n">
         <v>48497</v>
       </c>
       <c r="AC15" s="2" t="n">
@@ -2046,10 +2046,10 @@
           <t>Mar 2024</t>
         </is>
       </c>
-      <c r="D16" s="2" t="n">
+      <c r="D16" t="n">
         <v>9.369999999999999</v>
       </c>
-      <c r="E16" s="2" t="n">
+      <c r="E16" t="n">
         <v>87.42</v>
       </c>
       <c r="F16" s="2" t="n">
@@ -2064,55 +2064,55 @@
       <c r="I16" s="2" t="n">
         <v>160.03</v>
       </c>
-      <c r="J16" s="2" t="n">
+      <c r="J16" t="n">
         <v>0.32</v>
       </c>
       <c r="K16" s="2" t="n">
         <v>486</v>
       </c>
-      <c r="L16" s="2" t="n">
+      <c r="L16" t="n">
         <v>9.380000000000001</v>
       </c>
-      <c r="M16" s="2" t="n">
+      <c r="M16" t="n">
         <v>39</v>
       </c>
-      <c r="N16" s="2" t="n">
+      <c r="N16" t="n">
         <v>24.76</v>
       </c>
-      <c r="O16" s="2" t="n">
+      <c r="O16" t="n">
         <v>28</v>
       </c>
-      <c r="P16" s="2" t="n">
+      <c r="P16" t="n">
         <v>35</v>
       </c>
-      <c r="Q16" s="2" t="n">
+      <c r="Q16" t="n">
         <v>2407</v>
       </c>
-      <c r="R16" s="2" t="n">
+      <c r="R16" s="3" t="n">
         <v>12.91</v>
       </c>
-      <c r="S16" s="2" t="n">
+      <c r="S16" s="3" t="n">
         <v>12.84</v>
       </c>
-      <c r="T16" s="2" t="n">
+      <c r="T16" t="n">
         <v>11.14</v>
       </c>
-      <c r="U16" s="2" t="n">
+      <c r="U16" t="n">
         <v>18.99</v>
       </c>
-      <c r="V16" s="2" t="n">
+      <c r="V16" t="n">
         <v>0</v>
       </c>
-      <c r="W16" s="2" t="n">
+      <c r="W16" t="n">
         <v>3</v>
       </c>
-      <c r="X16" s="2" t="n">
+      <c r="X16" s="3" t="n">
         <v>68.59999999999999</v>
       </c>
-      <c r="Y16" s="2" t="n">
+      <c r="Y16" s="3" t="n">
         <v>108.05</v>
       </c>
-      <c r="Z16" s="2" t="n">
+      <c r="Z16" t="n">
         <v>1.05</v>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2120,7 +2120,7 @@
           <t>Financials</t>
         </is>
       </c>
-      <c r="AB16" s="2" t="n">
+      <c r="AB16" t="n">
         <v>20487</v>
       </c>
       <c r="AC16" s="2" t="n">
@@ -2146,10 +2146,10 @@
           <t>Mar 2024</t>
         </is>
       </c>
-      <c r="D17" s="2" t="n">
+      <c r="D17" t="n">
         <v>24.2</v>
       </c>
-      <c r="E17" s="2" t="n">
+      <c r="E17" t="n">
         <v>26.18</v>
       </c>
       <c r="F17" s="2" t="n">
@@ -2164,55 +2164,55 @@
       <c r="I17" s="2" t="n">
         <v>114.71</v>
       </c>
-      <c r="J17" s="2" t="n">
+      <c r="J17" t="n">
         <v>0.72</v>
       </c>
       <c r="K17" s="2" t="n">
         <v>890</v>
       </c>
-      <c r="L17" s="2" t="n">
+      <c r="L17" t="n">
         <v>17.14</v>
       </c>
-      <c r="M17" s="2" t="n">
+      <c r="M17" t="n">
         <v>146</v>
       </c>
-      <c r="N17" s="2" t="n">
+      <c r="N17" t="n">
         <v>668.33</v>
       </c>
-      <c r="O17" s="2" t="n">
+      <c r="O17" t="n">
         <v>35</v>
       </c>
-      <c r="P17" s="2" t="n">
+      <c r="P17" t="n">
         <v>419</v>
       </c>
-      <c r="Q17" s="2" t="n">
+      <c r="Q17" t="n">
         <v>3724</v>
       </c>
-      <c r="R17" s="2" t="n">
+      <c r="R17" s="3" t="n">
         <v>11.04</v>
       </c>
-      <c r="S17" s="2" t="n">
+      <c r="S17" s="3" t="n">
         <v>12.68</v>
       </c>
-      <c r="T17" s="2" t="n">
+      <c r="T17" t="n">
         <v>12.51</v>
       </c>
-      <c r="U17" s="2" t="n">
+      <c r="U17" t="n">
         <v>23.78</v>
       </c>
-      <c r="V17" s="2" t="n">
+      <c r="V17" t="n">
         <v>0</v>
       </c>
-      <c r="W17" s="2" t="n">
+      <c r="W17" t="n">
         <v>4</v>
       </c>
-      <c r="X17" s="2" t="n">
+      <c r="X17" s="3" t="n">
         <v>11.22</v>
       </c>
-      <c r="Y17" s="2" t="n">
+      <c r="Y17" s="3" t="n">
         <v>2.45</v>
       </c>
-      <c r="Z17" s="2" t="n">
+      <c r="Z17" t="n">
         <v>2.14</v>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2220,7 +2220,7 @@
           <t>Consumer Discretionary</t>
         </is>
       </c>
-      <c r="AB17" s="2" t="n">
+      <c r="AB17" t="n">
         <v>16536</v>
       </c>
       <c r="AC17" s="2" t="n">
@@ -2246,10 +2246,10 @@
           <t>Mar 2024</t>
         </is>
       </c>
-      <c r="D18" s="2" t="n">
+      <c r="D18" t="n">
         <v>19.91</v>
       </c>
-      <c r="E18" s="2" t="n">
+      <c r="E18" t="n">
         <v>28.32</v>
       </c>
       <c r="F18" s="2" t="n">
@@ -2264,55 +2264,55 @@
       <c r="I18" s="2" t="n">
         <v>51.71</v>
       </c>
-      <c r="J18" s="2" t="n">
+      <c r="J18" t="n">
         <v>0.72</v>
       </c>
       <c r="K18" s="2" t="n">
         <v>509</v>
       </c>
-      <c r="L18" s="2" t="n">
+      <c r="L18" t="n">
         <v>14.4</v>
       </c>
-      <c r="M18" s="2" t="n">
+      <c r="M18" t="n">
         <v>67</v>
       </c>
-      <c r="N18" s="2" t="n">
+      <c r="N18" t="n">
         <v>340.41</v>
       </c>
-      <c r="O18" s="2" t="n">
+      <c r="O18" t="n">
         <v>12</v>
       </c>
-      <c r="P18" s="2" t="n">
+      <c r="P18" t="n">
         <v>2002</v>
       </c>
-      <c r="Q18" s="2" t="n">
+      <c r="Q18" t="n">
         <v>4543</v>
       </c>
-      <c r="R18" s="2" t="n">
+      <c r="R18" s="3" t="n">
         <v>12.64</v>
       </c>
       <c r="S18" s="2" t="n">
         <v>23.39</v>
       </c>
-      <c r="T18" s="2" t="n">
+      <c r="T18" t="n">
         <v>23.84</v>
       </c>
-      <c r="U18" s="2" t="n">
+      <c r="U18" t="n">
         <v>13.72</v>
       </c>
-      <c r="V18" s="2" t="n">
+      <c r="V18" t="n">
         <v>0</v>
       </c>
-      <c r="W18" s="2" t="n">
+      <c r="W18" t="n">
         <v>4</v>
       </c>
-      <c r="X18" s="2" t="n">
+      <c r="X18" s="3" t="n">
         <v>117.76</v>
       </c>
-      <c r="Y18" s="2" t="n">
+      <c r="Y18" s="3" t="n">
         <v>23.18</v>
       </c>
-      <c r="Z18" s="2" t="n">
+      <c r="Z18" t="n">
         <v>0.15</v>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2320,7 +2320,7 @@
           <t>Healthcare</t>
         </is>
       </c>
-      <c r="AB18" s="2" t="n">
+      <c r="AB18" t="n">
         <v>28011</v>
       </c>
       <c r="AC18" s="2" t="n">
@@ -2346,46 +2346,46 @@
           <t>Mar 2024</t>
         </is>
       </c>
-      <c r="D19" s="2" t="n">
+      <c r="D19" t="n">
         <v>13.94</v>
       </c>
-      <c r="E19" s="2" t="n">
+      <c r="E19" t="n">
         <v>41.75</v>
       </c>
       <c r="F19" s="2" t="n">
         <v>16.72</v>
       </c>
-      <c r="G19" s="2" t="n">
+      <c r="G19" s="3" t="n">
         <v>3.16</v>
       </c>
-      <c r="H19" s="2" t="n">
+      <c r="H19" s="3" t="n">
         <v>14.87</v>
       </c>
-      <c r="I19" s="2" t="n">
+      <c r="I19" s="3" t="n">
         <v>1.61</v>
       </c>
-      <c r="J19" s="2" t="n">
+      <c r="J19" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="K19" s="2" t="n">
         <v>13296</v>
       </c>
-      <c r="L19" s="2" t="n">
+      <c r="L19" t="n">
         <v>1.58</v>
       </c>
-      <c r="M19" s="2" t="n">
+      <c r="M19" t="n">
         <v>17</v>
       </c>
-      <c r="N19" s="2" t="n">
+      <c r="N19" t="n">
         <v>50.79</v>
       </c>
-      <c r="O19" s="2" t="n">
+      <c r="O19" t="n">
         <v>19</v>
       </c>
-      <c r="P19" s="2" t="n">
+      <c r="P19" t="n">
         <v>1369780</v>
       </c>
-      <c r="Q19" s="2" t="n">
+      <c r="Q19" t="n">
         <v>15046</v>
       </c>
       <c r="R19" s="2" t="n">
@@ -2394,25 +2394,25 @@
       <c r="S19" s="2" t="n">
         <v>85.78</v>
       </c>
-      <c r="T19" s="2" t="n">
+      <c r="T19" t="n">
         <v>53.42</v>
       </c>
-      <c r="U19" s="2" t="n">
+      <c r="U19" t="n">
         <v>16.3</v>
       </c>
-      <c r="V19" s="2" t="n">
+      <c r="V19" t="n">
         <v>0</v>
       </c>
-      <c r="W19" s="2" t="n">
+      <c r="W19" t="n">
         <v>2</v>
       </c>
-      <c r="X19" s="2" t="n">
+      <c r="X19" s="3" t="n">
         <v>103.58</v>
       </c>
-      <c r="Y19" s="2" t="n">
+      <c r="Y19" s="3" t="n">
         <v>34.67</v>
       </c>
-      <c r="Z19" s="2" t="n">
+      <c r="Z19" t="n">
         <v>1.08</v>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2420,7 +2420,7 @@
           <t>Financials</t>
         </is>
       </c>
-      <c r="AB19" s="2" t="n">
+      <c r="AB19" t="n">
         <v>110519</v>
       </c>
       <c r="AC19" s="2" t="n">
@@ -2446,10 +2446,10 @@
           <t>Mar 2024</t>
         </is>
       </c>
-      <c r="D20" s="2" t="n">
+      <c r="D20" t="n">
         <v>9.51</v>
       </c>
-      <c r="E20" s="2" t="n">
+      <c r="E20" t="n">
         <v>13.13</v>
       </c>
       <c r="F20" s="2" t="n">
@@ -2464,55 +2464,55 @@
       <c r="I20" s="2" t="n">
         <v>117.91</v>
       </c>
-      <c r="J20" s="2" t="n">
+      <c r="J20" t="n">
         <v>1.23</v>
       </c>
       <c r="K20" s="2" t="n">
         <v>4936</v>
       </c>
-      <c r="L20" s="2" t="n">
+      <c r="L20" t="n">
         <v>8.359999999999999</v>
       </c>
-      <c r="M20" s="2" t="n">
+      <c r="M20" t="n">
         <v>429</v>
       </c>
-      <c r="N20" s="2" t="n">
+      <c r="N20" t="n">
         <v>545.45</v>
       </c>
-      <c r="O20" s="2" t="n">
+      <c r="O20" t="n">
         <v>29</v>
       </c>
-      <c r="P20" s="2" t="n">
+      <c r="P20" t="n">
         <v>119</v>
       </c>
-      <c r="Q20" s="2" t="n">
+      <c r="Q20" t="n">
         <v>16801</v>
       </c>
-      <c r="R20" s="2" t="n">
+      <c r="R20" s="3" t="n">
         <v>10.51</v>
       </c>
-      <c r="S20" s="2" t="n">
+      <c r="S20" s="3" t="n">
         <v>12.01</v>
       </c>
-      <c r="T20" s="2" t="n">
+      <c r="T20" t="n">
         <v>11.14</v>
       </c>
-      <c r="U20" s="2" t="n">
+      <c r="U20" t="n">
         <v>26.32</v>
       </c>
-      <c r="V20" s="2" t="n">
+      <c r="V20" t="n">
         <v>1</v>
       </c>
-      <c r="W20" s="2" t="n">
+      <c r="W20" t="n">
         <v>4</v>
       </c>
-      <c r="X20" s="2" t="n">
+      <c r="X20" s="3" t="n">
         <v>11.71</v>
       </c>
-      <c r="Y20" s="2" t="n">
+      <c r="Y20" s="3" t="n">
         <v>9.210000000000001</v>
       </c>
-      <c r="Z20" s="2" t="n">
+      <c r="Z20" t="n">
         <v>0.58</v>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2520,7 +2520,7 @@
           <t>Consumer Discretionary</t>
         </is>
       </c>
-      <c r="AB20" s="2" t="n">
+      <c r="AB20" t="n">
         <v>141858</v>
       </c>
       <c r="AC20" s="2" t="n">
@@ -2546,10 +2546,10 @@
           <t>Mar 2024</t>
         </is>
       </c>
-      <c r="D21" s="2" t="n">
+      <c r="D21" t="n">
         <v>14.11</v>
       </c>
-      <c r="E21" s="2" t="n">
+      <c r="E21" t="n">
         <v>21.87</v>
       </c>
       <c r="F21" s="2" t="n">
@@ -2564,55 +2564,55 @@
       <c r="I21" s="2" t="n">
         <v>54.33</v>
       </c>
-      <c r="J21" s="2" t="n">
+      <c r="J21" t="n">
         <v>1.03</v>
       </c>
       <c r="K21" s="2" t="n">
         <v>955</v>
       </c>
-      <c r="L21" s="2" t="n">
+      <c r="L21" t="n">
         <v>14.29</v>
       </c>
-      <c r="M21" s="2" t="n">
+      <c r="M21" t="n">
         <v>34</v>
       </c>
-      <c r="N21" s="2" t="n">
+      <c r="N21" t="n">
         <v>164.84</v>
       </c>
-      <c r="O21" s="2" t="n">
+      <c r="O21" t="n">
         <v>47</v>
       </c>
-      <c r="P21" s="2" t="n">
+      <c r="P21" t="n">
         <v>382</v>
       </c>
-      <c r="Q21" s="2" t="n">
+      <c r="Q21" t="n">
         <v>2724</v>
       </c>
-      <c r="R21" s="2" t="n">
+      <c r="R21" s="3" t="n">
         <v>11.84</v>
       </c>
-      <c r="S21" s="2" t="n">
+      <c r="S21" s="3" t="n">
         <v>13.49</v>
       </c>
-      <c r="T21" s="2" t="n">
+      <c r="T21" t="n">
         <v>13.56</v>
       </c>
-      <c r="U21" s="2" t="n">
+      <c r="U21" t="n">
         <v>19.3</v>
       </c>
-      <c r="V21" s="2" t="n">
+      <c r="V21" t="n">
         <v>1</v>
       </c>
-      <c r="W21" s="2" t="n">
+      <c r="W21" t="n">
         <v>5</v>
       </c>
-      <c r="X21" s="2" t="n">
+      <c r="X21" s="3" t="n">
         <v>20.14</v>
       </c>
-      <c r="Y21" s="2" t="n">
+      <c r="Y21" s="3" t="n">
         <v>4.15</v>
       </c>
-      <c r="Z21" s="2" t="n">
+      <c r="Z21" t="n">
         <v>6.86</v>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2620,7 +2620,7 @@
           <t>Materials</t>
         </is>
       </c>
-      <c r="AB21" s="2" t="n">
+      <c r="AB21" t="n">
         <v>12383</v>
       </c>
       <c r="AC21" s="2" t="n">
@@ -2646,10 +2646,10 @@
           <t>Sep 2024</t>
         </is>
       </c>
-      <c r="D22" s="2" t="n">
+      <c r="D22" t="n">
         <v>12.22</v>
       </c>
-      <c r="E22" s="2" t="n">
+      <c r="E22" t="n">
         <v>13.96</v>
       </c>
       <c r="F22" s="2" t="n">
@@ -2664,55 +2664,55 @@
       <c r="I22" s="2" t="n">
         <v>67.15000000000001</v>
       </c>
-      <c r="J22" s="2" t="n">
+      <c r="J22" t="n">
         <v>0.88</v>
       </c>
       <c r="K22" s="2" t="n">
         <v>1168</v>
       </c>
-      <c r="L22" s="2" t="n">
+      <c r="L22" t="n">
         <v>2.26</v>
       </c>
-      <c r="M22" s="2" t="n">
+      <c r="M22" t="n">
         <v>76</v>
       </c>
-      <c r="N22" s="2" t="n">
+      <c r="N22" t="n">
         <v>216.3</v>
       </c>
-      <c r="O22" s="2" t="n">
+      <c r="O22" t="n">
         <v>16</v>
       </c>
-      <c r="P22" s="2" t="n">
+      <c r="P22" t="n">
         <v>279</v>
       </c>
-      <c r="Q22" s="2" t="n">
+      <c r="Q22" t="n">
         <v>1670</v>
       </c>
-      <c r="R22" s="2" t="n">
+      <c r="R22" s="3" t="n">
         <v>11.19</v>
       </c>
       <c r="S22" s="2" t="n">
         <v>19.85</v>
       </c>
-      <c r="T22" s="2" t="n">
+      <c r="T22" t="n">
         <v>19.64</v>
       </c>
-      <c r="U22" s="2" t="n">
+      <c r="U22" t="n">
         <v>19</v>
       </c>
-      <c r="V22" s="2" t="n">
+      <c r="V22" t="n">
         <v>0</v>
       </c>
-      <c r="W22" s="2" t="n">
+      <c r="W22" t="n">
         <v>4</v>
       </c>
-      <c r="X22" s="2" t="n">
+      <c r="X22" s="3" t="n">
         <v>39.4</v>
       </c>
-      <c r="Y22" s="2" t="n">
+      <c r="Y22" s="3" t="n">
         <v>13.84</v>
       </c>
-      <c r="Z22" s="2" t="n">
+      <c r="Z22" t="n">
         <v>0.53</v>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2720,7 +2720,7 @@
           <t>Industrials</t>
         </is>
       </c>
-      <c r="AB22" s="2" t="n">
+      <c r="AB22" t="n">
         <v>22240</v>
       </c>
       <c r="AC22" s="2" t="n">
@@ -2746,10 +2746,10 @@
           <t>Mar 2024</t>
         </is>
       </c>
-      <c r="D23" s="2" t="n">
+      <c r="D23" t="n">
         <v>6.84</v>
       </c>
-      <c r="E23" s="2" t="n">
+      <c r="E23" t="n">
         <v>10.12</v>
       </c>
       <c r="F23" s="2" t="n">
@@ -2764,55 +2764,55 @@
       <c r="I23" s="2" t="n">
         <v>25.36</v>
       </c>
-      <c r="J23" s="2" t="n">
+      <c r="J23" t="n">
         <v>1.5</v>
       </c>
       <c r="K23" s="2" t="n">
         <v>335</v>
       </c>
-      <c r="L23" s="2" t="n">
+      <c r="L23" t="n">
         <v>8.699999999999999</v>
       </c>
-      <c r="M23" s="2" t="n">
+      <c r="M23" t="n">
         <v>20</v>
       </c>
-      <c r="N23" s="2" t="n">
+      <c r="N23" t="n">
         <v>118.21</v>
       </c>
-      <c r="O23" s="2" t="n">
+      <c r="O23" t="n">
         <v>44</v>
       </c>
-      <c r="P23" s="2" t="n">
+      <c r="P23" t="n">
         <v>303</v>
       </c>
-      <c r="Q23" s="2" t="n">
+      <c r="Q23" t="n">
         <v>1953</v>
       </c>
-      <c r="R23" s="2" t="n">
+      <c r="R23" s="3" t="n">
         <v>13.04</v>
       </c>
-      <c r="S23" s="2" t="n">
+      <c r="S23" s="3" t="n">
         <v>10.03</v>
       </c>
-      <c r="T23" s="2" t="n">
+      <c r="T23" t="n">
         <v>9</v>
       </c>
-      <c r="U23" s="2" t="n">
+      <c r="U23" t="n">
         <v>21.14</v>
       </c>
-      <c r="V23" s="2" t="n">
+      <c r="V23" t="n">
         <v>0</v>
       </c>
-      <c r="W23" s="2" t="n">
+      <c r="W23" t="n">
         <v>4</v>
       </c>
-      <c r="X23" s="2" t="n">
+      <c r="X23" s="3" t="n">
         <v>106.42</v>
       </c>
-      <c r="Y23" s="2" t="n">
+      <c r="Y23" s="3" t="n">
         <v>18</v>
       </c>
-      <c r="Z23" s="2" t="n">
+      <c r="Z23" t="n">
         <v>2.07</v>
       </c>
       <c r="AA23" t="inlineStr">
@@ -2820,7 +2820,7 @@
           <t>Industrials</t>
         </is>
       </c>
-      <c r="AB23" s="2" t="n">
+      <c r="AB23" t="n">
         <v>18590</v>
       </c>
       <c r="AC23" s="2" t="n">
@@ -3044,10 +3044,10 @@
           <t>Mar 2024</t>
         </is>
       </c>
-      <c r="D2" s="2" t="n">
+      <c r="D2" t="n">
         <v>11.85</v>
       </c>
-      <c r="E2" s="2" t="n">
+      <c r="E2" t="n">
         <v>76.3</v>
       </c>
       <c r="F2" s="2" t="n">
@@ -3062,28 +3062,28 @@
       <c r="I2" s="2" t="n">
         <v>22.61</v>
       </c>
-      <c r="J2" s="2" t="n">
+      <c r="J2" t="n">
         <v>56.39</v>
       </c>
       <c r="K2" s="2" t="n">
         <v>9424</v>
       </c>
-      <c r="L2" s="2" t="n">
+      <c r="L2" t="n">
         <v>17.07</v>
       </c>
-      <c r="M2" s="2" t="n">
+      <c r="M2" t="n">
         <v>212</v>
       </c>
-      <c r="N2" s="2" t="n">
+      <c r="N2" t="n">
         <v>19.06</v>
       </c>
-      <c r="O2" s="2" t="n">
+      <c r="O2" t="n">
         <v>0</v>
       </c>
-      <c r="P2" s="2" t="n">
+      <c r="P2" t="n">
         <v>17</v>
       </c>
-      <c r="Q2" s="2" t="n">
+      <c r="Q2" t="n">
         <v>21183</v>
       </c>
       <c r="R2" s="2" t="n">
@@ -3092,25 +3092,25 @@
       <c r="S2" s="2" t="n">
         <v>120.69</v>
       </c>
-      <c r="T2" s="2" t="n">
+      <c r="T2" t="n">
         <v>121.24</v>
       </c>
-      <c r="U2" s="2" t="n">
+      <c r="U2" t="n">
         <v>67.58</v>
       </c>
-      <c r="V2" s="2" t="n">
+      <c r="V2" t="n">
         <v>0</v>
       </c>
-      <c r="W2" s="2" t="n">
+      <c r="W2" t="n">
         <v>5</v>
       </c>
-      <c r="X2" s="2" t="n">
+      <c r="X2" s="3" t="n">
         <v>28.1</v>
       </c>
-      <c r="Y2" s="2" t="n">
+      <c r="Y2" s="3" t="n">
         <v>312.51</v>
       </c>
-      <c r="Z2" s="2" t="n">
+      <c r="Z2" t="n">
         <v>0</v>
       </c>
       <c r="AA2" t="inlineStr">
@@ -3118,7 +3118,7 @@
           <t>Consumer Discretionary</t>
         </is>
       </c>
-      <c r="AB2" s="2" t="n">
+      <c r="AB2" t="n">
         <v>68904</v>
       </c>
       <c r="AC2" s="2" t="n">
@@ -3144,10 +3144,10 @@
           <t>Mar 2024</t>
         </is>
       </c>
-      <c r="D3" s="2" t="n">
+      <c r="D3" t="n">
         <v>26.02</v>
       </c>
-      <c r="E3" s="2" t="n">
+      <c r="E3" t="n">
         <v>34.33</v>
       </c>
       <c r="F3" s="2" t="n">
@@ -3162,28 +3162,28 @@
       <c r="I3" s="2" t="n">
         <v>82.73999999999999</v>
       </c>
-      <c r="J3" s="2" t="n">
+      <c r="J3" t="n">
         <v>0.7</v>
       </c>
       <c r="K3" s="2" t="n">
         <v>667</v>
       </c>
-      <c r="L3" s="2" t="n">
+      <c r="L3" t="n">
         <v>5.04</v>
       </c>
-      <c r="M3" s="2" t="n">
+      <c r="M3" t="n">
         <v>14</v>
       </c>
-      <c r="N3" s="2" t="n">
+      <c r="N3" t="n">
         <v>20.19</v>
       </c>
-      <c r="O3" s="2" t="n">
+      <c r="O3" t="n">
         <v>47</v>
       </c>
-      <c r="P3" s="2" t="n">
+      <c r="P3" t="n">
         <v>60</v>
       </c>
-      <c r="Q3" s="2" t="n">
+      <c r="Q3" t="n">
         <v>882</v>
       </c>
       <c r="R3" s="2" t="n">
@@ -3192,25 +3192,25 @@
       <c r="S3" s="2" t="n">
         <v>29.17</v>
       </c>
-      <c r="T3" s="2" t="n">
+      <c r="T3" t="n">
         <v>28.47</v>
       </c>
-      <c r="U3" s="2" t="n">
+      <c r="U3" t="n">
         <v>76.47</v>
       </c>
-      <c r="V3" s="2" t="n">
+      <c r="V3" t="n">
         <v>1</v>
       </c>
-      <c r="W3" s="2" t="n">
+      <c r="W3" t="n">
         <v>4</v>
       </c>
-      <c r="X3" s="2" t="n">
+      <c r="X3" s="3" t="n">
         <v>799.9299999999999</v>
       </c>
-      <c r="Y3" s="2" t="n">
+      <c r="Y3" s="3" t="n">
         <v>554.6799999999999</v>
       </c>
-      <c r="Z3" s="2" t="n">
+      <c r="Z3" t="n">
         <v>0.42</v>
       </c>
       <c r="AA3" t="inlineStr">
@@ -3218,7 +3218,7 @@
           <t>Consumer Discretionary</t>
         </is>
       </c>
-      <c r="AB3" s="2" t="n">
+      <c r="AB3" t="n">
         <v>4270</v>
       </c>
       <c r="AC3" s="2" t="n">
@@ -3244,10 +3244,10 @@
           <t>Mar 2024</t>
         </is>
       </c>
-      <c r="D4" s="2" t="n">
+      <c r="D4" t="n">
         <v>11.94</v>
       </c>
-      <c r="E4" s="2" t="n">
+      <c r="E4" t="n">
         <v>15.93</v>
       </c>
       <c r="F4" s="2" t="n">
@@ -3259,31 +3259,31 @@
       <c r="H4" s="2" t="n">
         <v>0.43</v>
       </c>
-      <c r="I4" s="2" t="n">
+      <c r="I4" s="3" t="n">
         <v>8.039999999999999</v>
       </c>
-      <c r="J4" s="2" t="n">
+      <c r="J4" t="n">
         <v>1.73</v>
       </c>
       <c r="K4" s="2" t="n">
         <v>841</v>
       </c>
-      <c r="L4" s="2" t="n">
+      <c r="L4" t="n">
         <v>4.11</v>
       </c>
-      <c r="M4" s="2" t="n">
+      <c r="M4" t="n">
         <v>42</v>
       </c>
-      <c r="N4" s="2" t="n">
+      <c r="N4" t="n">
         <v>113</v>
       </c>
-      <c r="O4" s="2" t="n">
+      <c r="O4" t="n">
         <v>8</v>
       </c>
-      <c r="P4" s="2" t="n">
+      <c r="P4" t="n">
         <v>1753</v>
       </c>
-      <c r="Q4" s="2" t="n">
+      <c r="Q4" t="n">
         <v>1349</v>
       </c>
       <c r="R4" s="2" t="n">
@@ -3292,25 +3292,25 @@
       <c r="S4" s="2" t="n">
         <v>73.11</v>
       </c>
-      <c r="T4" s="2" t="n">
+      <c r="T4" t="n">
         <v>69.52</v>
       </c>
-      <c r="U4" s="2" t="n">
+      <c r="U4" t="n">
         <v>68.36</v>
       </c>
-      <c r="V4" s="2" t="n">
+      <c r="V4" t="n">
         <v>1</v>
       </c>
-      <c r="W4" s="2" t="n">
+      <c r="W4" t="n">
         <v>5</v>
       </c>
-      <c r="X4" s="2" t="n">
+      <c r="X4" s="3" t="n">
         <v>19.88</v>
       </c>
-      <c r="Y4" s="2" t="n">
+      <c r="Y4" s="3" t="n">
         <v>7.39</v>
       </c>
-      <c r="Z4" s="2" t="n">
+      <c r="Z4" t="n">
         <v>0.96</v>
       </c>
       <c r="AA4" t="inlineStr">
@@ -3318,7 +3318,7 @@
           <t>Consumer Discretionary</t>
         </is>
       </c>
-      <c r="AB4" s="2" t="n">
+      <c r="AB4" t="n">
         <v>12375</v>
       </c>
       <c r="AC4" s="2" t="n">
@@ -3344,46 +3344,46 @@
           <t>Mar 2024</t>
         </is>
       </c>
-      <c r="D5" s="2" t="n">
+      <c r="D5" t="n">
         <v>28.89</v>
       </c>
-      <c r="E5" s="2" t="n">
+      <c r="E5" t="n">
         <v>62.41</v>
       </c>
       <c r="F5" s="2" t="n">
         <v>17.99</v>
       </c>
-      <c r="G5" s="2" t="n">
+      <c r="G5" s="3" t="n">
         <v>5.22</v>
       </c>
-      <c r="H5" s="2" t="n">
+      <c r="H5" s="3" t="n">
         <v>6.45</v>
       </c>
-      <c r="I5" s="2" t="n">
+      <c r="I5" s="3" t="n">
         <v>1.3</v>
       </c>
-      <c r="J5" s="2" t="n">
+      <c r="J5" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="K5" s="2" t="n">
         <v>12547</v>
       </c>
-      <c r="L5" s="2" t="n">
+      <c r="L5" t="n">
         <v>90.73999999999999</v>
       </c>
-      <c r="M5" s="2" t="n">
+      <c r="M5" t="n">
         <v>63</v>
       </c>
-      <c r="N5" s="2" t="n">
+      <c r="N5" t="n">
         <v>182.31</v>
       </c>
-      <c r="O5" s="2" t="n">
+      <c r="O5" t="n">
         <v>16</v>
       </c>
-      <c r="P5" s="2" t="n">
+      <c r="P5" t="n">
         <v>1651008</v>
       </c>
-      <c r="Q5" s="2" t="n">
+      <c r="Q5" t="n">
         <v>157284</v>
       </c>
       <c r="R5" s="2" t="n">
@@ -3392,25 +3392,25 @@
       <c r="S5" s="2" t="n">
         <v>51.95</v>
       </c>
-      <c r="T5" s="2" t="n">
+      <c r="T5" t="n">
         <v>55.18</v>
       </c>
-      <c r="U5" s="2" t="n">
+      <c r="U5" t="n">
         <v>21.4</v>
       </c>
-      <c r="V5" s="2" t="n">
+      <c r="V5" t="n">
         <v>0</v>
       </c>
-      <c r="W5" s="2" t="n">
+      <c r="W5" t="n">
         <v>2</v>
       </c>
-      <c r="X5" s="2" t="n">
+      <c r="X5" s="3" t="n">
         <v>115.62</v>
       </c>
-      <c r="Y5" s="2" t="n">
+      <c r="Y5" s="3" t="n">
         <v>39.95</v>
       </c>
-      <c r="Z5" s="2" t="n">
+      <c r="Z5" t="n">
         <v>0.22</v>
       </c>
       <c r="AA5" t="inlineStr">
@@ -3418,7 +3418,7 @@
           <t>Financials</t>
         </is>
       </c>
-      <c r="AB5" s="2" t="n">
+      <c r="AB5" t="n">
         <v>159516</v>
       </c>
       <c r="AC5" s="2" t="n">
@@ -3444,10 +3444,10 @@
           <t>Mar 2024</t>
         </is>
       </c>
-      <c r="D6" s="2" t="n">
+      <c r="D6" t="n">
         <v>12.91</v>
       </c>
-      <c r="E6" s="2" t="n">
+      <c r="E6" t="n">
         <v>17.98</v>
       </c>
       <c r="F6" s="2" t="n">
@@ -3462,28 +3462,28 @@
       <c r="I6" s="2" t="n">
         <v>31.93</v>
       </c>
-      <c r="J6" s="2" t="n">
+      <c r="J6" t="n">
         <v>1.29</v>
       </c>
       <c r="K6" s="2" t="n">
         <v>1752</v>
       </c>
-      <c r="L6" s="2" t="n">
+      <c r="L6" t="n">
         <v>11.03</v>
       </c>
-      <c r="M6" s="2" t="n">
+      <c r="M6" t="n">
         <v>155</v>
       </c>
-      <c r="N6" s="2" t="n">
+      <c r="N6" t="n">
         <v>667.27</v>
       </c>
-      <c r="O6" s="2" t="n">
+      <c r="O6" t="n">
         <v>42</v>
       </c>
-      <c r="P6" s="2" t="n">
+      <c r="P6" t="n">
         <v>2071</v>
       </c>
-      <c r="Q6" s="2" t="n">
+      <c r="Q6" t="n">
         <v>5670</v>
       </c>
       <c r="R6" s="2" t="n">
@@ -3492,25 +3492,25 @@
       <c r="S6" s="2" t="n">
         <v>24.78</v>
       </c>
-      <c r="T6" s="2" t="n">
+      <c r="T6" t="n">
         <v>12.24</v>
       </c>
-      <c r="U6" s="2" t="n">
+      <c r="U6" t="n">
         <v>42.13</v>
       </c>
-      <c r="V6" s="2" t="n">
+      <c r="V6" t="n">
         <v>0</v>
       </c>
-      <c r="W6" s="2" t="n">
+      <c r="W6" t="n">
         <v>5</v>
       </c>
-      <c r="X6" s="2" t="n">
+      <c r="X6" s="3" t="n">
         <v>14.13</v>
       </c>
-      <c r="Y6" s="2" t="n">
+      <c r="Y6" s="3" t="n">
         <v>3.28</v>
       </c>
-      <c r="Z6" s="2" t="n">
+      <c r="Z6" t="n">
         <v>1.92</v>
       </c>
       <c r="AA6" t="inlineStr">
@@ -3518,7 +3518,7 @@
           <t>Information Technology</t>
         </is>
       </c>
-      <c r="AB6" s="2" t="n">
+      <c r="AB6" t="n">
         <v>35517</v>
       </c>
       <c r="AC6" s="2" t="n">
@@ -3544,46 +3544,46 @@
           <t>Mar 2024</t>
         </is>
       </c>
-      <c r="D7" s="2" t="n">
+      <c r="D7" t="n">
         <v>23.07</v>
       </c>
-      <c r="E7" s="2" t="n">
+      <c r="E7" t="n">
         <v>61.41</v>
       </c>
-      <c r="F7" s="2" t="n">
+      <c r="F7" s="3" t="n">
         <v>14.34</v>
       </c>
-      <c r="G7" s="2" t="n">
+      <c r="G7" s="3" t="n">
         <v>4.89</v>
       </c>
-      <c r="H7" s="2" t="n">
+      <c r="H7" s="3" t="n">
         <v>6.81</v>
       </c>
-      <c r="I7" s="2" t="n">
+      <c r="I7" s="3" t="n">
         <v>1.4</v>
       </c>
-      <c r="J7" s="2" t="n">
+      <c r="J7" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="K7" s="2" t="n">
         <v>35669</v>
       </c>
-      <c r="L7" s="2" t="n">
+      <c r="L7" t="n">
         <v>5.85</v>
       </c>
-      <c r="M7" s="2" t="n">
+      <c r="M7" t="n">
         <v>84</v>
       </c>
-      <c r="N7" s="2" t="n">
+      <c r="N7" t="n">
         <v>600.52</v>
       </c>
-      <c r="O7" s="2" t="n">
+      <c r="O7" t="n">
         <v>23</v>
       </c>
-      <c r="P7" s="2" t="n">
+      <c r="P7" t="n">
         <v>3107503</v>
       </c>
-      <c r="Q7" s="2" t="n">
+      <c r="Q7" t="n">
         <v>19069</v>
       </c>
       <c r="R7" s="2" t="n">
@@ -3592,25 +3592,25 @@
       <c r="S7" s="2" t="n">
         <v>23.87</v>
       </c>
-      <c r="T7" s="2" t="n">
+      <c r="T7" t="n">
         <v>15.42</v>
       </c>
-      <c r="U7" s="2" t="n">
+      <c r="U7" t="n">
         <v>30.19</v>
       </c>
-      <c r="V7" s="2" t="n">
+      <c r="V7" t="n">
         <v>0</v>
       </c>
-      <c r="W7" s="2" t="n">
+      <c r="W7" t="n">
         <v>1</v>
       </c>
-      <c r="X7" s="2" t="n">
+      <c r="X7" s="3" t="n">
         <v>51.08</v>
       </c>
-      <c r="Y7" s="2" t="n">
+      <c r="Y7" s="3" t="n">
         <v>7.15</v>
       </c>
-      <c r="Z7" s="2" t="n">
+      <c r="Z7" t="n">
         <v>0.54</v>
       </c>
       <c r="AA7" t="inlineStr">
@@ -3618,7 +3618,7 @@
           <t>Financials</t>
         </is>
       </c>
-      <c r="AB7" s="2" t="n">
+      <c r="AB7" t="n">
         <v>283649</v>
       </c>
       <c r="AC7" s="2" t="n">
@@ -3644,10 +3644,10 @@
           <t>Mar 2024</t>
         </is>
       </c>
-      <c r="D8" s="2" t="n">
+      <c r="D8" t="n">
         <v>6.84</v>
       </c>
-      <c r="E8" s="2" t="n">
+      <c r="E8" t="n">
         <v>10.36</v>
       </c>
       <c r="F8" s="2" t="n">
@@ -3656,34 +3656,34 @@
       <c r="G8" s="2" t="n">
         <v>21.24</v>
       </c>
-      <c r="H8" s="2" t="n">
+      <c r="H8" s="3" t="n">
         <v>1.65</v>
       </c>
-      <c r="I8" s="2" t="n">
+      <c r="I8" s="3" t="n">
         <v>9.41</v>
       </c>
-      <c r="J8" s="2" t="n">
+      <c r="J8" t="n">
         <v>1.62</v>
       </c>
       <c r="K8" s="2" t="n">
         <v>1506</v>
       </c>
-      <c r="L8" s="2" t="n">
+      <c r="L8" t="n">
         <v>0.37</v>
       </c>
-      <c r="M8" s="2" t="n">
+      <c r="M8" t="n">
         <v>39</v>
       </c>
-      <c r="N8" s="2" t="n">
+      <c r="N8" t="n">
         <v>105.54</v>
       </c>
-      <c r="O8" s="2" t="n">
+      <c r="O8" t="n">
         <v>28</v>
       </c>
-      <c r="P8" s="2" t="n">
+      <c r="P8" t="n">
         <v>15528</v>
       </c>
-      <c r="Q8" s="2" t="n">
+      <c r="Q8" t="n">
         <v>1695</v>
       </c>
       <c r="R8" s="2" t="n">
@@ -3692,25 +3692,25 @@
       <c r="S8" s="2" t="n">
         <v>20.27</v>
       </c>
-      <c r="T8" s="2" t="n">
+      <c r="T8" t="n">
         <v>19.51</v>
       </c>
-      <c r="U8" s="2" t="n">
+      <c r="U8" t="n">
         <v>33.14</v>
       </c>
-      <c r="V8" s="2" t="n">
+      <c r="V8" t="n">
         <v>0</v>
       </c>
-      <c r="W8" s="2" t="n">
+      <c r="W8" t="n">
         <v>3</v>
       </c>
-      <c r="X8" s="2" t="n">
+      <c r="X8" s="3" t="n">
         <v>135.66</v>
       </c>
-      <c r="Y8" s="2" t="n">
+      <c r="Y8" s="3" t="n">
         <v>50.13</v>
       </c>
-      <c r="Z8" s="2" t="n">
+      <c r="Z8" t="n">
         <v>0.53</v>
       </c>
       <c r="AA8" t="inlineStr">
@@ -3718,7 +3718,7 @@
           <t>Consumer Discretionary</t>
         </is>
       </c>
-      <c r="AB8" s="2" t="n">
+      <c r="AB8" t="n">
         <v>51084</v>
       </c>
       <c r="AC8" s="2" t="n">
@@ -3744,46 +3744,46 @@
           <t>Mar 2024</t>
         </is>
       </c>
-      <c r="D9" s="2" t="n">
+      <c r="D9" t="n">
         <v>13.94</v>
       </c>
-      <c r="E9" s="2" t="n">
+      <c r="E9" t="n">
         <v>41.75</v>
       </c>
       <c r="F9" s="2" t="n">
         <v>16.72</v>
       </c>
-      <c r="G9" s="2" t="n">
+      <c r="G9" s="3" t="n">
         <v>3.16</v>
       </c>
-      <c r="H9" s="2" t="n">
+      <c r="H9" s="3" t="n">
         <v>14.87</v>
       </c>
-      <c r="I9" s="2" t="n">
+      <c r="I9" s="3" t="n">
         <v>1.61</v>
       </c>
-      <c r="J9" s="2" t="n">
+      <c r="J9" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="K9" s="2" t="n">
         <v>13296</v>
       </c>
-      <c r="L9" s="2" t="n">
+      <c r="L9" t="n">
         <v>1.58</v>
       </c>
-      <c r="M9" s="2" t="n">
+      <c r="M9" t="n">
         <v>17</v>
       </c>
-      <c r="N9" s="2" t="n">
+      <c r="N9" t="n">
         <v>50.79</v>
       </c>
-      <c r="O9" s="2" t="n">
+      <c r="O9" t="n">
         <v>19</v>
       </c>
-      <c r="P9" s="2" t="n">
+      <c r="P9" t="n">
         <v>1369780</v>
       </c>
-      <c r="Q9" s="2" t="n">
+      <c r="Q9" t="n">
         <v>15046</v>
       </c>
       <c r="R9" s="2" t="n">
@@ -3792,25 +3792,25 @@
       <c r="S9" s="2" t="n">
         <v>85.78</v>
       </c>
-      <c r="T9" s="2" t="n">
+      <c r="T9" t="n">
         <v>53.42</v>
       </c>
-      <c r="U9" s="2" t="n">
+      <c r="U9" t="n">
         <v>16.3</v>
       </c>
-      <c r="V9" s="2" t="n">
+      <c r="V9" t="n">
         <v>0</v>
       </c>
-      <c r="W9" s="2" t="n">
+      <c r="W9" t="n">
         <v>2</v>
       </c>
-      <c r="X9" s="2" t="n">
+      <c r="X9" s="3" t="n">
         <v>103.58</v>
       </c>
-      <c r="Y9" s="2" t="n">
+      <c r="Y9" s="3" t="n">
         <v>34.67</v>
       </c>
-      <c r="Z9" s="2" t="n">
+      <c r="Z9" t="n">
         <v>1.08</v>
       </c>
       <c r="AA9" t="inlineStr">
@@ -3818,7 +3818,7 @@
           <t>Financials</t>
         </is>
       </c>
-      <c r="AB9" s="2" t="n">
+      <c r="AB9" t="n">
         <v>110519</v>
       </c>
       <c r="AC9" s="2" t="n">
@@ -3844,13 +3844,13 @@
           <t>Mar 2024</t>
         </is>
       </c>
-      <c r="D10" s="2" t="n">
+      <c r="D10" t="n">
         <v>4.99</v>
       </c>
-      <c r="E10" s="2" t="n">
+      <c r="E10" t="n">
         <v>8.08</v>
       </c>
-      <c r="F10" s="2" t="n">
+      <c r="F10" s="3" t="n">
         <v>13.56</v>
       </c>
       <c r="G10" s="2" t="n">
@@ -3862,28 +3862,28 @@
       <c r="I10" s="2" t="n">
         <v>73.29000000000001</v>
       </c>
-      <c r="J10" s="2" t="n">
+      <c r="J10" t="n">
         <v>2.4</v>
       </c>
       <c r="K10" s="2" t="n">
         <v>278</v>
       </c>
-      <c r="L10" s="2" t="n">
+      <c r="L10" t="n">
         <v>4.86</v>
       </c>
-      <c r="M10" s="2" t="n">
+      <c r="M10" t="n">
         <v>39</v>
       </c>
-      <c r="N10" s="2" t="n">
+      <c r="N10" t="n">
         <v>28.72</v>
       </c>
-      <c r="O10" s="2" t="n">
+      <c r="O10" t="n">
         <v>0</v>
       </c>
-      <c r="P10" s="2" t="n">
+      <c r="P10" t="n">
         <v>592</v>
       </c>
-      <c r="Q10" s="2" t="n">
+      <c r="Q10" t="n">
         <v>2746</v>
       </c>
       <c r="R10" s="2" t="n">
@@ -3892,25 +3892,25 @@
       <c r="S10" s="2" t="n">
         <v>22.97</v>
       </c>
-      <c r="T10" s="2" t="n">
+      <c r="T10" t="n">
         <v>22.74</v>
       </c>
-      <c r="U10" s="2" t="n">
+      <c r="U10" t="n">
         <v>28.13</v>
       </c>
-      <c r="V10" s="2" t="n">
+      <c r="V10" t="n">
         <v>1</v>
       </c>
-      <c r="W10" s="2" t="n">
+      <c r="W10" t="n">
         <v>3</v>
       </c>
-      <c r="X10" s="2" t="n">
+      <c r="X10" s="3" t="n">
         <v>9.720000000000001</v>
       </c>
-      <c r="Y10" s="2" t="n">
+      <c r="Y10" s="3" t="n">
         <v>13.2</v>
       </c>
-      <c r="Z10" s="2" t="n">
+      <c r="Z10" t="n">
         <v>0</v>
       </c>
       <c r="AA10" t="inlineStr">
@@ -3918,7 +3918,7 @@
           <t>Consumer Discretionary</t>
         </is>
       </c>
-      <c r="AB10" s="2" t="n">
+      <c r="AB10" t="n">
         <v>50789</v>
       </c>
       <c r="AC10" s="2" t="n">
@@ -3944,46 +3944,46 @@
           <t>Mar 2024</t>
         </is>
       </c>
-      <c r="D11" s="2" t="n">
+      <c r="D11" t="n">
         <v>24.06</v>
       </c>
-      <c r="E11" s="2" t="n">
+      <c r="E11" t="n">
         <v>99.5</v>
       </c>
-      <c r="F11" s="2" t="n">
+      <c r="F11" s="3" t="n">
         <v>13.04</v>
       </c>
-      <c r="G11" s="2" t="n">
+      <c r="G11" s="3" t="n">
         <v>5.75</v>
       </c>
-      <c r="H11" s="2" t="n">
+      <c r="H11" s="3" t="n">
         <v>8.380000000000001</v>
       </c>
-      <c r="I11" s="2" t="n">
+      <c r="I11" s="3" t="n">
         <v>1.32</v>
       </c>
-      <c r="J11" s="2" t="n">
+      <c r="J11" t="n">
         <v>0.05</v>
       </c>
       <c r="K11" s="2" t="n">
         <v>7906</v>
       </c>
-      <c r="L11" s="2" t="n">
+      <c r="L11" t="n">
         <v>0.03</v>
       </c>
-      <c r="M11" s="2" t="n">
+      <c r="M11" t="n">
         <v>5</v>
       </c>
-      <c r="N11" s="2" t="n">
+      <c r="N11" t="n">
         <v>3.76</v>
       </c>
-      <c r="O11" s="2" t="n">
+      <c r="O11" t="n">
         <v>31</v>
       </c>
-      <c r="P11" s="2" t="n">
+      <c r="P11" t="n">
         <v>412039</v>
       </c>
-      <c r="Q11" s="2" t="n">
+      <c r="Q11" t="n">
         <v>7914</v>
       </c>
       <c r="R11" s="2" t="n">
@@ -3992,25 +3992,25 @@
       <c r="S11" s="2" t="n">
         <v>23.25</v>
       </c>
-      <c r="T11" s="2" t="n">
+      <c r="T11" t="n">
         <v>20.11</v>
       </c>
-      <c r="U11" s="2" t="n">
+      <c r="U11" t="n">
         <v>19.1</v>
       </c>
-      <c r="V11" s="2" t="n">
+      <c r="V11" t="n">
         <v>1</v>
       </c>
-      <c r="W11" s="2" t="n">
+      <c r="W11" t="n">
         <v>1</v>
       </c>
-      <c r="X11" s="2" t="n">
+      <c r="X11" s="3" t="n">
         <v>1084.11</v>
       </c>
-      <c r="Y11" s="2" t="n">
+      <c r="Y11" s="3" t="n">
         <v>1441.63</v>
       </c>
-      <c r="Z11" s="2" t="n">
+      <c r="Z11" t="n">
         <v>0.57</v>
       </c>
       <c r="AA11" t="inlineStr">
@@ -4018,7 +4018,7 @@
           <t>Financials</t>
         </is>
       </c>
-      <c r="AB11" s="2" t="n">
+      <c r="AB11" t="n">
         <v>26645</v>
       </c>
       <c r="AC11" s="2" t="n">
@@ -4044,46 +4044,46 @@
           <t>Mar 2024</t>
         </is>
       </c>
-      <c r="D12" s="2" t="n">
+      <c r="D12" t="n">
         <v>26.29</v>
       </c>
-      <c r="E12" s="2" t="n">
+      <c r="E12" t="n">
         <v>29.29</v>
       </c>
       <c r="F12" s="2" t="n">
         <v>18.84</v>
       </c>
-      <c r="G12" s="2" t="n">
+      <c r="G12" s="3" t="n">
         <v>4.35</v>
       </c>
-      <c r="H12" s="2" t="n">
+      <c r="H12" s="3" t="n">
         <v>3.82</v>
       </c>
       <c r="I12" s="2" t="n">
         <v>2689.17</v>
       </c>
-      <c r="J12" s="2" t="n">
+      <c r="J12" t="n">
         <v>0.15</v>
       </c>
       <c r="K12" s="3" t="n">
         <v>-79931</v>
       </c>
-      <c r="L12" s="2" t="n">
+      <c r="L12" t="n">
         <v>13.04</v>
       </c>
-      <c r="M12" s="2" t="n">
+      <c r="M12" t="n">
         <v>233</v>
       </c>
-      <c r="N12" s="2" t="n">
+      <c r="N12" t="n">
         <v>618.52</v>
       </c>
-      <c r="O12" s="2" t="n">
+      <c r="O12" t="n">
         <v>15</v>
       </c>
-      <c r="P12" s="2" t="n">
+      <c r="P12" t="n">
         <v>293346</v>
       </c>
-      <c r="Q12" s="3" t="n">
+      <c r="Q12" t="n">
         <v>-72760</v>
       </c>
       <c r="R12" s="2" t="n">
@@ -4092,25 +4092,25 @@
       <c r="S12" s="2" t="n">
         <v>29.32</v>
       </c>
-      <c r="T12" s="2" t="n">
+      <c r="T12" t="n">
         <v>27.56</v>
       </c>
-      <c r="U12" s="2" t="n">
+      <c r="U12" t="n">
         <v>27.26</v>
       </c>
-      <c r="V12" s="2" t="n">
+      <c r="V12" t="n">
         <v>0</v>
       </c>
-      <c r="W12" s="2" t="n">
+      <c r="W12" t="n">
         <v>3</v>
       </c>
-      <c r="X12" s="2" t="n">
+      <c r="X12" s="3" t="n">
         <v>7.74</v>
       </c>
-      <c r="Y12" s="2" t="n">
+      <c r="Y12" s="3" t="n">
         <v>2.91</v>
       </c>
-      <c r="Z12" s="2" t="n">
+      <c r="Z12" t="n">
         <v>0.83</v>
       </c>
       <c r="AA12" t="inlineStr">
@@ -4118,7 +4118,7 @@
           <t>Financials</t>
         </is>
       </c>
-      <c r="AB12" s="2" t="n">
+      <c r="AB12" t="n">
         <v>54972</v>
       </c>
       <c r="AC12" s="2" t="n">
@@ -4144,16 +4144,16 @@
           <t>Mar 2024</t>
         </is>
       </c>
-      <c r="D13" s="2" t="n">
+      <c r="D13" t="n">
         <v>7.99</v>
       </c>
-      <c r="E13" s="2" t="n">
+      <c r="E13" t="n">
         <v>15.02</v>
       </c>
-      <c r="F13" s="2" t="n">
+      <c r="F13" s="3" t="n">
         <v>7.57</v>
       </c>
-      <c r="G13" s="2" t="n">
+      <c r="G13" s="3" t="n">
         <v>11.69</v>
       </c>
       <c r="H13" s="2" t="n">
@@ -4162,28 +4162,28 @@
       <c r="I13" s="2" t="n">
         <v>25.32</v>
       </c>
-      <c r="J13" s="2" t="n">
+      <c r="J13" t="n">
         <v>0.55</v>
       </c>
       <c r="K13" s="2" t="n">
         <v>26</v>
       </c>
-      <c r="L13" s="2" t="n">
+      <c r="L13" t="n">
         <v>12.57</v>
       </c>
-      <c r="M13" s="2" t="n">
+      <c r="M13" t="n">
         <v>12</v>
       </c>
-      <c r="N13" s="2" t="n">
+      <c r="N13" t="n">
         <v>169.02</v>
       </c>
-      <c r="O13" s="2" t="n">
+      <c r="O13" t="n">
         <v>64</v>
       </c>
-      <c r="P13" s="2" t="n">
+      <c r="P13" t="n">
         <v>3477</v>
       </c>
-      <c r="Q13" s="2" t="n">
+      <c r="Q13" t="n">
         <v>1937</v>
       </c>
       <c r="R13" s="2" t="n">
@@ -4192,25 +4192,25 @@
       <c r="S13" s="2" t="n">
         <v>21.6</v>
       </c>
-      <c r="T13" s="2" t="n">
+      <c r="T13" t="n">
         <v>14.87</v>
       </c>
-      <c r="U13" s="2" t="n">
+      <c r="U13" t="n">
         <v>9.44</v>
       </c>
-      <c r="V13" s="2" t="n">
+      <c r="V13" t="n">
         <v>0</v>
       </c>
-      <c r="W13" s="2" t="n">
+      <c r="W13" t="n">
         <v>2</v>
       </c>
-      <c r="X13" s="2" t="n">
+      <c r="X13" s="3" t="n">
         <v>320.46</v>
       </c>
-      <c r="Y13" s="2" t="n">
+      <c r="Y13" s="3" t="n">
         <v>22.75</v>
       </c>
-      <c r="Z13" s="2" t="n">
+      <c r="Z13" t="n">
         <v>1.66</v>
       </c>
       <c r="AA13" t="inlineStr">
@@ -4218,7 +4218,7 @@
           <t>Consumer Staples</t>
         </is>
       </c>
-      <c r="AB13" s="2" t="n">
+      <c r="AB13" t="n">
         <v>15206</v>
       </c>
       <c r="AC13" s="2" t="n">
@@ -4244,46 +4244,46 @@
           <t>Mar 2024</t>
         </is>
       </c>
-      <c r="D14" s="2" t="n">
+      <c r="D14" t="n">
         <v>3.46</v>
       </c>
-      <c r="E14" s="2" t="n">
+      <c r="E14" t="n">
         <v>11.8</v>
       </c>
-      <c r="F14" s="2" t="n">
+      <c r="F14" s="3" t="n">
         <v>8.529999999999999</v>
       </c>
-      <c r="G14" s="2" t="n">
+      <c r="G14" s="3" t="n">
         <v>10.9</v>
       </c>
-      <c r="H14" s="2" t="n">
+      <c r="H14" s="3" t="n">
         <v>1.67</v>
       </c>
-      <c r="I14" s="2" t="n">
+      <c r="I14" s="3" t="n">
         <v>2.75</v>
       </c>
-      <c r="J14" s="2" t="n">
+      <c r="J14" t="n">
         <v>0.6</v>
       </c>
       <c r="K14" s="3" t="n">
         <v>-8455</v>
       </c>
-      <c r="L14" s="2" t="n">
+      <c r="L14" t="n">
         <v>19.46</v>
       </c>
-      <c r="M14" s="2" t="n">
+      <c r="M14" t="n">
         <v>28</v>
       </c>
-      <c r="N14" s="2" t="n">
+      <c r="N14" t="n">
         <v>342.77</v>
       </c>
-      <c r="O14" s="2" t="n">
+      <c r="O14" t="n">
         <v>5</v>
       </c>
-      <c r="P14" s="2" t="n">
+      <c r="P14" t="n">
         <v>65310</v>
       </c>
-      <c r="Q14" s="2" t="n">
+      <c r="Q14" t="n">
         <v>10312</v>
       </c>
       <c r="R14" s="2" t="n">
@@ -4292,25 +4292,25 @@
       <c r="S14" s="2" t="n">
         <v>45.81</v>
       </c>
-      <c r="T14" s="2" t="n">
+      <c r="T14" t="n">
         <v>31.95</v>
       </c>
-      <c r="U14" s="2" t="n">
+      <c r="U14" t="n">
         <v>34.6</v>
       </c>
-      <c r="V14" s="2" t="n">
+      <c r="V14" t="n">
         <v>0</v>
       </c>
-      <c r="W14" s="2" t="n">
+      <c r="W14" t="n">
         <v>0</v>
       </c>
-      <c r="X14" s="2" t="n">
+      <c r="X14" s="3" t="n">
         <v>310.23</v>
       </c>
-      <c r="Y14" s="2" t="n">
+      <c r="Y14" s="3" t="n">
         <v>25.34</v>
       </c>
-      <c r="Z14" s="2" t="n">
+      <c r="Z14" t="n">
         <v>0.06</v>
       </c>
       <c r="AA14" t="inlineStr">
@@ -4318,7 +4318,7 @@
           <t>Industrials</t>
         </is>
       </c>
-      <c r="AB14" s="2" t="n">
+      <c r="AB14" t="n">
         <v>96421</v>
       </c>
       <c r="AC14" s="2" t="n">
@@ -4344,46 +4344,46 @@
           <t>Mar 2024</t>
         </is>
       </c>
-      <c r="D15" s="2" t="n">
+      <c r="D15" t="n">
         <v>14.13</v>
       </c>
-      <c r="E15" s="2" t="n">
+      <c r="E15" t="n">
         <v>37.04</v>
       </c>
       <c r="F15" s="2" t="n">
         <v>25.85</v>
       </c>
-      <c r="G15" s="2" t="n">
+      <c r="G15" s="3" t="n">
         <v>11.71</v>
       </c>
-      <c r="H15" s="2" t="n">
+      <c r="H15" s="3" t="n">
         <v>4.79</v>
       </c>
-      <c r="I15" s="2" t="n">
+      <c r="I15" s="3" t="n">
         <v>2.2</v>
       </c>
-      <c r="J15" s="2" t="n">
+      <c r="J15" t="n">
         <v>0.21</v>
       </c>
       <c r="K15" s="3" t="n">
         <v>-79634</v>
       </c>
-      <c r="L15" s="2" t="n">
+      <c r="L15" t="n">
         <v>9.93</v>
       </c>
-      <c r="M15" s="2" t="n">
+      <c r="M15" t="n">
         <v>51</v>
       </c>
-      <c r="N15" s="2" t="n">
+      <c r="N15" t="n">
         <v>379.42</v>
       </c>
-      <c r="O15" s="2" t="n">
+      <c r="O15" t="n">
         <v>2</v>
       </c>
-      <c r="P15" s="2" t="n">
+      <c r="P15" t="n">
         <v>288933</v>
       </c>
-      <c r="Q15" s="3" t="n">
+      <c r="Q15" t="n">
         <v>-68674</v>
       </c>
       <c r="R15" s="2" t="n">
@@ -4392,25 +4392,25 @@
       <c r="S15" s="2" t="n">
         <v>23.75</v>
       </c>
-      <c r="T15" s="2" t="n">
+      <c r="T15" t="n">
         <v>20.59</v>
       </c>
-      <c r="U15" s="2" t="n">
+      <c r="U15" t="n">
         <v>22.13</v>
       </c>
-      <c r="V15" s="2" t="n">
+      <c r="V15" t="n">
         <v>0</v>
       </c>
-      <c r="W15" s="2" t="n">
+      <c r="W15" t="n">
         <v>2</v>
       </c>
-      <c r="X15" s="2" t="n">
+      <c r="X15" s="3" t="n">
         <v>107.87</v>
       </c>
-      <c r="Y15" s="2" t="n">
+      <c r="Y15" s="3" t="n">
         <v>14.5</v>
       </c>
-      <c r="Z15" s="2" t="n">
+      <c r="Z15" t="n">
         <v>0.04</v>
       </c>
       <c r="AA15" t="inlineStr">
@@ -4418,7 +4418,7 @@
           <t>Financials</t>
         </is>
       </c>
-      <c r="AB15" s="2" t="n">
+      <c r="AB15" t="n">
         <v>110382</v>
       </c>
       <c r="AC15" s="2" t="n">
@@ -4444,46 +4444,46 @@
           <t>Mar 2024</t>
         </is>
       </c>
-      <c r="D16" s="2" t="n">
+      <c r="D16" t="n">
         <v>15.94</v>
       </c>
-      <c r="E16" s="2" t="n">
+      <c r="E16" t="n">
         <v>37.49</v>
       </c>
       <c r="F16" s="2" t="n">
         <v>15.76</v>
       </c>
-      <c r="G16" s="2" t="n">
+      <c r="G16" s="3" t="n">
         <v>2.82</v>
       </c>
-      <c r="H16" s="2" t="n">
+      <c r="H16" s="3" t="n">
         <v>12.14</v>
       </c>
-      <c r="I16" s="2" t="n">
+      <c r="I16" s="3" t="n">
         <v>1.9</v>
       </c>
-      <c r="J16" s="2" t="n">
+      <c r="J16" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="K16" s="3" t="n">
         <v>-7559</v>
       </c>
-      <c r="L16" s="2" t="n">
+      <c r="L16" t="n">
         <v>1.09</v>
       </c>
-      <c r="M16" s="2" t="n">
+      <c r="M16" t="n">
         <v>36</v>
       </c>
-      <c r="N16" s="2" t="n">
+      <c r="N16" t="n">
         <v>115.55</v>
       </c>
-      <c r="O16" s="2" t="n">
+      <c r="O16" t="n">
         <v>21</v>
       </c>
-      <c r="P16" s="2" t="n">
+      <c r="P16" t="n">
         <v>1453761</v>
       </c>
-      <c r="Q16" s="3" t="n">
+      <c r="Q16" t="n">
         <v>-6274</v>
       </c>
       <c r="R16" s="2" t="n">
@@ -4492,25 +4492,25 @@
       <c r="S16" s="2" t="n">
         <v>74.51000000000001</v>
       </c>
-      <c r="T16" s="2" t="n">
+      <c r="T16" t="n">
         <v>55.18</v>
       </c>
-      <c r="U16" s="2" t="n">
+      <c r="U16" t="n">
         <v>16.79</v>
       </c>
-      <c r="V16" s="2" t="n">
+      <c r="V16" t="n">
         <v>0</v>
       </c>
-      <c r="W16" s="2" t="n">
+      <c r="W16" t="n">
         <v>2</v>
       </c>
-      <c r="X16" s="2" t="n">
+      <c r="X16" s="3" t="n">
         <v>47.26</v>
       </c>
-      <c r="Y16" s="2" t="n">
+      <c r="Y16" s="3" t="n">
         <v>14.72</v>
       </c>
-      <c r="Z16" s="2" t="n">
+      <c r="Z16" t="n">
         <v>1.23</v>
       </c>
       <c r="AA16" t="inlineStr">
@@ -4518,7 +4518,7 @@
           <t>Financials</t>
         </is>
       </c>
-      <c r="AB16" s="2" t="n">
+      <c r="AB16" t="n">
         <v>118379</v>
       </c>
       <c r="AC16" s="2" t="n">
@@ -4544,46 +4544,46 @@
           <t>Mar 2024</t>
         </is>
       </c>
-      <c r="D17" s="2" t="n">
+      <c r="D17" t="n">
         <v>20.33</v>
       </c>
-      <c r="E17" s="2" t="n">
+      <c r="E17" t="n">
         <v>28.92</v>
       </c>
       <c r="F17" s="2" t="n">
         <v>15.12</v>
       </c>
-      <c r="G17" s="2" t="n">
+      <c r="G17" s="3" t="n">
         <v>4.3</v>
       </c>
-      <c r="H17" s="2" t="n">
+      <c r="H17" s="3" t="n">
         <v>3.99</v>
       </c>
-      <c r="I17" s="2" t="n">
+      <c r="I17" s="3" t="n">
         <v>0.68</v>
       </c>
-      <c r="J17" s="2" t="n">
+      <c r="J17" t="n">
         <v>0.15</v>
       </c>
       <c r="K17" s="3" t="n">
         <v>-31359</v>
       </c>
-      <c r="L17" s="2" t="n">
+      <c r="L17" t="n">
         <v>0.71</v>
       </c>
-      <c r="M17" s="2" t="n">
+      <c r="M17" t="n">
         <v>39</v>
       </c>
-      <c r="N17" s="2" t="n">
+      <c r="N17" t="n">
         <v>130.18</v>
       </c>
-      <c r="O17" s="2" t="n">
+      <c r="O17" t="n">
         <v>23</v>
       </c>
-      <c r="P17" s="2" t="n">
+      <c r="P17" t="n">
         <v>195496</v>
       </c>
-      <c r="Q17" s="3" t="n">
+      <c r="Q17" t="n">
         <v>-31101</v>
       </c>
       <c r="R17" s="2" t="n">
@@ -4592,25 +4592,25 @@
       <c r="S17" s="2" t="n">
         <v>23.49</v>
       </c>
-      <c r="T17" s="2" t="n">
+      <c r="T17" t="n">
         <v>14.29</v>
       </c>
-      <c r="U17" s="2" t="n">
+      <c r="U17" t="n">
         <v>27.83</v>
       </c>
-      <c r="V17" s="2" t="n">
+      <c r="V17" t="n">
         <v>0</v>
       </c>
-      <c r="W17" s="2" t="n">
+      <c r="W17" t="n">
         <v>2</v>
       </c>
-      <c r="X17" s="2" t="n">
+      <c r="X17" s="3" t="n">
         <v>35.87</v>
       </c>
-      <c r="Y17" s="2" t="n">
+      <c r="Y17" s="3" t="n">
         <v>10.75</v>
       </c>
-      <c r="Z17" s="2" t="n">
+      <c r="Z17" t="n">
         <v>1.64</v>
       </c>
       <c r="AA17" t="inlineStr">
@@ -4618,7 +4618,7 @@
           <t>Financials</t>
         </is>
       </c>
-      <c r="AB17" s="2" t="n">
+      <c r="AB17" t="n">
         <v>36388</v>
       </c>
       <c r="AC17" s="2" t="n">
@@ -4644,46 +4644,46 @@
           <t>Mar 2024</t>
         </is>
       </c>
-      <c r="D18" s="2" t="n">
+      <c r="D18" t="n">
         <v>17.85</v>
       </c>
-      <c r="E18" s="2" t="n">
+      <c r="E18" t="n">
         <v>28.1</v>
       </c>
       <c r="F18" s="2" t="n">
         <v>17.46</v>
       </c>
-      <c r="G18" s="2" t="n">
+      <c r="G18" s="3" t="n">
         <v>3.5</v>
       </c>
-      <c r="H18" s="2" t="n">
+      <c r="H18" s="3" t="n">
         <v>6.86</v>
       </c>
       <c r="I18" s="2" t="n">
         <v>21.21</v>
       </c>
-      <c r="J18" s="2" t="n">
+      <c r="J18" t="n">
         <v>0.12</v>
       </c>
       <c r="K18" s="3" t="n">
         <v>-38538</v>
       </c>
-      <c r="L18" s="2" t="n">
+      <c r="L18" t="n">
         <v>14.9</v>
       </c>
-      <c r="M18" s="2" t="n">
+      <c r="M18" t="n">
         <v>41</v>
       </c>
-      <c r="N18" s="2" t="n">
+      <c r="N18" t="n">
         <v>116.62</v>
       </c>
-      <c r="O18" s="2" t="n">
+      <c r="O18" t="n">
         <v>5</v>
       </c>
-      <c r="P18" s="2" t="n">
+      <c r="P18" t="n">
         <v>134475</v>
       </c>
-      <c r="Q18" s="3" t="n">
+      <c r="Q18" t="n">
         <v>-35683</v>
       </c>
       <c r="R18" s="2" t="n">
@@ -4692,25 +4692,25 @@
       <c r="S18" s="2" t="n">
         <v>23.36</v>
       </c>
-      <c r="T18" s="2" t="n">
+      <c r="T18" t="n">
         <v>22.28</v>
       </c>
-      <c r="U18" s="2" t="n">
+      <c r="U18" t="n">
         <v>25.99</v>
       </c>
-      <c r="V18" s="2" t="n">
+      <c r="V18" t="n">
         <v>0</v>
       </c>
-      <c r="W18" s="2" t="n">
+      <c r="W18" t="n">
         <v>3</v>
       </c>
-      <c r="X18" s="2" t="n">
+      <c r="X18" s="3" t="n">
         <v>47.79</v>
       </c>
-      <c r="Y18" s="2" t="n">
+      <c r="Y18" s="3" t="n">
         <v>16.8</v>
       </c>
-      <c r="Z18" s="2" t="n">
+      <c r="Z18" t="n">
         <v>0.26</v>
       </c>
       <c r="AA18" t="inlineStr">
@@ -4718,13 +4718,13 @@
           <t>Financials</t>
         </is>
       </c>
-      <c r="AB18" s="2" t="n">
+      <c r="AB18" t="n">
         <v>19163</v>
       </c>
       <c r="AC18" s="2" t="n">
         <v>25.92</v>
       </c>
-      <c r="AD18" s="2" t="n">
+      <c r="AD18" s="3" t="n">
         <v>11.74</v>
       </c>
     </row>
@@ -4744,46 +4744,46 @@
           <t>Mar 2024</t>
         </is>
       </c>
-      <c r="D19" s="2" t="n">
+      <c r="D19" t="n">
         <v>19.56</v>
       </c>
-      <c r="E19" s="2" t="n">
+      <c r="E19" t="n">
         <v>38.55</v>
       </c>
-      <c r="F19" s="2" t="n">
+      <c r="F19" s="3" t="n">
         <v>14.25</v>
       </c>
-      <c r="G19" s="2" t="n">
+      <c r="G19" s="3" t="n">
         <v>3.56</v>
       </c>
-      <c r="H19" s="2" t="n">
+      <c r="H19" s="3" t="n">
         <v>6.89</v>
       </c>
-      <c r="I19" s="2" t="n">
+      <c r="I19" s="3" t="n">
         <v>1.88</v>
       </c>
-      <c r="J19" s="2" t="n">
+      <c r="J19" t="n">
         <v>0.09</v>
       </c>
       <c r="K19" s="3" t="n">
         <v>-17468</v>
       </c>
-      <c r="L19" s="2" t="n">
+      <c r="L19" t="n">
         <v>1.37</v>
       </c>
-      <c r="M19" s="2" t="n">
+      <c r="M19" t="n">
         <v>115</v>
       </c>
-      <c r="N19" s="2" t="n">
+      <c r="N19" t="n">
         <v>80.72</v>
       </c>
-      <c r="O19" s="2" t="n">
+      <c r="O19" t="n">
         <v>14</v>
       </c>
-      <c r="P19" s="2" t="n">
+      <c r="P19" t="n">
         <v>432404</v>
       </c>
-      <c r="Q19" s="3" t="n">
+      <c r="Q19" t="n">
         <v>-16843</v>
       </c>
       <c r="R19" s="2" t="n">
@@ -4792,25 +4792,25 @@
       <c r="S19" s="2" t="n">
         <v>22.08</v>
       </c>
-      <c r="T19" s="2" t="n">
+      <c r="T19" t="n">
         <v>15.9</v>
       </c>
-      <c r="U19" s="2" t="n">
+      <c r="U19" t="n">
         <v>16.41</v>
       </c>
-      <c r="V19" s="2" t="n">
+      <c r="V19" t="n">
         <v>0</v>
       </c>
-      <c r="W19" s="2" t="n">
+      <c r="W19" t="n">
         <v>1</v>
       </c>
-      <c r="X19" s="2" t="n">
+      <c r="X19" s="3" t="n">
         <v>63.46</v>
       </c>
-      <c r="Y19" s="2" t="n">
+      <c r="Y19" s="3" t="n">
         <v>90.41</v>
       </c>
-      <c r="Z19" s="2" t="n">
+      <c r="Z19" t="n">
         <v>0.19</v>
       </c>
       <c r="AA19" t="inlineStr">
@@ -4818,13 +4818,13 @@
           <t>Financials</t>
         </is>
       </c>
-      <c r="AB19" s="2" t="n">
+      <c r="AB19" t="n">
         <v>45748</v>
       </c>
       <c r="AC19" s="2" t="n">
         <v>20.83</v>
       </c>
-      <c r="AD19" s="2" t="n">
+      <c r="AD19" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5042,10 +5042,10 @@
           <t>Mar 2024</t>
         </is>
       </c>
-      <c r="D2" s="2" t="n">
+      <c r="D2" t="n">
         <v>24.2</v>
       </c>
-      <c r="E2" s="2" t="n">
+      <c r="E2" t="n">
         <v>26.18</v>
       </c>
       <c r="F2" s="2" t="n">
@@ -5060,55 +5060,55 @@
       <c r="I2" s="2" t="n">
         <v>114.71</v>
       </c>
-      <c r="J2" s="2" t="n">
+      <c r="J2" t="n">
         <v>0.72</v>
       </c>
       <c r="K2" s="2" t="n">
         <v>890</v>
       </c>
-      <c r="L2" s="2" t="n">
+      <c r="L2" t="n">
         <v>17.14</v>
       </c>
-      <c r="M2" s="2" t="n">
+      <c r="M2" t="n">
         <v>146</v>
       </c>
-      <c r="N2" s="2" t="n">
+      <c r="N2" t="n">
         <v>668.33</v>
       </c>
-      <c r="O2" s="2" t="n">
+      <c r="O2" t="n">
         <v>35</v>
       </c>
-      <c r="P2" s="2" t="n">
+      <c r="P2" t="n">
         <v>419</v>
       </c>
-      <c r="Q2" s="2" t="n">
+      <c r="Q2" t="n">
         <v>3724</v>
       </c>
-      <c r="R2" s="2" t="n">
+      <c r="R2" s="3" t="n">
         <v>11.04</v>
       </c>
-      <c r="S2" s="2" t="n">
+      <c r="S2" s="3" t="n">
         <v>12.68</v>
       </c>
-      <c r="T2" s="2" t="n">
+      <c r="T2" t="n">
         <v>12.51</v>
       </c>
-      <c r="U2" s="2" t="n">
+      <c r="U2" t="n">
         <v>23.78</v>
       </c>
-      <c r="V2" s="2" t="n">
+      <c r="V2" t="n">
         <v>0</v>
       </c>
-      <c r="W2" s="2" t="n">
+      <c r="W2" t="n">
         <v>4</v>
       </c>
-      <c r="X2" s="2" t="n">
+      <c r="X2" s="3" t="n">
         <v>11.22</v>
       </c>
-      <c r="Y2" s="2" t="n">
+      <c r="Y2" s="3" t="n">
         <v>2.45</v>
       </c>
-      <c r="Z2" s="2" t="n">
+      <c r="Z2" t="n">
         <v>2.14</v>
       </c>
       <c r="AA2" t="inlineStr">
@@ -5116,7 +5116,7 @@
           <t>Consumer Discretionary</t>
         </is>
       </c>
-      <c r="AB2" s="2" t="n">
+      <c r="AB2" t="n">
         <v>16536</v>
       </c>
       <c r="AC2" s="2" t="n">
@@ -5142,10 +5142,10 @@
           <t>Mar 2024</t>
         </is>
       </c>
-      <c r="D3" s="2" t="n">
+      <c r="D3" t="n">
         <v>16.61</v>
       </c>
-      <c r="E3" s="2" t="n">
+      <c r="E3" t="n">
         <v>76.31999999999999</v>
       </c>
       <c r="F3" s="2" t="n">
@@ -5160,55 +5160,55 @@
       <c r="I3" s="2" t="n">
         <v>57.85</v>
       </c>
-      <c r="J3" s="2" t="n">
+      <c r="J3" t="n">
         <v>0.79</v>
       </c>
       <c r="K3" s="2" t="n">
         <v>10145</v>
       </c>
-      <c r="L3" s="2" t="n">
+      <c r="L3" t="n">
         <v>8.6</v>
       </c>
-      <c r="M3" s="2" t="n">
+      <c r="M3" t="n">
         <v>44</v>
       </c>
-      <c r="N3" s="2" t="n">
+      <c r="N3" t="n">
         <v>217.95</v>
       </c>
-      <c r="O3" s="2" t="n">
+      <c r="O3" t="n">
         <v>96</v>
       </c>
-      <c r="P3" s="2" t="n">
+      <c r="P3" t="n">
         <v>1484</v>
       </c>
-      <c r="Q3" s="2" t="n">
+      <c r="Q3" t="n">
         <v>15469</v>
       </c>
-      <c r="R3" s="2" t="n">
+      <c r="R3" s="3" t="n">
         <v>9.5</v>
       </c>
-      <c r="S3" s="2" t="n">
+      <c r="S3" s="3" t="n">
         <v>11.15</v>
       </c>
-      <c r="T3" s="2" t="n">
+      <c r="T3" t="n">
         <v>9.460000000000001</v>
       </c>
-      <c r="U3" s="2" t="n">
+      <c r="U3" t="n">
         <v>9.59</v>
       </c>
-      <c r="V3" s="2" t="n">
+      <c r="V3" t="n">
         <v>0</v>
       </c>
-      <c r="W3" s="2" t="n">
+      <c r="W3" t="n">
         <v>4</v>
       </c>
-      <c r="X3" s="2" t="n">
+      <c r="X3" s="3" t="n">
         <v>6.94</v>
       </c>
-      <c r="Y3" s="2" t="n">
+      <c r="Y3" s="3" t="n">
         <v>1.4</v>
       </c>
-      <c r="Z3" s="2" t="n">
+      <c r="Z3" t="n">
         <v>31.42</v>
       </c>
       <c r="AA3" t="inlineStr">
@@ -5216,7 +5216,7 @@
           <t>Consumer Staples</t>
         </is>
       </c>
-      <c r="AB3" s="2" t="n">
+      <c r="AB3" t="n">
         <v>61896</v>
       </c>
       <c r="AC3" s="2" t="n">
@@ -5242,10 +5242,10 @@
           <t>Mar 2024</t>
         </is>
       </c>
-      <c r="D4" s="2" t="n">
+      <c r="D4" t="n">
         <v>9.9</v>
       </c>
-      <c r="E4" s="2" t="n">
+      <c r="E4" t="n">
         <v>86.15000000000001</v>
       </c>
       <c r="F4" s="2" t="n">
@@ -5260,55 +5260,55 @@
       <c r="I4" s="2" t="n">
         <v>47.27</v>
       </c>
-      <c r="J4" s="2" t="n">
+      <c r="J4" t="n">
         <v>1.44</v>
       </c>
       <c r="K4" s="2" t="n">
         <v>3095</v>
       </c>
-      <c r="L4" s="2" t="n">
+      <c r="L4" t="n">
         <v>4.84</v>
       </c>
-      <c r="M4" s="2" t="n">
+      <c r="M4" t="n">
         <v>187</v>
       </c>
-      <c r="N4" s="2" t="n">
+      <c r="N4" t="n">
         <v>442.48</v>
       </c>
-      <c r="O4" s="2" t="n">
+      <c r="O4" t="n">
         <v>75</v>
       </c>
-      <c r="P4" s="2" t="n">
+      <c r="P4" t="n">
         <v>606</v>
       </c>
-      <c r="Q4" s="2" t="n">
+      <c r="Q4" t="n">
         <v>4923</v>
       </c>
-      <c r="R4" s="2" t="n">
+      <c r="R4" s="3" t="n">
         <v>2.15</v>
       </c>
-      <c r="S4" s="2" t="n">
+      <c r="S4" s="3" t="n">
         <v>1.54</v>
       </c>
-      <c r="T4" s="2" t="n">
+      <c r="T4" t="n">
         <v>1.69</v>
       </c>
-      <c r="U4" s="2" t="n">
+      <c r="U4" t="n">
         <v>6.87</v>
       </c>
-      <c r="V4" s="2" t="n">
+      <c r="V4" t="n">
         <v>0</v>
       </c>
-      <c r="W4" s="2" t="n">
+      <c r="W4" t="n">
         <v>4</v>
       </c>
-      <c r="X4" s="2" t="n">
+      <c r="X4" s="3" t="n">
         <v>6.43</v>
       </c>
-      <c r="Y4" s="2" t="n">
+      <c r="Y4" s="3" t="n">
         <v>2.72</v>
       </c>
-      <c r="Z4" s="2" t="n">
+      <c r="Z4" t="n">
         <v>6.24</v>
       </c>
       <c r="AA4" t="inlineStr">
@@ -5316,7 +5316,7 @@
           <t>Consumer Discretionary</t>
         </is>
       </c>
-      <c r="AB4" s="2" t="n">
+      <c r="AB4" t="n">
         <v>37789</v>
       </c>
       <c r="AC4" s="2" t="n">
@@ -5342,10 +5342,10 @@
           <t>Mar 2024</t>
         </is>
       </c>
-      <c r="D5" s="2" t="n">
+      <c r="D5" t="n">
         <v>12.73</v>
       </c>
-      <c r="E5" s="2" t="n">
+      <c r="E5" t="n">
         <v>18.89</v>
       </c>
       <c r="F5" s="2" t="n">
@@ -5360,55 +5360,55 @@
       <c r="I5" s="2" t="n">
         <v>20.6</v>
       </c>
-      <c r="J5" s="2" t="n">
+      <c r="J5" t="n">
         <v>1.85</v>
       </c>
       <c r="K5" s="2" t="n">
         <v>3050</v>
       </c>
-      <c r="L5" s="2" t="n">
+      <c r="L5" t="n">
         <v>2.84</v>
       </c>
-      <c r="M5" s="2" t="n">
+      <c r="M5" t="n">
         <v>89</v>
       </c>
-      <c r="N5" s="2" t="n">
+      <c r="N5" t="n">
         <v>164.21</v>
       </c>
-      <c r="O5" s="2" t="n">
+      <c r="O5" t="n">
         <v>83</v>
       </c>
-      <c r="P5" s="2" t="n">
+      <c r="P5" t="n">
         <v>2065</v>
       </c>
-      <c r="Q5" s="2" t="n">
+      <c r="Q5" t="n">
         <v>2573</v>
       </c>
-      <c r="R5" s="2" t="n">
+      <c r="R5" s="3" t="n">
         <v>8.69</v>
       </c>
-      <c r="S5" s="2" t="n">
+      <c r="S5" s="3" t="n">
         <v>13.06</v>
       </c>
-      <c r="T5" s="2" t="n">
+      <c r="T5" t="n">
         <v>13.14</v>
       </c>
-      <c r="U5" s="2" t="n">
+      <c r="U5" t="n">
         <v>8.48</v>
       </c>
-      <c r="V5" s="2" t="n">
+      <c r="V5" t="n">
         <v>1</v>
       </c>
-      <c r="W5" s="2" t="n">
+      <c r="W5" t="n">
         <v>5</v>
       </c>
-      <c r="X5" s="2" t="n">
+      <c r="X5" s="3" t="n">
         <v>3.97</v>
       </c>
-      <c r="Y5" s="2" t="n">
+      <c r="Y5" s="3" t="n">
         <v>2.15</v>
       </c>
-      <c r="Z5" s="2" t="n">
+      <c r="Z5" t="n">
         <v>23.48</v>
       </c>
       <c r="AA5" t="inlineStr">
@@ -5416,7 +5416,7 @@
           <t>Consumer Staples</t>
         </is>
       </c>
-      <c r="AB5" s="2" t="n">
+      <c r="AB5" t="n">
         <v>16769</v>
       </c>
       <c r="AC5" s="2" t="n">
@@ -5640,10 +5640,10 @@
           <t>Mar 2024</t>
         </is>
       </c>
-      <c r="D2" s="2" t="n">
+      <c r="D2" t="n">
         <v>41.37</v>
       </c>
-      <c r="E2" s="2" t="n">
+      <c r="E2" t="n">
         <v>36.2</v>
       </c>
       <c r="F2" s="2" t="n">
@@ -5655,31 +5655,31 @@
       <c r="H2" s="2" t="n">
         <v>0.8</v>
       </c>
-      <c r="I2" s="2" t="n">
+      <c r="I2" s="3" t="n">
         <v>8.300000000000001</v>
       </c>
-      <c r="J2" s="2" t="n">
+      <c r="J2" t="n">
         <v>0.55</v>
       </c>
       <c r="K2" s="2" t="n">
         <v>17651</v>
       </c>
-      <c r="L2" s="2" t="n">
+      <c r="L2" t="n">
         <v>6.91</v>
       </c>
-      <c r="M2" s="2" t="n">
+      <c r="M2" t="n">
         <v>54</v>
       </c>
-      <c r="N2" s="2" t="n">
+      <c r="N2" t="n">
         <v>11.19</v>
       </c>
-      <c r="O2" s="2" t="n">
+      <c r="O2" t="n">
         <v>0</v>
       </c>
-      <c r="P2" s="2" t="n">
+      <c r="P2" t="n">
         <v>34616</v>
       </c>
-      <c r="Q2" s="2" t="n">
+      <c r="Q2" t="n">
         <v>14170</v>
       </c>
       <c r="R2" s="2" t="n">
@@ -5688,25 +5688,25 @@
       <c r="S2" s="3" t="n">
         <v/>
       </c>
-      <c r="T2" s="3" t="n">
+      <c r="T2" t="n">
         <v/>
       </c>
-      <c r="U2" s="2" t="n">
+      <c r="U2" t="n">
         <v>24.29</v>
       </c>
-      <c r="V2" s="2" t="n">
+      <c r="V2" t="n">
         <v>1</v>
       </c>
-      <c r="W2" s="2" t="n">
+      <c r="W2" t="n">
         <v>4</v>
       </c>
-      <c r="X2" s="2" t="n">
+      <c r="X2" s="3" t="n">
         <v>46.05</v>
       </c>
-      <c r="Y2" s="2" t="n">
+      <c r="Y2" s="3" t="n">
         <v>222.2</v>
       </c>
-      <c r="Z2" s="2" t="n">
+      <c r="Z2" t="n">
         <v>0</v>
       </c>
       <c r="AA2" t="inlineStr">
@@ -5714,7 +5714,7 @@
           <t>Energy</t>
         </is>
       </c>
-      <c r="AB2" s="2" t="n">
+      <c r="AB2" t="n">
         <v>50351</v>
       </c>
       <c r="AC2" s="2" t="n">
@@ -5740,10 +5740,10 @@
           <t>Mar 2024</t>
         </is>
       </c>
-      <c r="D3" s="2" t="n">
+      <c r="D3" t="n">
         <v>29.28</v>
       </c>
-      <c r="E3" s="2" t="n">
+      <c r="E3" t="n">
         <v>37.02</v>
       </c>
       <c r="F3" s="2" t="n">
@@ -5758,55 +5758,55 @@
       <c r="I3" s="2" t="n">
         <v>362.96</v>
       </c>
-      <c r="J3" s="2" t="n">
+      <c r="J3" t="n">
         <v>0.77</v>
       </c>
       <c r="K3" s="2" t="n">
         <v>18742</v>
       </c>
-      <c r="L3" s="2" t="n">
+      <c r="L3" t="n">
         <v>2.21</v>
       </c>
-      <c r="M3" s="2" t="n">
+      <c r="M3" t="n">
         <v>16</v>
       </c>
-      <c r="N3" s="2" t="n">
+      <c r="N3" t="n">
         <v>59.7</v>
       </c>
-      <c r="O3" s="2" t="n">
+      <c r="O3" t="n">
         <v>84</v>
       </c>
-      <c r="P3" s="2" t="n">
+      <c r="P3" t="n">
         <v>303</v>
       </c>
-      <c r="Q3" s="2" t="n">
+      <c r="Q3" t="n">
         <v>17179</v>
       </c>
-      <c r="R3" s="2" t="n">
+      <c r="R3" s="3" t="n">
         <v>7.95</v>
       </c>
-      <c r="S3" s="2" t="n">
+      <c r="S3" s="3" t="n">
         <v>10.08</v>
       </c>
-      <c r="T3" s="2" t="n">
+      <c r="T3" t="n">
         <v>9.859999999999999</v>
       </c>
-      <c r="U3" s="2" t="n">
+      <c r="U3" t="n">
         <v>12.89</v>
       </c>
-      <c r="V3" s="2" t="n">
+      <c r="V3" t="n">
         <v>1</v>
       </c>
-      <c r="W3" s="2" t="n">
+      <c r="W3" t="n">
         <v>4</v>
       </c>
-      <c r="X3" s="2" t="n">
+      <c r="X3" s="3" t="n">
         <v>840.78</v>
       </c>
-      <c r="Y3" s="2" t="n">
+      <c r="Y3" s="3" t="n">
         <v>225.33</v>
       </c>
-      <c r="Z3" s="2" t="n">
+      <c r="Z3" t="n">
         <v>0.62</v>
       </c>
       <c r="AA3" t="inlineStr">
@@ -5814,7 +5814,7 @@
           <t>Consumer Staples</t>
         </is>
       </c>
-      <c r="AB3" s="2" t="n">
+      <c r="AB3" t="n">
         <v>70866</v>
       </c>
       <c r="AC3" s="2" t="n">
@@ -5840,10 +5840,10 @@
           <t>Mar 2024</t>
         </is>
       </c>
-      <c r="D4" s="2" t="n">
+      <c r="D4" t="n">
         <v>26.02</v>
       </c>
-      <c r="E4" s="2" t="n">
+      <c r="E4" t="n">
         <v>34.33</v>
       </c>
       <c r="F4" s="2" t="n">
@@ -5858,28 +5858,28 @@
       <c r="I4" s="2" t="n">
         <v>82.73999999999999</v>
       </c>
-      <c r="J4" s="2" t="n">
+      <c r="J4" t="n">
         <v>0.7</v>
       </c>
       <c r="K4" s="2" t="n">
         <v>667</v>
       </c>
-      <c r="L4" s="2" t="n">
+      <c r="L4" t="n">
         <v>5.04</v>
       </c>
-      <c r="M4" s="2" t="n">
+      <c r="M4" t="n">
         <v>14</v>
       </c>
-      <c r="N4" s="2" t="n">
+      <c r="N4" t="n">
         <v>20.19</v>
       </c>
-      <c r="O4" s="2" t="n">
+      <c r="O4" t="n">
         <v>47</v>
       </c>
-      <c r="P4" s="2" t="n">
+      <c r="P4" t="n">
         <v>60</v>
       </c>
-      <c r="Q4" s="2" t="n">
+      <c r="Q4" t="n">
         <v>882</v>
       </c>
       <c r="R4" s="2" t="n">
@@ -5888,25 +5888,25 @@
       <c r="S4" s="2" t="n">
         <v>29.17</v>
       </c>
-      <c r="T4" s="2" t="n">
+      <c r="T4" t="n">
         <v>28.47</v>
       </c>
-      <c r="U4" s="2" t="n">
+      <c r="U4" t="n">
         <v>76.47</v>
       </c>
-      <c r="V4" s="2" t="n">
+      <c r="V4" t="n">
         <v>1</v>
       </c>
-      <c r="W4" s="2" t="n">
+      <c r="W4" t="n">
         <v>4</v>
       </c>
-      <c r="X4" s="2" t="n">
+      <c r="X4" s="3" t="n">
         <v>799.9299999999999</v>
       </c>
-      <c r="Y4" s="2" t="n">
+      <c r="Y4" s="3" t="n">
         <v>554.6799999999999</v>
       </c>
-      <c r="Z4" s="2" t="n">
+      <c r="Z4" t="n">
         <v>0.42</v>
       </c>
       <c r="AA4" t="inlineStr">
@@ -5914,7 +5914,7 @@
           <t>Consumer Discretionary</t>
         </is>
       </c>
-      <c r="AB4" s="2" t="n">
+      <c r="AB4" t="n">
         <v>4270</v>
       </c>
       <c r="AC4" s="2" t="n">
@@ -5940,10 +5940,10 @@
           <t>Mar 2024</t>
         </is>
       </c>
-      <c r="D5" s="2" t="n">
+      <c r="D5" t="n">
         <v>5.99</v>
       </c>
-      <c r="E5" s="2" t="n">
+      <c r="E5" t="n">
         <v>9.84</v>
       </c>
       <c r="F5" s="2" t="n">
@@ -5955,58 +5955,58 @@
       <c r="H5" s="2" t="n">
         <v>0.72</v>
       </c>
-      <c r="I5" s="2" t="n">
+      <c r="I5" s="3" t="n">
         <v>11.36</v>
       </c>
-      <c r="J5" s="2" t="n">
+      <c r="J5" t="n">
         <v>2.21</v>
       </c>
       <c r="K5" s="2" t="n">
         <v>25415</v>
       </c>
-      <c r="L5" s="2" t="n">
+      <c r="L5" t="n">
         <v>2.35</v>
       </c>
-      <c r="M5" s="2" t="n">
+      <c r="M5" t="n">
         <v>62</v>
       </c>
-      <c r="N5" s="2" t="n">
+      <c r="N5" t="n">
         <v>35.41</v>
       </c>
-      <c r="O5" s="2" t="n">
+      <c r="O5" t="n">
         <v>33</v>
       </c>
-      <c r="P5" s="2" t="n">
+      <c r="P5" t="n">
         <v>54599</v>
       </c>
-      <c r="Q5" s="2" t="n">
+      <c r="Q5" t="n">
         <v>35936</v>
       </c>
-      <c r="R5" s="2" t="n">
+      <c r="R5" s="3" t="n">
         <v>8.48</v>
       </c>
       <c r="S5" s="2" t="n">
         <v>25.79</v>
       </c>
-      <c r="T5" s="2" t="n">
+      <c r="T5" t="n">
         <v>28.06</v>
       </c>
-      <c r="U5" s="2" t="n">
+      <c r="U5" t="n">
         <v>24.86</v>
       </c>
-      <c r="V5" s="2" t="n">
+      <c r="V5" t="n">
         <v>1</v>
       </c>
-      <c r="W5" s="2" t="n">
+      <c r="W5" t="n">
         <v>4</v>
       </c>
-      <c r="X5" s="2" t="n">
+      <c r="X5" s="3" t="n">
         <v>79.56999999999999</v>
       </c>
-      <c r="Y5" s="2" t="n">
+      <c r="Y5" s="3" t="n">
         <v>139.33</v>
       </c>
-      <c r="Z5" s="2" t="n">
+      <c r="Z5" t="n">
         <v>0.67</v>
       </c>
       <c r="AA5" t="inlineStr">
@@ -6014,7 +6014,7 @@
           <t>Energy</t>
         </is>
       </c>
-      <c r="AB5" s="2" t="n">
+      <c r="AB5" t="n">
         <v>448083</v>
       </c>
       <c r="AC5" s="2" t="n">
@@ -6040,10 +6040,10 @@
           <t>Mar 2024</t>
         </is>
       </c>
-      <c r="D6" s="2" t="n">
+      <c r="D6" t="n">
         <v>11.94</v>
       </c>
-      <c r="E6" s="2" t="n">
+      <c r="E6" t="n">
         <v>15.93</v>
       </c>
       <c r="F6" s="2" t="n">
@@ -6055,31 +6055,31 @@
       <c r="H6" s="2" t="n">
         <v>0.43</v>
       </c>
-      <c r="I6" s="2" t="n">
+      <c r="I6" s="3" t="n">
         <v>8.039999999999999</v>
       </c>
-      <c r="J6" s="2" t="n">
+      <c r="J6" t="n">
         <v>1.73</v>
       </c>
       <c r="K6" s="2" t="n">
         <v>841</v>
       </c>
-      <c r="L6" s="2" t="n">
+      <c r="L6" t="n">
         <v>4.11</v>
       </c>
-      <c r="M6" s="2" t="n">
+      <c r="M6" t="n">
         <v>42</v>
       </c>
-      <c r="N6" s="2" t="n">
+      <c r="N6" t="n">
         <v>113</v>
       </c>
-      <c r="O6" s="2" t="n">
+      <c r="O6" t="n">
         <v>8</v>
       </c>
-      <c r="P6" s="2" t="n">
+      <c r="P6" t="n">
         <v>1753</v>
       </c>
-      <c r="Q6" s="2" t="n">
+      <c r="Q6" t="n">
         <v>1349</v>
       </c>
       <c r="R6" s="2" t="n">
@@ -6088,25 +6088,25 @@
       <c r="S6" s="2" t="n">
         <v>73.11</v>
       </c>
-      <c r="T6" s="2" t="n">
+      <c r="T6" t="n">
         <v>69.52</v>
       </c>
-      <c r="U6" s="2" t="n">
+      <c r="U6" t="n">
         <v>68.36</v>
       </c>
-      <c r="V6" s="2" t="n">
+      <c r="V6" t="n">
         <v>1</v>
       </c>
-      <c r="W6" s="2" t="n">
+      <c r="W6" t="n">
         <v>5</v>
       </c>
-      <c r="X6" s="2" t="n">
+      <c r="X6" s="3" t="n">
         <v>19.88</v>
       </c>
-      <c r="Y6" s="2" t="n">
+      <c r="Y6" s="3" t="n">
         <v>7.39</v>
       </c>
-      <c r="Z6" s="2" t="n">
+      <c r="Z6" t="n">
         <v>0.96</v>
       </c>
       <c r="AA6" t="inlineStr">
@@ -6114,7 +6114,7 @@
           <t>Consumer Discretionary</t>
         </is>
       </c>
-      <c r="AB6" s="2" t="n">
+      <c r="AB6" t="n">
         <v>12375</v>
       </c>
       <c r="AC6" s="2" t="n">
@@ -6140,16 +6140,16 @@
           <t>Mar 2024</t>
         </is>
       </c>
-      <c r="D7" s="2" t="n">
+      <c r="D7" t="n">
         <v>432.73</v>
       </c>
-      <c r="E7" s="2" t="n">
+      <c r="E7" t="n">
         <v>91.77</v>
       </c>
-      <c r="F7" s="2" t="n">
+      <c r="F7" s="3" t="n">
         <v>13.58</v>
       </c>
-      <c r="G7" s="2" t="n">
+      <c r="G7" s="3" t="n">
         <v>2.88</v>
       </c>
       <c r="H7" s="2" t="n">
@@ -6158,28 +6158,28 @@
       <c r="I7" s="2" t="n">
         <v>3764.5</v>
       </c>
-      <c r="J7" s="2" t="n">
+      <c r="J7" t="n">
         <v>0.03</v>
       </c>
       <c r="K7" s="2" t="n">
         <v>1469</v>
       </c>
-      <c r="L7" s="2" t="n">
+      <c r="L7" t="n">
         <v>27.73</v>
       </c>
-      <c r="M7" s="2" t="n">
+      <c r="M7" t="n">
         <v>653</v>
       </c>
-      <c r="N7" s="2" t="n">
+      <c r="N7" t="n">
         <v>488.71</v>
       </c>
-      <c r="O7" s="2" t="n">
+      <c r="O7" t="n">
         <v>20</v>
       </c>
-      <c r="P7" s="2" t="n">
+      <c r="P7" t="n">
         <v>63</v>
       </c>
-      <c r="Q7" s="2" t="n">
+      <c r="Q7" t="n">
         <v>1941</v>
       </c>
       <c r="R7" s="2" t="n">
@@ -6188,25 +6188,25 @@
       <c r="S7" s="2" t="n">
         <v>19.3</v>
       </c>
-      <c r="T7" s="2" t="n">
+      <c r="T7" t="n">
         <v>18.97</v>
       </c>
-      <c r="U7" s="2" t="n">
+      <c r="U7" t="n">
         <v>55.01</v>
       </c>
-      <c r="V7" s="2" t="n">
+      <c r="V7" t="n">
         <v>1</v>
       </c>
-      <c r="W7" s="2" t="n">
+      <c r="W7" t="n">
         <v>3</v>
       </c>
-      <c r="X7" s="2" t="n">
+      <c r="X7" s="3" t="n">
         <v>3.77</v>
       </c>
-      <c r="Y7" s="2" t="n">
+      <c r="Y7" s="3" t="n">
         <v>5.03</v>
       </c>
-      <c r="Z7" s="2" t="n">
+      <c r="Z7" t="n">
         <v>0.8100000000000001</v>
       </c>
       <c r="AA7" t="inlineStr">
@@ -6214,7 +6214,7 @@
           <t>Financials</t>
         </is>
       </c>
-      <c r="AB7" s="2" t="n">
+      <c r="AB7" t="n">
         <v>1702</v>
       </c>
       <c r="AC7" s="2" t="n">
@@ -6240,10 +6240,10 @@
           <t>Mar 2024</t>
         </is>
       </c>
-      <c r="D8" s="2" t="n">
+      <c r="D8" t="n">
         <v>30.34</v>
       </c>
-      <c r="E8" s="2" t="n">
+      <c r="E8" t="n">
         <v>58.36</v>
       </c>
       <c r="F8" s="2" t="n">
@@ -6255,58 +6255,58 @@
       <c r="H8" s="2" t="n">
         <v>0.9399999999999999</v>
       </c>
-      <c r="I8" s="2" t="n">
+      <c r="I8" s="3" t="n">
         <v>5.95</v>
       </c>
-      <c r="J8" s="2" t="n">
+      <c r="J8" t="n">
         <v>0.23</v>
       </c>
       <c r="K8" s="2" t="n">
         <v>8250</v>
       </c>
-      <c r="L8" s="2" t="n">
+      <c r="L8" t="n">
         <v>25.34</v>
       </c>
-      <c r="M8" s="2" t="n">
+      <c r="M8" t="n">
         <v>38</v>
       </c>
-      <c r="N8" s="2" t="n">
+      <c r="N8" t="n">
         <v>122.17</v>
       </c>
-      <c r="O8" s="2" t="n">
+      <c r="O8" t="n">
         <v>16</v>
       </c>
-      <c r="P8" s="2" t="n">
+      <c r="P8" t="n">
         <v>49470</v>
       </c>
-      <c r="Q8" s="2" t="n">
+      <c r="Q8" t="n">
         <v>15018</v>
       </c>
       <c r="R8" s="2" t="n">
         <v>19.58</v>
       </c>
-      <c r="S8" s="2" t="n">
+      <c r="S8" s="3" t="n">
         <v>14.91</v>
       </c>
-      <c r="T8" s="2" t="n">
+      <c r="T8" t="n">
         <v>14.87</v>
       </c>
-      <c r="U8" s="2" t="n">
+      <c r="U8" t="n">
         <v>28.63</v>
       </c>
-      <c r="V8" s="2" t="n">
+      <c r="V8" t="n">
         <v>1</v>
       </c>
-      <c r="W8" s="2" t="n">
+      <c r="W8" t="n">
         <v>4</v>
       </c>
-      <c r="X8" s="2" t="n">
+      <c r="X8" s="3" t="n">
         <v>35.34</v>
       </c>
-      <c r="Y8" s="2" t="n">
+      <c r="Y8" s="3" t="n">
         <v>10.99</v>
       </c>
-      <c r="Z8" s="2" t="n">
+      <c r="Z8" t="n">
         <v>1.19</v>
       </c>
       <c r="AA8" t="inlineStr">
@@ -6314,7 +6314,7 @@
           <t>Industrials</t>
         </is>
       </c>
-      <c r="AB8" s="2" t="n">
+      <c r="AB8" t="n">
         <v>26711</v>
       </c>
       <c r="AC8" s="2" t="n">
@@ -6340,10 +6340,10 @@
           <t>Mar 2024</t>
         </is>
       </c>
-      <c r="D9" s="2" t="n">
+      <c r="D9" t="n">
         <v>20.53</v>
       </c>
-      <c r="E9" s="2" t="n">
+      <c r="E9" t="n">
         <v>24.84</v>
       </c>
       <c r="F9" s="2" t="n">
@@ -6358,55 +6358,55 @@
       <c r="I9" s="2" t="n">
         <v>141.75</v>
       </c>
-      <c r="J9" s="2" t="n">
+      <c r="J9" t="n">
         <v>1.13</v>
       </c>
       <c r="K9" s="2" t="n">
         <v>797</v>
       </c>
-      <c r="L9" s="2" t="n">
+      <c r="L9" t="n">
         <v>7.11</v>
       </c>
-      <c r="M9" s="2" t="n">
+      <c r="M9" t="n">
         <v>565</v>
       </c>
-      <c r="N9" s="2" t="n">
+      <c r="N9" t="n">
         <v>176.14</v>
       </c>
-      <c r="O9" s="2" t="n">
+      <c r="O9" t="n">
         <v>73</v>
       </c>
-      <c r="P9" s="2" t="n">
+      <c r="P9" t="n">
         <v>83</v>
       </c>
-      <c r="Q9" s="2" t="n">
+      <c r="Q9" t="n">
         <v>1213</v>
       </c>
-      <c r="R9" s="2" t="n">
+      <c r="R9" s="3" t="n">
         <v>9.720000000000001</v>
       </c>
       <c r="S9" s="2" t="n">
         <v>21.69</v>
       </c>
-      <c r="T9" s="2" t="n">
+      <c r="T9" t="n">
         <v>21.66</v>
       </c>
-      <c r="U9" s="2" t="n">
+      <c r="U9" t="n">
         <v>10.71</v>
       </c>
-      <c r="V9" s="2" t="n">
+      <c r="V9" t="n">
         <v>1</v>
       </c>
-      <c r="W9" s="2" t="n">
+      <c r="W9" t="n">
         <v>5</v>
       </c>
-      <c r="X9" s="2" t="n">
+      <c r="X9" s="3" t="n">
         <v>8.699999999999999</v>
       </c>
-      <c r="Y9" s="2" t="n">
+      <c r="Y9" s="3" t="n">
         <v>27.89</v>
       </c>
-      <c r="Z9" s="2" t="n">
+      <c r="Z9" t="n">
         <v>1.49</v>
       </c>
       <c r="AA9" t="inlineStr">
@@ -6414,7 +6414,7 @@
           <t>Industrials</t>
         </is>
       </c>
-      <c r="AB9" s="2" t="n">
+      <c r="AB9" t="n">
         <v>5849</v>
       </c>
       <c r="AC9" s="2" t="n">
@@ -6440,10 +6440,10 @@
           <t>Mar 2024</t>
         </is>
       </c>
-      <c r="D10" s="2" t="n">
+      <c r="D10" t="n">
         <v>5.56</v>
       </c>
-      <c r="E10" s="2" t="n">
+      <c r="E10" t="n">
         <v>9.74</v>
       </c>
       <c r="F10" s="2" t="n">
@@ -6455,58 +6455,58 @@
       <c r="H10" s="2" t="n">
         <v>0.72</v>
       </c>
-      <c r="I10" s="2" t="n">
+      <c r="I10" s="3" t="n">
         <v>10.28</v>
       </c>
-      <c r="J10" s="2" t="n">
+      <c r="J10" t="n">
         <v>1.61</v>
       </c>
       <c r="K10" s="2" t="n">
         <v>39635</v>
       </c>
-      <c r="L10" s="2" t="n">
+      <c r="L10" t="n">
         <v>4.05</v>
       </c>
-      <c r="M10" s="2" t="n">
+      <c r="M10" t="n">
         <v>30</v>
       </c>
-      <c r="N10" s="2" t="n">
+      <c r="N10" t="n">
         <v>13.32</v>
       </c>
-      <c r="O10" s="2" t="n">
+      <c r="O10" t="n">
         <v>40</v>
       </c>
-      <c r="P10" s="2" t="n">
+      <c r="P10" t="n">
         <v>132628</v>
       </c>
-      <c r="Q10" s="2" t="n">
+      <c r="Q10" t="n">
         <v>71099</v>
       </c>
-      <c r="R10" s="2" t="n">
+      <c r="R10" s="3" t="n">
         <v>8.01</v>
       </c>
       <c r="S10" s="2" t="n">
         <v>20.1</v>
       </c>
-      <c r="T10" s="2" t="n">
+      <c r="T10" t="n">
         <v>20.11</v>
       </c>
-      <c r="U10" s="2" t="n">
+      <c r="U10" t="n">
         <v>28.73</v>
       </c>
-      <c r="V10" s="2" t="n">
+      <c r="V10" t="n">
         <v>1</v>
       </c>
-      <c r="W10" s="2" t="n">
+      <c r="W10" t="n">
         <v>4</v>
       </c>
-      <c r="X10" s="2" t="n">
+      <c r="X10" s="3" t="n">
         <v>29.92</v>
       </c>
-      <c r="Y10" s="2" t="n">
+      <c r="Y10" s="3" t="n">
         <v>67.39</v>
       </c>
-      <c r="Z10" s="2" t="n">
+      <c r="Z10" t="n">
         <v>4.46</v>
       </c>
       <c r="AA10" t="inlineStr">
@@ -6514,7 +6514,7 @@
           <t>Energy</t>
         </is>
       </c>
-      <c r="AB10" s="2" t="n">
+      <c r="AB10" t="n">
         <v>776352</v>
       </c>
       <c r="AC10" s="2" t="n">
@@ -6540,73 +6540,73 @@
           <t>Mar 2024</t>
         </is>
       </c>
-      <c r="D11" s="2" t="n">
+      <c r="D11" t="n">
         <v>5.71</v>
       </c>
-      <c r="E11" s="2" t="n">
+      <c r="E11" t="n">
         <v>52.2</v>
       </c>
-      <c r="F11" s="2" t="n">
+      <c r="F11" s="3" t="n">
         <v>10.36</v>
       </c>
       <c r="G11" s="2" t="n">
         <v>26.25</v>
       </c>
-      <c r="H11" s="2" t="n">
+      <c r="H11" s="3" t="n">
         <v>2.61</v>
       </c>
-      <c r="I11" s="2" t="n">
+      <c r="I11" s="3" t="n">
         <v>3.31</v>
       </c>
-      <c r="J11" s="2" t="n">
+      <c r="J11" t="n">
         <v>0.34</v>
       </c>
       <c r="K11" s="2" t="n">
         <v>27809</v>
       </c>
-      <c r="L11" s="2" t="n">
+      <c r="L11" t="n">
         <v>34.06</v>
       </c>
-      <c r="M11" s="2" t="n">
+      <c r="M11" t="n">
         <v>13</v>
       </c>
-      <c r="N11" s="2" t="n">
+      <c r="N11" t="n">
         <v>28.72</v>
       </c>
-      <c r="O11" s="2" t="n">
+      <c r="O11" t="n">
         <v>62</v>
       </c>
-      <c r="P11" s="2" t="n">
+      <c r="P11" t="n">
         <v>215592</v>
       </c>
-      <c r="Q11" s="2" t="n">
+      <c r="Q11" t="n">
         <v>78898</v>
       </c>
-      <c r="R11" s="2" t="n">
+      <c r="R11" s="3" t="n">
         <v>13.17</v>
       </c>
       <c r="S11" s="2" t="n">
         <v>38.36</v>
       </c>
-      <c r="T11" s="2" t="n">
+      <c r="T11" t="n">
         <v>67.03</v>
       </c>
-      <c r="U11" s="2" t="n">
+      <c r="U11" t="n">
         <v>14.23</v>
       </c>
-      <c r="V11" s="2" t="n">
+      <c r="V11" t="n">
         <v>1</v>
       </c>
-      <c r="W11" s="2" t="n">
+      <c r="W11" t="n">
         <v>1</v>
       </c>
-      <c r="X11" s="2" t="n">
+      <c r="X11" s="3" t="n">
         <v>410.95</v>
       </c>
-      <c r="Y11" s="2" t="n">
+      <c r="Y11" s="3" t="n">
         <v>186.02</v>
       </c>
-      <c r="Z11" s="2" t="n">
+      <c r="Z11" t="n">
         <v>1.16</v>
       </c>
       <c r="AA11" t="inlineStr">
@@ -6614,7 +6614,7 @@
           <t>Communication Services</t>
         </is>
       </c>
-      <c r="AB11" s="2" t="n">
+      <c r="AB11" t="n">
         <v>149982</v>
       </c>
       <c r="AC11" s="2" t="n">
@@ -6640,10 +6640,10 @@
           <t>Mar 2024</t>
         </is>
       </c>
-      <c r="D12" s="2" t="n">
+      <c r="D12" t="n">
         <v>7.26</v>
       </c>
-      <c r="E12" s="2" t="n">
+      <c r="E12" t="n">
         <v>13.6</v>
       </c>
       <c r="F12" s="2" t="n">
@@ -6652,61 +6652,61 @@
       <c r="G12" s="2" t="n">
         <v>30.98</v>
       </c>
-      <c r="H12" s="2" t="n">
+      <c r="H12" s="3" t="n">
         <v>1.26</v>
       </c>
-      <c r="I12" s="2" t="n">
+      <c r="I12" s="3" t="n">
         <v>6.53</v>
       </c>
-      <c r="J12" s="2" t="n">
+      <c r="J12" t="n">
         <v>1.19</v>
       </c>
       <c r="K12" s="2" t="n">
         <v>45133</v>
       </c>
-      <c r="L12" s="2" t="n">
+      <c r="L12" t="n">
         <v>5.2</v>
       </c>
-      <c r="M12" s="2" t="n">
+      <c r="M12" t="n">
         <v>94</v>
       </c>
-      <c r="N12" s="2" t="n">
+      <c r="N12" t="n">
         <v>110.86</v>
       </c>
-      <c r="O12" s="2" t="n">
+      <c r="O12" t="n">
         <v>7</v>
       </c>
-      <c r="P12" s="2" t="n">
+      <c r="P12" t="n">
         <v>107262</v>
       </c>
-      <c r="Q12" s="2" t="n">
+      <c r="Q12" t="n">
         <v>67915</v>
       </c>
-      <c r="R12" s="2" t="n">
+      <c r="R12" s="3" t="n">
         <v>7.72</v>
       </c>
       <c r="S12" s="3" t="n">
         <v/>
       </c>
-      <c r="T12" s="3" t="n">
+      <c r="T12" t="n">
         <v/>
       </c>
-      <c r="U12" s="2" t="n">
+      <c r="U12" t="n">
         <v>20.58</v>
       </c>
-      <c r="V12" s="2" t="n">
+      <c r="V12" t="n">
         <v>1</v>
       </c>
-      <c r="W12" s="2" t="n">
+      <c r="W12" t="n">
         <v>3</v>
       </c>
-      <c r="X12" s="2" t="n">
+      <c r="X12" s="3" t="n">
         <v>5.32</v>
       </c>
-      <c r="Y12" s="2" t="n">
+      <c r="Y12" s="3" t="n">
         <v>4.51</v>
       </c>
-      <c r="Z12" s="2" t="n">
+      <c r="Z12" t="n">
         <v>1.4</v>
       </c>
       <c r="AA12" t="inlineStr">
@@ -6714,7 +6714,7 @@
           <t>Consumer Discretionary</t>
         </is>
       </c>
-      <c r="AB12" s="2" t="n">
+      <c r="AB12" t="n">
         <v>437928</v>
       </c>
       <c r="AC12" s="2" t="n">
@@ -6740,13 +6740,13 @@
           <t>Mar 2024</t>
         </is>
       </c>
-      <c r="D13" s="2" t="n">
+      <c r="D13" t="n">
         <v>4.7</v>
       </c>
-      <c r="E13" s="2" t="n">
+      <c r="E13" t="n">
         <v>88.95</v>
       </c>
-      <c r="F13" s="2" t="n">
+      <c r="F13" s="3" t="n">
         <v>9.57</v>
       </c>
       <c r="G13" s="2" t="n">
@@ -6758,55 +6758,55 @@
       <c r="I13" s="2" t="n">
         <v>126.47</v>
       </c>
-      <c r="J13" s="2" t="n">
+      <c r="J13" t="n">
         <v>0.9399999999999999</v>
       </c>
       <c r="K13" s="2" t="n">
         <v>9789</v>
       </c>
-      <c r="L13" s="2" t="n">
+      <c r="L13" t="n">
         <v>6.61</v>
       </c>
-      <c r="M13" s="2" t="n">
+      <c r="M13" t="n">
         <v>45</v>
       </c>
-      <c r="N13" s="2" t="n">
+      <c r="N13" t="n">
         <v>478.14</v>
       </c>
-      <c r="O13" s="2" t="n">
+      <c r="O13" t="n">
         <v>8</v>
       </c>
-      <c r="P13" s="2" t="n">
+      <c r="P13" t="n">
         <v>56356</v>
       </c>
-      <c r="Q13" s="2" t="n">
+      <c r="Q13" t="n">
         <v>24056</v>
       </c>
-      <c r="R13" s="2" t="n">
+      <c r="R13" s="3" t="n">
         <v>10.59</v>
       </c>
-      <c r="S13" s="2" t="n">
+      <c r="S13" s="3" t="n">
         <v>13.07</v>
       </c>
-      <c r="T13" s="2" t="n">
+      <c r="T13" t="n">
         <v>13.4</v>
       </c>
-      <c r="U13" s="2" t="n">
+      <c r="U13" t="n">
         <v>17.83</v>
       </c>
-      <c r="V13" s="2" t="n">
+      <c r="V13" t="n">
         <v>1</v>
       </c>
-      <c r="W13" s="2" t="n">
+      <c r="W13" t="n">
         <v>2</v>
       </c>
-      <c r="X13" s="2" t="n">
+      <c r="X13" s="3" t="n">
         <v>64.68000000000001</v>
       </c>
-      <c r="Y13" s="2" t="n">
+      <c r="Y13" s="3" t="n">
         <v>6.09</v>
       </c>
-      <c r="Z13" s="2" t="n">
+      <c r="Z13" t="n">
         <v>0.27</v>
       </c>
       <c r="AA13" t="inlineStr">
@@ -6814,7 +6814,7 @@
           <t>Materials</t>
         </is>
       </c>
-      <c r="AB13" s="2" t="n">
+      <c r="AB13" t="n">
         <v>215962</v>
       </c>
       <c r="AC13" s="2" t="n">
@@ -6840,10 +6840,10 @@
           <t>Mar 2024</t>
         </is>
       </c>
-      <c r="D14" s="2" t="n">
+      <c r="D14" t="n">
         <v>19.82</v>
       </c>
-      <c r="E14" s="2" t="n">
+      <c r="E14" t="n">
         <v>26.84</v>
       </c>
       <c r="F14" s="2" t="n">
@@ -6858,55 +6858,55 @@
       <c r="I14" s="2" t="n">
         <v>58.33</v>
       </c>
-      <c r="J14" s="2" t="n">
+      <c r="J14" t="n">
         <v>0.57</v>
       </c>
       <c r="K14" s="2" t="n">
         <v>11372</v>
       </c>
-      <c r="L14" s="2" t="n">
+      <c r="L14" t="n">
         <v>1.57</v>
       </c>
-      <c r="M14" s="2" t="n">
+      <c r="M14" t="n">
         <v>40</v>
       </c>
-      <c r="N14" s="2" t="n">
+      <c r="N14" t="n">
         <v>265.28</v>
       </c>
-      <c r="O14" s="2" t="n">
+      <c r="O14" t="n">
         <v>34</v>
       </c>
-      <c r="P14" s="2" t="n">
+      <c r="P14" t="n">
         <v>3274</v>
       </c>
-      <c r="Q14" s="2" t="n">
+      <c r="Q14" t="n">
         <v>12135</v>
       </c>
-      <c r="R14" s="2" t="n">
+      <c r="R14" s="3" t="n">
         <v>10.78</v>
       </c>
       <c r="S14" s="2" t="n">
         <v>24.54</v>
       </c>
-      <c r="T14" s="2" t="n">
+      <c r="T14" t="n">
         <v>29.46</v>
       </c>
-      <c r="U14" s="2" t="n">
+      <c r="U14" t="n">
         <v>13.13</v>
       </c>
-      <c r="V14" s="2" t="n">
+      <c r="V14" t="n">
         <v>1</v>
       </c>
-      <c r="W14" s="2" t="n">
+      <c r="W14" t="n">
         <v>4</v>
       </c>
-      <c r="X14" s="2" t="n">
+      <c r="X14" s="3" t="n">
         <v>113.17</v>
       </c>
-      <c r="Y14" s="2" t="n">
+      <c r="Y14" s="3" t="n">
         <v>17.06</v>
       </c>
-      <c r="Z14" s="2" t="n">
+      <c r="Z14" t="n">
         <v>0.75</v>
       </c>
       <c r="AA14" t="inlineStr">
@@ -6914,7 +6914,7 @@
           <t>Healthcare</t>
         </is>
       </c>
-      <c r="AB14" s="2" t="n">
+      <c r="AB14" t="n">
         <v>48497</v>
       </c>
       <c r="AC14" s="2" t="n">
@@ -6940,10 +6940,10 @@
           <t>Mar 2024</t>
         </is>
       </c>
-      <c r="D15" s="2" t="n">
+      <c r="D15" t="n">
         <v>16.12</v>
       </c>
-      <c r="E15" s="2" t="n">
+      <c r="E15" t="n">
         <v>75.59</v>
       </c>
       <c r="F15" s="2" t="n">
@@ -6958,55 +6958,55 @@
       <c r="I15" s="2" t="n">
         <v>35.34</v>
       </c>
-      <c r="J15" s="2" t="n">
+      <c r="J15" t="n">
         <v>0.79</v>
       </c>
       <c r="K15" s="2" t="n">
         <v>1152</v>
       </c>
-      <c r="L15" s="2" t="n">
+      <c r="L15" t="n">
         <v>11.57</v>
       </c>
-      <c r="M15" s="2" t="n">
+      <c r="M15" t="n">
         <v>51</v>
       </c>
-      <c r="N15" s="2" t="n">
+      <c r="N15" t="n">
         <v>165.88</v>
       </c>
-      <c r="O15" s="2" t="n">
+      <c r="O15" t="n">
         <v>25</v>
       </c>
-      <c r="P15" s="2" t="n">
+      <c r="P15" t="n">
         <v>559</v>
       </c>
-      <c r="Q15" s="2" t="n">
+      <c r="Q15" t="n">
         <v>4134</v>
       </c>
-      <c r="R15" s="2" t="n">
+      <c r="R15" s="3" t="n">
         <v>9.51</v>
       </c>
       <c r="S15" s="2" t="n">
         <v>22.73</v>
       </c>
-      <c r="T15" s="2" t="n">
+      <c r="T15" t="n">
         <v>21.83</v>
       </c>
-      <c r="U15" s="2" t="n">
+      <c r="U15" t="n">
         <v>10.39</v>
       </c>
-      <c r="V15" s="2" t="n">
+      <c r="V15" t="n">
         <v>1</v>
       </c>
-      <c r="W15" s="2" t="n">
+      <c r="W15" t="n">
         <v>4</v>
       </c>
-      <c r="X15" s="2" t="n">
+      <c r="X15" s="3" t="n">
         <v>63.28</v>
       </c>
-      <c r="Y15" s="2" t="n">
+      <c r="Y15" s="3" t="n">
         <v>19.46</v>
       </c>
-      <c r="Z15" s="2" t="n">
+      <c r="Z15" t="n">
         <v>0.77</v>
       </c>
       <c r="AA15" t="inlineStr">
@@ -7014,7 +7014,7 @@
           <t>Healthcare</t>
         </is>
       </c>
-      <c r="AB15" s="2" t="n">
+      <c r="AB15" t="n">
         <v>25774</v>
       </c>
       <c r="AC15" s="2" t="n">
@@ -7040,10 +7040,10 @@
           <t>Mar 2024</t>
         </is>
       </c>
-      <c r="D16" s="2" t="n">
+      <c r="D16" t="n">
         <v>15.44</v>
       </c>
-      <c r="E16" s="2" t="n">
+      <c r="E16" t="n">
         <v>31.39</v>
       </c>
       <c r="F16" s="2" t="n">
@@ -7055,58 +7055,58 @@
       <c r="H16" s="2" t="n">
         <v>0.59</v>
       </c>
-      <c r="I16" s="2" t="n">
+      <c r="I16" s="3" t="n">
         <v>9.93</v>
       </c>
-      <c r="J16" s="2" t="n">
+      <c r="J16" t="n">
         <v>0.74</v>
       </c>
       <c r="K16" s="2" t="n">
         <v>3106</v>
       </c>
-      <c r="L16" s="2" t="n">
+      <c r="L16" t="n">
         <v>1.49</v>
       </c>
-      <c r="M16" s="2" t="n">
+      <c r="M16" t="n">
         <v>49</v>
       </c>
-      <c r="N16" s="2" t="n">
+      <c r="N16" t="n">
         <v>40.57</v>
       </c>
-      <c r="O16" s="2" t="n">
+      <c r="O16" t="n">
         <v>57</v>
       </c>
-      <c r="P16" s="2" t="n">
+      <c r="P16" t="n">
         <v>4022</v>
       </c>
-      <c r="Q16" s="2" t="n">
+      <c r="Q16" t="n">
         <v>3266</v>
       </c>
-      <c r="R16" s="2" t="n">
+      <c r="R16" s="3" t="n">
         <v>6.93</v>
       </c>
       <c r="S16" s="2" t="n">
         <v>30.59</v>
       </c>
-      <c r="T16" s="2" t="n">
+      <c r="T16" t="n">
         <v>30.39</v>
       </c>
-      <c r="U16" s="2" t="n">
+      <c r="U16" t="n">
         <v>10.25</v>
       </c>
-      <c r="V16" s="2" t="n">
+      <c r="V16" t="n">
         <v>1</v>
       </c>
-      <c r="W16" s="2" t="n">
+      <c r="W16" t="n">
         <v>4</v>
       </c>
-      <c r="X16" s="2" t="n">
+      <c r="X16" s="3" t="n">
         <v>45.88</v>
       </c>
-      <c r="Y16" s="2" t="n">
+      <c r="Y16" s="3" t="n">
         <v>55.42</v>
       </c>
-      <c r="Z16" s="2" t="n">
+      <c r="Z16" t="n">
         <v>2.54</v>
       </c>
       <c r="AA16" t="inlineStr">
@@ -7114,7 +7114,7 @@
           <t>Healthcare</t>
         </is>
       </c>
-      <c r="AB16" s="2" t="n">
+      <c r="AB16" t="n">
         <v>10728</v>
       </c>
       <c r="AC16" s="2" t="n">
@@ -7140,13 +7140,13 @@
           <t>Mar 2024</t>
         </is>
       </c>
-      <c r="D17" s="2" t="n">
+      <c r="D17" t="n">
         <v>4.99</v>
       </c>
-      <c r="E17" s="2" t="n">
+      <c r="E17" t="n">
         <v>8.08</v>
       </c>
-      <c r="F17" s="2" t="n">
+      <c r="F17" s="3" t="n">
         <v>13.56</v>
       </c>
       <c r="G17" s="2" t="n">
@@ -7158,28 +7158,28 @@
       <c r="I17" s="2" t="n">
         <v>73.29000000000001</v>
       </c>
-      <c r="J17" s="2" t="n">
+      <c r="J17" t="n">
         <v>2.4</v>
       </c>
       <c r="K17" s="2" t="n">
         <v>278</v>
       </c>
-      <c r="L17" s="2" t="n">
+      <c r="L17" t="n">
         <v>4.86</v>
       </c>
-      <c r="M17" s="2" t="n">
+      <c r="M17" t="n">
         <v>39</v>
       </c>
-      <c r="N17" s="2" t="n">
+      <c r="N17" t="n">
         <v>28.72</v>
       </c>
-      <c r="O17" s="2" t="n">
+      <c r="O17" t="n">
         <v>0</v>
       </c>
-      <c r="P17" s="2" t="n">
+      <c r="P17" t="n">
         <v>592</v>
       </c>
-      <c r="Q17" s="2" t="n">
+      <c r="Q17" t="n">
         <v>2746</v>
       </c>
       <c r="R17" s="2" t="n">
@@ -7188,25 +7188,25 @@
       <c r="S17" s="2" t="n">
         <v>22.97</v>
       </c>
-      <c r="T17" s="2" t="n">
+      <c r="T17" t="n">
         <v>22.74</v>
       </c>
-      <c r="U17" s="2" t="n">
+      <c r="U17" t="n">
         <v>28.13</v>
       </c>
-      <c r="V17" s="2" t="n">
+      <c r="V17" t="n">
         <v>1</v>
       </c>
-      <c r="W17" s="2" t="n">
+      <c r="W17" t="n">
         <v>3</v>
       </c>
-      <c r="X17" s="2" t="n">
+      <c r="X17" s="3" t="n">
         <v>9.720000000000001</v>
       </c>
-      <c r="Y17" s="2" t="n">
+      <c r="Y17" s="3" t="n">
         <v>13.2</v>
       </c>
-      <c r="Z17" s="2" t="n">
+      <c r="Z17" t="n">
         <v>0</v>
       </c>
       <c r="AA17" t="inlineStr">
@@ -7214,7 +7214,7 @@
           <t>Consumer Discretionary</t>
         </is>
       </c>
-      <c r="AB17" s="2" t="n">
+      <c r="AB17" t="n">
         <v>50789</v>
       </c>
       <c r="AC17" s="2" t="n">
@@ -7240,10 +7240,10 @@
           <t>Mar 2024</t>
         </is>
       </c>
-      <c r="D18" s="2" t="n">
+      <c r="D18" t="n">
         <v>9.51</v>
       </c>
-      <c r="E18" s="2" t="n">
+      <c r="E18" t="n">
         <v>13.13</v>
       </c>
       <c r="F18" s="2" t="n">
@@ -7258,55 +7258,55 @@
       <c r="I18" s="2" t="n">
         <v>117.91</v>
       </c>
-      <c r="J18" s="2" t="n">
+      <c r="J18" t="n">
         <v>1.23</v>
       </c>
       <c r="K18" s="2" t="n">
         <v>4936</v>
       </c>
-      <c r="L18" s="2" t="n">
+      <c r="L18" t="n">
         <v>8.359999999999999</v>
       </c>
-      <c r="M18" s="2" t="n">
+      <c r="M18" t="n">
         <v>429</v>
       </c>
-      <c r="N18" s="2" t="n">
+      <c r="N18" t="n">
         <v>545.45</v>
       </c>
-      <c r="O18" s="2" t="n">
+      <c r="O18" t="n">
         <v>29</v>
       </c>
-      <c r="P18" s="2" t="n">
+      <c r="P18" t="n">
         <v>119</v>
       </c>
-      <c r="Q18" s="2" t="n">
+      <c r="Q18" t="n">
         <v>16801</v>
       </c>
-      <c r="R18" s="2" t="n">
+      <c r="R18" s="3" t="n">
         <v>10.51</v>
       </c>
-      <c r="S18" s="2" t="n">
+      <c r="S18" s="3" t="n">
         <v>12.01</v>
       </c>
-      <c r="T18" s="2" t="n">
+      <c r="T18" t="n">
         <v>11.14</v>
       </c>
-      <c r="U18" s="2" t="n">
+      <c r="U18" t="n">
         <v>26.32</v>
       </c>
-      <c r="V18" s="2" t="n">
+      <c r="V18" t="n">
         <v>1</v>
       </c>
-      <c r="W18" s="2" t="n">
+      <c r="W18" t="n">
         <v>4</v>
       </c>
-      <c r="X18" s="2" t="n">
+      <c r="X18" s="3" t="n">
         <v>11.71</v>
       </c>
-      <c r="Y18" s="2" t="n">
+      <c r="Y18" s="3" t="n">
         <v>9.210000000000001</v>
       </c>
-      <c r="Z18" s="2" t="n">
+      <c r="Z18" t="n">
         <v>0.58</v>
       </c>
       <c r="AA18" t="inlineStr">
@@ -7314,7 +7314,7 @@
           <t>Consumer Discretionary</t>
         </is>
       </c>
-      <c r="AB18" s="2" t="n">
+      <c r="AB18" t="n">
         <v>141858</v>
       </c>
       <c r="AC18" s="2" t="n">
@@ -7340,10 +7340,10 @@
           <t>Mar 2024</t>
         </is>
       </c>
-      <c r="D19" s="2" t="n">
+      <c r="D19" t="n">
         <v>14.11</v>
       </c>
-      <c r="E19" s="2" t="n">
+      <c r="E19" t="n">
         <v>21.87</v>
       </c>
       <c r="F19" s="2" t="n">
@@ -7358,55 +7358,55 @@
       <c r="I19" s="2" t="n">
         <v>54.33</v>
       </c>
-      <c r="J19" s="2" t="n">
+      <c r="J19" t="n">
         <v>1.03</v>
       </c>
       <c r="K19" s="2" t="n">
         <v>955</v>
       </c>
-      <c r="L19" s="2" t="n">
+      <c r="L19" t="n">
         <v>14.29</v>
       </c>
-      <c r="M19" s="2" t="n">
+      <c r="M19" t="n">
         <v>34</v>
       </c>
-      <c r="N19" s="2" t="n">
+      <c r="N19" t="n">
         <v>164.84</v>
       </c>
-      <c r="O19" s="2" t="n">
+      <c r="O19" t="n">
         <v>47</v>
       </c>
-      <c r="P19" s="2" t="n">
+      <c r="P19" t="n">
         <v>382</v>
       </c>
-      <c r="Q19" s="2" t="n">
+      <c r="Q19" t="n">
         <v>2724</v>
       </c>
-      <c r="R19" s="2" t="n">
+      <c r="R19" s="3" t="n">
         <v>11.84</v>
       </c>
-      <c r="S19" s="2" t="n">
+      <c r="S19" s="3" t="n">
         <v>13.49</v>
       </c>
-      <c r="T19" s="2" t="n">
+      <c r="T19" t="n">
         <v>13.56</v>
       </c>
-      <c r="U19" s="2" t="n">
+      <c r="U19" t="n">
         <v>19.3</v>
       </c>
-      <c r="V19" s="2" t="n">
+      <c r="V19" t="n">
         <v>1</v>
       </c>
-      <c r="W19" s="2" t="n">
+      <c r="W19" t="n">
         <v>5</v>
       </c>
-      <c r="X19" s="2" t="n">
+      <c r="X19" s="3" t="n">
         <v>20.14</v>
       </c>
-      <c r="Y19" s="2" t="n">
+      <c r="Y19" s="3" t="n">
         <v>4.15</v>
       </c>
-      <c r="Z19" s="2" t="n">
+      <c r="Z19" t="n">
         <v>6.86</v>
       </c>
       <c r="AA19" t="inlineStr">
@@ -7414,7 +7414,7 @@
           <t>Materials</t>
         </is>
       </c>
-      <c r="AB19" s="2" t="n">
+      <c r="AB19" t="n">
         <v>12383</v>
       </c>
       <c r="AC19" s="2" t="n">
@@ -7440,46 +7440,46 @@
           <t>Mar 2024</t>
         </is>
       </c>
-      <c r="D20" s="2" t="n">
+      <c r="D20" t="n">
         <v>24.06</v>
       </c>
-      <c r="E20" s="2" t="n">
+      <c r="E20" t="n">
         <v>99.5</v>
       </c>
-      <c r="F20" s="2" t="n">
+      <c r="F20" s="3" t="n">
         <v>13.04</v>
       </c>
-      <c r="G20" s="2" t="n">
+      <c r="G20" s="3" t="n">
         <v>5.75</v>
       </c>
-      <c r="H20" s="2" t="n">
+      <c r="H20" s="3" t="n">
         <v>8.380000000000001</v>
       </c>
-      <c r="I20" s="2" t="n">
+      <c r="I20" s="3" t="n">
         <v>1.32</v>
       </c>
-      <c r="J20" s="2" t="n">
+      <c r="J20" t="n">
         <v>0.05</v>
       </c>
       <c r="K20" s="2" t="n">
         <v>7906</v>
       </c>
-      <c r="L20" s="2" t="n">
+      <c r="L20" t="n">
         <v>0.03</v>
       </c>
-      <c r="M20" s="2" t="n">
+      <c r="M20" t="n">
         <v>5</v>
       </c>
-      <c r="N20" s="2" t="n">
+      <c r="N20" t="n">
         <v>3.76</v>
       </c>
-      <c r="O20" s="2" t="n">
+      <c r="O20" t="n">
         <v>31</v>
       </c>
-      <c r="P20" s="2" t="n">
+      <c r="P20" t="n">
         <v>412039</v>
       </c>
-      <c r="Q20" s="2" t="n">
+      <c r="Q20" t="n">
         <v>7914</v>
       </c>
       <c r="R20" s="2" t="n">
@@ -7488,25 +7488,25 @@
       <c r="S20" s="2" t="n">
         <v>23.25</v>
       </c>
-      <c r="T20" s="2" t="n">
+      <c r="T20" t="n">
         <v>20.11</v>
       </c>
-      <c r="U20" s="2" t="n">
+      <c r="U20" t="n">
         <v>19.1</v>
       </c>
-      <c r="V20" s="2" t="n">
+      <c r="V20" t="n">
         <v>1</v>
       </c>
-      <c r="W20" s="2" t="n">
+      <c r="W20" t="n">
         <v>1</v>
       </c>
-      <c r="X20" s="2" t="n">
+      <c r="X20" s="3" t="n">
         <v>1084.11</v>
       </c>
-      <c r="Y20" s="2" t="n">
+      <c r="Y20" s="3" t="n">
         <v>1441.63</v>
       </c>
-      <c r="Z20" s="2" t="n">
+      <c r="Z20" t="n">
         <v>0.57</v>
       </c>
       <c r="AA20" t="inlineStr">
@@ -7514,7 +7514,7 @@
           <t>Financials</t>
         </is>
       </c>
-      <c r="AB20" s="2" t="n">
+      <c r="AB20" t="n">
         <v>26645</v>
       </c>
       <c r="AC20" s="2" t="n">
@@ -7540,10 +7540,10 @@
           <t>Mar 2024</t>
         </is>
       </c>
-      <c r="D21" s="2" t="n">
+      <c r="D21" t="n">
         <v>14.89</v>
       </c>
-      <c r="E21" s="2" t="n">
+      <c r="E21" t="n">
         <v>12.52</v>
       </c>
       <c r="F21" s="2" t="n">
@@ -7558,55 +7558,55 @@
       <c r="I21" s="2" t="n">
         <v>71.78</v>
       </c>
-      <c r="J21" s="2" t="n">
+      <c r="J21" t="n">
         <v>0.96</v>
       </c>
       <c r="K21" s="2" t="n">
         <v>1536</v>
       </c>
-      <c r="L21" s="2" t="n">
+      <c r="L21" t="n">
         <v>1.69</v>
       </c>
-      <c r="M21" s="2" t="n">
+      <c r="M21" t="n">
         <v>844</v>
       </c>
-      <c r="N21" s="2" t="n">
+      <c r="N21" t="n">
         <v>402.13</v>
       </c>
-      <c r="O21" s="2" t="n">
+      <c r="O21" t="n">
         <v>44</v>
       </c>
-      <c r="P21" s="2" t="n">
+      <c r="P21" t="n">
         <v>39</v>
       </c>
-      <c r="Q21" s="2" t="n">
+      <c r="Q21" t="n">
         <v>1253</v>
       </c>
-      <c r="R21" s="2" t="n">
+      <c r="R21" s="3" t="n">
         <v>6.72</v>
       </c>
-      <c r="S21" s="2" t="n">
+      <c r="S21" s="3" t="n">
         <v>9.279999999999999</v>
       </c>
-      <c r="T21" s="2" t="n">
+      <c r="T21" t="n">
         <v>9.26</v>
       </c>
-      <c r="U21" s="2" t="n">
+      <c r="U21" t="n">
         <v>19.84</v>
       </c>
-      <c r="V21" s="2" t="n">
+      <c r="V21" t="n">
         <v>1</v>
       </c>
-      <c r="W21" s="2" t="n">
+      <c r="W21" t="n">
         <v>4</v>
       </c>
-      <c r="X21" s="2" t="n">
+      <c r="X21" s="3" t="n">
         <v>4.11</v>
       </c>
-      <c r="Y21" s="2" t="n">
+      <c r="Y21" s="3" t="n">
         <v>8.619999999999999</v>
       </c>
-      <c r="Z21" s="2" t="n">
+      <c r="Z21" t="n">
         <v>1.27</v>
       </c>
       <c r="AA21" t="inlineStr">
@@ -7614,7 +7614,7 @@
           <t>Consumer Discretionary</t>
         </is>
       </c>
-      <c r="AB21" s="2" t="n">
+      <c r="AB21" t="n">
         <v>16727</v>
       </c>
       <c r="AC21" s="2" t="n">
@@ -7640,13 +7640,13 @@
           <t>Mar 2024</t>
         </is>
       </c>
-      <c r="D22" s="2" t="n">
+      <c r="D22" t="n">
         <v>8.449999999999999</v>
       </c>
-      <c r="E22" s="2" t="n">
+      <c r="E22" t="n">
         <v>22.02</v>
       </c>
-      <c r="F22" s="2" t="n">
+      <c r="F22" s="3" t="n">
         <v>8.369999999999999</v>
       </c>
       <c r="G22" s="2" t="n">
@@ -7658,55 +7658,55 @@
       <c r="I22" s="2" t="n">
         <v>19.83</v>
       </c>
-      <c r="J22" s="2" t="n">
+      <c r="J22" t="n">
         <v>0.73</v>
       </c>
       <c r="K22" s="2" t="n">
         <v>1929</v>
       </c>
-      <c r="L22" s="2" t="n">
+      <c r="L22" t="n">
         <v>6.91</v>
       </c>
-      <c r="M22" s="2" t="n">
+      <c r="M22" t="n">
         <v>480</v>
       </c>
-      <c r="N22" s="2" t="n">
+      <c r="N22" t="n">
         <v>575.08</v>
       </c>
-      <c r="O22" s="2" t="n">
+      <c r="O22" t="n">
         <v>16</v>
       </c>
-      <c r="P22" s="2" t="n">
+      <c r="P22" t="n">
         <v>1656</v>
       </c>
-      <c r="Q22" s="2" t="n">
+      <c r="Q22" t="n">
         <v>3347</v>
       </c>
-      <c r="R22" s="2" t="n">
+      <c r="R22" s="3" t="n">
         <v>10.33</v>
       </c>
-      <c r="S22" s="2" t="n">
+      <c r="S22" s="3" t="n">
         <v>11.29</v>
       </c>
-      <c r="T22" s="2" t="n">
+      <c r="T22" t="n">
         <v>10.68</v>
       </c>
-      <c r="U22" s="2" t="n">
+      <c r="U22" t="n">
         <v>14.81</v>
       </c>
-      <c r="V22" s="2" t="n">
+      <c r="V22" t="n">
         <v>1</v>
       </c>
-      <c r="W22" s="2" t="n">
+      <c r="W22" t="n">
         <v>2</v>
       </c>
-      <c r="X22" s="2" t="n">
+      <c r="X22" s="3" t="n">
         <v>5.08</v>
       </c>
-      <c r="Y22" s="2" t="n">
+      <c r="Y22" s="3" t="n">
         <v>4.24</v>
       </c>
-      <c r="Z22" s="2" t="n">
+      <c r="Z22" t="n">
         <v>0.66</v>
       </c>
       <c r="AA22" t="inlineStr">
@@ -7714,7 +7714,7 @@
           <t>Materials</t>
         </is>
       </c>
-      <c r="AB22" s="2" t="n">
+      <c r="AB22" t="n">
         <v>20521</v>
       </c>
       <c r="AC22" s="2" t="n">
@@ -7740,13 +7740,13 @@
           <t>Mar 2024</t>
         </is>
       </c>
-      <c r="D23" s="2" t="n">
+      <c r="D23" t="n">
         <v>4.61</v>
       </c>
-      <c r="E23" s="2" t="n">
+      <c r="E23" t="n">
         <v>8.67</v>
       </c>
-      <c r="F23" s="2" t="n">
+      <c r="F23" s="3" t="n">
         <v>8.99</v>
       </c>
       <c r="G23" s="2" t="n">
@@ -7755,58 +7755,58 @@
       <c r="H23" s="2" t="n">
         <v>0.1</v>
       </c>
-      <c r="I23" s="2" t="n">
+      <c r="I23" s="3" t="n">
         <v>13.86</v>
       </c>
-      <c r="J23" s="2" t="n">
+      <c r="J23" t="n">
         <v>1.21</v>
       </c>
       <c r="K23" s="2" t="n">
         <v>5058</v>
       </c>
-      <c r="L23" s="2" t="n">
+      <c r="L23" t="n">
         <v>2.53</v>
       </c>
-      <c r="M23" s="2" t="n">
+      <c r="M23" t="n">
         <v>24</v>
       </c>
-      <c r="N23" s="2" t="n">
+      <c r="N23" t="n">
         <v>60.47</v>
       </c>
-      <c r="O23" s="2" t="n">
+      <c r="O23" t="n">
         <v>150</v>
       </c>
-      <c r="P23" s="2" t="n">
+      <c r="P23" t="n">
         <v>2537</v>
       </c>
-      <c r="Q23" s="2" t="n">
+      <c r="Q23" t="n">
         <v>6376</v>
       </c>
-      <c r="R23" s="2" t="n">
+      <c r="R23" s="3" t="n">
         <v>8.4</v>
       </c>
       <c r="S23" s="3" t="n">
         <v>-10.99</v>
       </c>
-      <c r="T23" s="3" t="n">
+      <c r="T23" t="n">
         <v>-11.42</v>
       </c>
-      <c r="U23" s="2" t="n">
+      <c r="U23" t="n">
         <v>11.16</v>
       </c>
-      <c r="V23" s="2" t="n">
+      <c r="V23" t="n">
         <v>1</v>
       </c>
-      <c r="W23" s="2" t="n">
+      <c r="W23" t="n">
         <v>3</v>
       </c>
-      <c r="X23" s="2" t="n">
+      <c r="X23" s="3" t="n">
         <v>242.19</v>
       </c>
-      <c r="Y23" s="2" t="n">
+      <c r="Y23" s="3" t="n">
         <v>96.12</v>
       </c>
-      <c r="Z23" s="2" t="n">
+      <c r="Z23" t="n">
         <v>2.58</v>
       </c>
       <c r="AA23" t="inlineStr">
@@ -7814,13 +7814,13 @@
           <t>Information Technology</t>
         </is>
       </c>
-      <c r="AB23" s="2" t="n">
+      <c r="AB23" t="n">
         <v>51996</v>
       </c>
       <c r="AC23" s="2" t="n">
         <v>29.72</v>
       </c>
-      <c r="AD23" s="2" t="n">
+      <c r="AD23" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8038,10 +8038,10 @@
           <t>Mar 2024</t>
         </is>
       </c>
-      <c r="D2" s="2" t="n">
+      <c r="D2" t="n">
         <v>16.12</v>
       </c>
-      <c r="E2" s="2" t="n">
+      <c r="E2" t="n">
         <v>23.83</v>
       </c>
       <c r="F2" s="2" t="n">
@@ -8056,55 +8056,55 @@
       <c r="I2" s="2" t="n">
         <v>41.19</v>
       </c>
-      <c r="J2" s="2" t="n">
+      <c r="J2" t="n">
         <v>2.32</v>
       </c>
       <c r="K2" s="2" t="n">
         <v>2938</v>
       </c>
-      <c r="L2" s="2" t="n">
+      <c r="L2" t="n">
         <v>5.07</v>
       </c>
-      <c r="M2" s="2" t="n">
+      <c r="M2" t="n">
         <v>41</v>
       </c>
-      <c r="N2" s="2" t="n">
+      <c r="N2" t="n">
         <v>34.79</v>
       </c>
-      <c r="O2" s="2" t="n">
+      <c r="O2" t="n">
         <v>79</v>
       </c>
-      <c r="P2" s="2" t="n">
+      <c r="P2" t="n">
         <v>345</v>
       </c>
-      <c r="Q2" s="2" t="n">
+      <c r="Q2" t="n">
         <v>4175</v>
       </c>
-      <c r="R2" s="2" t="n">
+      <c r="R2" s="3" t="n">
         <v>14.55</v>
       </c>
-      <c r="S2" s="2" t="n">
+      <c r="S2" s="3" t="n">
         <v>14.85</v>
       </c>
-      <c r="T2" s="2" t="n">
+      <c r="T2" t="n">
         <v>15.44</v>
       </c>
-      <c r="U2" s="2" t="n">
+      <c r="U2" t="n">
         <v>18.28</v>
       </c>
-      <c r="V2" s="2" t="n">
+      <c r="V2" t="n">
         <v>0</v>
       </c>
-      <c r="W2" s="2" t="n">
+      <c r="W2" t="n">
         <v>5</v>
       </c>
-      <c r="X2" s="2" t="n">
+      <c r="X2" s="3" t="n">
         <v>25.17</v>
       </c>
-      <c r="Y2" s="2" t="n">
+      <c r="Y2" s="3" t="n">
         <v>29.66</v>
       </c>
-      <c r="Z2" s="2" t="n">
+      <c r="Z2" t="n">
         <v>7.66</v>
       </c>
       <c r="AA2" t="inlineStr">
@@ -8112,7 +8112,7 @@
           <t>Consumer Staples</t>
         </is>
       </c>
-      <c r="AB2" s="2" t="n">
+      <c r="AB2" t="n">
         <v>24394</v>
       </c>
       <c r="AC2" s="2" t="n">
@@ -8138,10 +8138,10 @@
           <t>Mar 2024</t>
         </is>
       </c>
-      <c r="D3" s="2" t="n">
+      <c r="D3" t="n">
         <v>4.84</v>
       </c>
-      <c r="E3" s="2" t="n">
+      <c r="E3" t="n">
         <v>3.87</v>
       </c>
       <c r="F3" s="2" t="n">
@@ -8156,55 +8156,55 @@
       <c r="I3" s="2" t="n">
         <v>371.94</v>
       </c>
-      <c r="J3" s="2" t="n">
+      <c r="J3" t="n">
         <v>0.16</v>
       </c>
       <c r="K3" s="2" t="n">
         <v>853</v>
       </c>
-      <c r="L3" s="2" t="n">
+      <c r="L3" t="n">
         <v>2.99</v>
       </c>
-      <c r="M3" s="2" t="n">
+      <c r="M3" t="n">
         <v>66</v>
       </c>
-      <c r="N3" s="2" t="n">
+      <c r="N3" t="n">
         <v>13.08</v>
       </c>
-      <c r="O3" s="2" t="n">
+      <c r="O3" t="n">
         <v>15</v>
       </c>
-      <c r="P3" s="2" t="n">
+      <c r="P3" t="n">
         <v>0</v>
       </c>
-      <c r="Q3" s="2" t="n">
+      <c r="Q3" t="n">
         <v>26122</v>
       </c>
-      <c r="R3" s="2" t="n">
+      <c r="R3" s="3" t="n">
         <v>8.16</v>
       </c>
       <c r="S3" s="2" t="n">
         <v>73.18000000000001</v>
       </c>
-      <c r="T3" s="3" t="n">
+      <c r="T3" t="n">
         <v/>
       </c>
-      <c r="U3" s="2" t="n">
+      <c r="U3" t="n">
         <v>6.98</v>
       </c>
-      <c r="V3" s="2" t="n">
+      <c r="V3" t="n">
         <v>0</v>
       </c>
-      <c r="W3" s="2" t="n">
+      <c r="W3" t="n">
         <v>3</v>
       </c>
-      <c r="X3" s="2" t="n">
+      <c r="X3" s="3" t="n">
         <v>4.8</v>
       </c>
-      <c r="Y3" s="2" t="n">
+      <c r="Y3" s="3" t="n">
         <v>24.2</v>
       </c>
-      <c r="Z3" s="2" t="n">
+      <c r="Z3" t="n">
         <v>4.74</v>
       </c>
       <c r="AA3" t="inlineStr">
@@ -8212,7 +8212,7 @@
           <t>Financials</t>
         </is>
       </c>
-      <c r="AB3" s="2" t="n">
+      <c r="AB3" t="n">
         <v>845966</v>
       </c>
       <c r="AC3" s="2" t="n">
@@ -8238,10 +8238,10 @@
           <t>Mar 2024</t>
         </is>
       </c>
-      <c r="D4" s="2" t="n">
+      <c r="D4" t="n">
         <v>14.29</v>
       </c>
-      <c r="E4" s="2" t="n">
+      <c r="E4" t="n">
         <v>22.02</v>
       </c>
       <c r="F4" s="2" t="n">
@@ -8256,55 +8256,55 @@
       <c r="I4" s="2" t="n">
         <v>46.46</v>
       </c>
-      <c r="J4" s="2" t="n">
+      <c r="J4" t="n">
         <v>1.11</v>
       </c>
       <c r="K4" s="2" t="n">
         <v>15840</v>
       </c>
-      <c r="L4" s="2" t="n">
+      <c r="L4" t="n">
         <v>6.01</v>
       </c>
-      <c r="M4" s="2" t="n">
+      <c r="M4" t="n">
         <v>58</v>
       </c>
-      <c r="N4" s="2" t="n">
+      <c r="N4" t="n">
         <v>125.71</v>
       </c>
-      <c r="O4" s="2" t="n">
+      <c r="O4" t="n">
         <v>90</v>
       </c>
-      <c r="P4" s="2" t="n">
+      <c r="P4" t="n">
         <v>5758</v>
       </c>
-      <c r="Q4" s="2" t="n">
+      <c r="Q4" t="n">
         <v>22448</v>
       </c>
-      <c r="R4" s="2" t="n">
+      <c r="R4" s="3" t="n">
         <v>12.71</v>
       </c>
-      <c r="S4" s="2" t="n">
+      <c r="S4" s="3" t="n">
         <v>9.19</v>
       </c>
-      <c r="T4" s="2" t="n">
+      <c r="T4" t="n">
         <v>9.41</v>
       </c>
-      <c r="U4" s="2" t="n">
+      <c r="U4" t="n">
         <v>13.4</v>
       </c>
-      <c r="V4" s="2" t="n">
+      <c r="V4" t="n">
         <v>0</v>
       </c>
-      <c r="W4" s="2" t="n">
+      <c r="W4" t="n">
         <v>5</v>
       </c>
-      <c r="X4" s="2" t="n">
+      <c r="X4" s="3" t="n">
         <v>16.63</v>
       </c>
-      <c r="Y4" s="2" t="n">
+      <c r="Y4" s="3" t="n">
         <v>7.67</v>
       </c>
-      <c r="Z4" s="2" t="n">
+      <c r="Z4" t="n">
         <v>9.33</v>
       </c>
       <c r="AA4" t="inlineStr">
@@ -8312,7 +8312,7 @@
           <t>Information Technology</t>
         </is>
       </c>
-      <c r="AB4" s="2" t="n">
+      <c r="AB4" t="n">
         <v>109913</v>
       </c>
       <c r="AC4" s="2" t="n">
@@ -8338,10 +8338,10 @@
           <t>Mar 2024</t>
         </is>
       </c>
-      <c r="D5" s="2" t="n">
+      <c r="D5" t="n">
         <v>16.61</v>
       </c>
-      <c r="E5" s="2" t="n">
+      <c r="E5" t="n">
         <v>76.31999999999999</v>
       </c>
       <c r="F5" s="2" t="n">
@@ -8356,55 +8356,55 @@
       <c r="I5" s="2" t="n">
         <v>57.85</v>
       </c>
-      <c r="J5" s="2" t="n">
+      <c r="J5" t="n">
         <v>0.79</v>
       </c>
       <c r="K5" s="2" t="n">
         <v>10145</v>
       </c>
-      <c r="L5" s="2" t="n">
+      <c r="L5" t="n">
         <v>8.6</v>
       </c>
-      <c r="M5" s="2" t="n">
+      <c r="M5" t="n">
         <v>44</v>
       </c>
-      <c r="N5" s="2" t="n">
+      <c r="N5" t="n">
         <v>217.95</v>
       </c>
-      <c r="O5" s="2" t="n">
+      <c r="O5" t="n">
         <v>96</v>
       </c>
-      <c r="P5" s="2" t="n">
+      <c r="P5" t="n">
         <v>1484</v>
       </c>
-      <c r="Q5" s="2" t="n">
+      <c r="Q5" t="n">
         <v>15469</v>
       </c>
-      <c r="R5" s="2" t="n">
+      <c r="R5" s="3" t="n">
         <v>9.5</v>
       </c>
-      <c r="S5" s="2" t="n">
+      <c r="S5" s="3" t="n">
         <v>11.15</v>
       </c>
-      <c r="T5" s="2" t="n">
+      <c r="T5" t="n">
         <v>9.460000000000001</v>
       </c>
-      <c r="U5" s="2" t="n">
+      <c r="U5" t="n">
         <v>9.59</v>
       </c>
-      <c r="V5" s="2" t="n">
+      <c r="V5" t="n">
         <v>0</v>
       </c>
-      <c r="W5" s="2" t="n">
+      <c r="W5" t="n">
         <v>4</v>
       </c>
-      <c r="X5" s="2" t="n">
+      <c r="X5" s="3" t="n">
         <v>6.94</v>
       </c>
-      <c r="Y5" s="2" t="n">
+      <c r="Y5" s="3" t="n">
         <v>1.4</v>
       </c>
-      <c r="Z5" s="2" t="n">
+      <c r="Z5" t="n">
         <v>31.42</v>
       </c>
       <c r="AA5" t="inlineStr">
@@ -8412,7 +8412,7 @@
           <t>Consumer Staples</t>
         </is>
       </c>
-      <c r="AB5" s="2" t="n">
+      <c r="AB5" t="n">
         <v>61896</v>
       </c>
       <c r="AC5" s="2" t="n">
@@ -8438,10 +8438,10 @@
           <t>Mar 2024</t>
         </is>
       </c>
-      <c r="D6" s="2" t="n">
+      <c r="D6" t="n">
         <v>5.56</v>
       </c>
-      <c r="E6" s="2" t="n">
+      <c r="E6" t="n">
         <v>9.74</v>
       </c>
       <c r="F6" s="2" t="n">
@@ -8453,58 +8453,58 @@
       <c r="H6" s="2" t="n">
         <v>0.72</v>
       </c>
-      <c r="I6" s="2" t="n">
+      <c r="I6" s="3" t="n">
         <v>10.28</v>
       </c>
-      <c r="J6" s="2" t="n">
+      <c r="J6" t="n">
         <v>1.61</v>
       </c>
       <c r="K6" s="2" t="n">
         <v>39635</v>
       </c>
-      <c r="L6" s="2" t="n">
+      <c r="L6" t="n">
         <v>4.05</v>
       </c>
-      <c r="M6" s="2" t="n">
+      <c r="M6" t="n">
         <v>30</v>
       </c>
-      <c r="N6" s="2" t="n">
+      <c r="N6" t="n">
         <v>13.32</v>
       </c>
-      <c r="O6" s="2" t="n">
+      <c r="O6" t="n">
         <v>40</v>
       </c>
-      <c r="P6" s="2" t="n">
+      <c r="P6" t="n">
         <v>132628</v>
       </c>
-      <c r="Q6" s="2" t="n">
+      <c r="Q6" t="n">
         <v>71099</v>
       </c>
-      <c r="R6" s="2" t="n">
+      <c r="R6" s="3" t="n">
         <v>8.01</v>
       </c>
       <c r="S6" s="2" t="n">
         <v>20.1</v>
       </c>
-      <c r="T6" s="2" t="n">
+      <c r="T6" t="n">
         <v>20.11</v>
       </c>
-      <c r="U6" s="2" t="n">
+      <c r="U6" t="n">
         <v>28.73</v>
       </c>
-      <c r="V6" s="2" t="n">
+      <c r="V6" t="n">
         <v>1</v>
       </c>
-      <c r="W6" s="2" t="n">
+      <c r="W6" t="n">
         <v>4</v>
       </c>
-      <c r="X6" s="2" t="n">
+      <c r="X6" s="3" t="n">
         <v>29.92</v>
       </c>
-      <c r="Y6" s="2" t="n">
+      <c r="Y6" s="3" t="n">
         <v>67.39</v>
       </c>
-      <c r="Z6" s="2" t="n">
+      <c r="Z6" t="n">
         <v>4.46</v>
       </c>
       <c r="AA6" t="inlineStr">
@@ -8512,7 +8512,7 @@
           <t>Energy</t>
         </is>
       </c>
-      <c r="AB6" s="2" t="n">
+      <c r="AB6" t="n">
         <v>776352</v>
       </c>
       <c r="AC6" s="2" t="n">
@@ -8538,10 +8538,10 @@
           <t>Mar 2024</t>
         </is>
       </c>
-      <c r="D7" s="2" t="n">
+      <c r="D7" t="n">
         <v>12.73</v>
       </c>
-      <c r="E7" s="2" t="n">
+      <c r="E7" t="n">
         <v>18.89</v>
       </c>
       <c r="F7" s="2" t="n">
@@ -8556,55 +8556,55 @@
       <c r="I7" s="2" t="n">
         <v>20.6</v>
       </c>
-      <c r="J7" s="2" t="n">
+      <c r="J7" t="n">
         <v>1.85</v>
       </c>
       <c r="K7" s="2" t="n">
         <v>3050</v>
       </c>
-      <c r="L7" s="2" t="n">
+      <c r="L7" t="n">
         <v>2.84</v>
       </c>
-      <c r="M7" s="2" t="n">
+      <c r="M7" t="n">
         <v>89</v>
       </c>
-      <c r="N7" s="2" t="n">
+      <c r="N7" t="n">
         <v>164.21</v>
       </c>
-      <c r="O7" s="2" t="n">
+      <c r="O7" t="n">
         <v>83</v>
       </c>
-      <c r="P7" s="2" t="n">
+      <c r="P7" t="n">
         <v>2065</v>
       </c>
-      <c r="Q7" s="2" t="n">
+      <c r="Q7" t="n">
         <v>2573</v>
       </c>
-      <c r="R7" s="2" t="n">
+      <c r="R7" s="3" t="n">
         <v>8.69</v>
       </c>
-      <c r="S7" s="2" t="n">
+      <c r="S7" s="3" t="n">
         <v>13.06</v>
       </c>
-      <c r="T7" s="2" t="n">
+      <c r="T7" t="n">
         <v>13.14</v>
       </c>
-      <c r="U7" s="2" t="n">
+      <c r="U7" t="n">
         <v>8.48</v>
       </c>
-      <c r="V7" s="2" t="n">
+      <c r="V7" t="n">
         <v>1</v>
       </c>
-      <c r="W7" s="2" t="n">
+      <c r="W7" t="n">
         <v>5</v>
       </c>
-      <c r="X7" s="2" t="n">
+      <c r="X7" s="3" t="n">
         <v>3.97</v>
       </c>
-      <c r="Y7" s="2" t="n">
+      <c r="Y7" s="3" t="n">
         <v>2.15</v>
       </c>
-      <c r="Z7" s="2" t="n">
+      <c r="Z7" t="n">
         <v>23.48</v>
       </c>
       <c r="AA7" t="inlineStr">
@@ -8612,7 +8612,7 @@
           <t>Consumer Staples</t>
         </is>
       </c>
-      <c r="AB7" s="2" t="n">
+      <c r="AB7" t="n">
         <v>16769</v>
       </c>
       <c r="AC7" s="2" t="n">
@@ -8638,10 +8638,10 @@
           <t>Mar 2024</t>
         </is>
       </c>
-      <c r="D8" s="2" t="n">
+      <c r="D8" t="n">
         <v>24.2</v>
       </c>
-      <c r="E8" s="2" t="n">
+      <c r="E8" t="n">
         <v>26.18</v>
       </c>
       <c r="F8" s="2" t="n">
@@ -8656,55 +8656,55 @@
       <c r="I8" s="2" t="n">
         <v>114.71</v>
       </c>
-      <c r="J8" s="2" t="n">
+      <c r="J8" t="n">
         <v>0.72</v>
       </c>
       <c r="K8" s="2" t="n">
         <v>890</v>
       </c>
-      <c r="L8" s="2" t="n">
+      <c r="L8" t="n">
         <v>17.14</v>
       </c>
-      <c r="M8" s="2" t="n">
+      <c r="M8" t="n">
         <v>146</v>
       </c>
-      <c r="N8" s="2" t="n">
+      <c r="N8" t="n">
         <v>668.33</v>
       </c>
-      <c r="O8" s="2" t="n">
+      <c r="O8" t="n">
         <v>35</v>
       </c>
-      <c r="P8" s="2" t="n">
+      <c r="P8" t="n">
         <v>419</v>
       </c>
-      <c r="Q8" s="2" t="n">
+      <c r="Q8" t="n">
         <v>3724</v>
       </c>
-      <c r="R8" s="2" t="n">
+      <c r="R8" s="3" t="n">
         <v>11.04</v>
       </c>
-      <c r="S8" s="2" t="n">
+      <c r="S8" s="3" t="n">
         <v>12.68</v>
       </c>
-      <c r="T8" s="2" t="n">
+      <c r="T8" t="n">
         <v>12.51</v>
       </c>
-      <c r="U8" s="2" t="n">
+      <c r="U8" t="n">
         <v>23.78</v>
       </c>
-      <c r="V8" s="2" t="n">
+      <c r="V8" t="n">
         <v>0</v>
       </c>
-      <c r="W8" s="2" t="n">
+      <c r="W8" t="n">
         <v>4</v>
       </c>
-      <c r="X8" s="2" t="n">
+      <c r="X8" s="3" t="n">
         <v>11.22</v>
       </c>
-      <c r="Y8" s="2" t="n">
+      <c r="Y8" s="3" t="n">
         <v>2.45</v>
       </c>
-      <c r="Z8" s="2" t="n">
+      <c r="Z8" t="n">
         <v>2.14</v>
       </c>
       <c r="AA8" t="inlineStr">
@@ -8712,7 +8712,7 @@
           <t>Consumer Discretionary</t>
         </is>
       </c>
-      <c r="AB8" s="2" t="n">
+      <c r="AB8" t="n">
         <v>16536</v>
       </c>
       <c r="AC8" s="2" t="n">
@@ -8738,10 +8738,10 @@
           <t>Mar 2024</t>
         </is>
       </c>
-      <c r="D9" s="2" t="n">
+      <c r="D9" t="n">
         <v>15.44</v>
       </c>
-      <c r="E9" s="2" t="n">
+      <c r="E9" t="n">
         <v>31.39</v>
       </c>
       <c r="F9" s="2" t="n">
@@ -8753,58 +8753,58 @@
       <c r="H9" s="2" t="n">
         <v>0.59</v>
       </c>
-      <c r="I9" s="2" t="n">
+      <c r="I9" s="3" t="n">
         <v>9.93</v>
       </c>
-      <c r="J9" s="2" t="n">
+      <c r="J9" t="n">
         <v>0.74</v>
       </c>
       <c r="K9" s="2" t="n">
         <v>3106</v>
       </c>
-      <c r="L9" s="2" t="n">
+      <c r="L9" t="n">
         <v>1.49</v>
       </c>
-      <c r="M9" s="2" t="n">
+      <c r="M9" t="n">
         <v>49</v>
       </c>
-      <c r="N9" s="2" t="n">
+      <c r="N9" t="n">
         <v>40.57</v>
       </c>
-      <c r="O9" s="2" t="n">
+      <c r="O9" t="n">
         <v>57</v>
       </c>
-      <c r="P9" s="2" t="n">
+      <c r="P9" t="n">
         <v>4022</v>
       </c>
-      <c r="Q9" s="2" t="n">
+      <c r="Q9" t="n">
         <v>3266</v>
       </c>
-      <c r="R9" s="2" t="n">
+      <c r="R9" s="3" t="n">
         <v>6.93</v>
       </c>
       <c r="S9" s="2" t="n">
         <v>30.59</v>
       </c>
-      <c r="T9" s="2" t="n">
+      <c r="T9" t="n">
         <v>30.39</v>
       </c>
-      <c r="U9" s="2" t="n">
+      <c r="U9" t="n">
         <v>10.25</v>
       </c>
-      <c r="V9" s="2" t="n">
+      <c r="V9" t="n">
         <v>1</v>
       </c>
-      <c r="W9" s="2" t="n">
+      <c r="W9" t="n">
         <v>4</v>
       </c>
-      <c r="X9" s="2" t="n">
+      <c r="X9" s="3" t="n">
         <v>45.88</v>
       </c>
-      <c r="Y9" s="2" t="n">
+      <c r="Y9" s="3" t="n">
         <v>55.42</v>
       </c>
-      <c r="Z9" s="2" t="n">
+      <c r="Z9" t="n">
         <v>2.54</v>
       </c>
       <c r="AA9" t="inlineStr">
@@ -8812,7 +8812,7 @@
           <t>Healthcare</t>
         </is>
       </c>
-      <c r="AB9" s="2" t="n">
+      <c r="AB9" t="n">
         <v>10728</v>
       </c>
       <c r="AC9" s="2" t="n">
@@ -8838,73 +8838,73 @@
           <t>Mar 2024</t>
         </is>
       </c>
-      <c r="D10" s="2" t="n">
+      <c r="D10" t="n">
         <v>11.95</v>
       </c>
-      <c r="E10" s="2" t="n">
+      <c r="E10" t="n">
         <v>28.83</v>
       </c>
-      <c r="F10" s="2" t="n">
+      <c r="F10" s="3" t="n">
         <v>13.27</v>
       </c>
-      <c r="G10" s="2" t="n">
+      <c r="G10" s="3" t="n">
         <v>12.93</v>
       </c>
-      <c r="H10" s="2" t="n">
+      <c r="H10" s="3" t="n">
         <v>1.48</v>
       </c>
-      <c r="I10" s="2" t="n">
+      <c r="I10" s="3" t="n">
         <v>4.6</v>
       </c>
-      <c r="J10" s="2" t="n">
+      <c r="J10" t="n">
         <v>0.37</v>
       </c>
       <c r="K10" s="2" t="n">
         <v>8644</v>
       </c>
-      <c r="L10" s="2" t="n">
+      <c r="L10" t="n">
         <v>18.01</v>
       </c>
-      <c r="M10" s="2" t="n">
+      <c r="M10" t="n">
         <v>21</v>
       </c>
-      <c r="N10" s="2" t="n">
+      <c r="N10" t="n">
         <v>16.57</v>
       </c>
-      <c r="O10" s="2" t="n">
+      <c r="O10" t="n">
         <v>36</v>
       </c>
-      <c r="P10" s="2" t="n">
+      <c r="P10" t="n">
         <v>237131</v>
       </c>
-      <c r="Q10" s="2" t="n">
+      <c r="Q10" t="n">
         <v>40785</v>
       </c>
-      <c r="R10" s="2" t="n">
+      <c r="R10" s="3" t="n">
         <v>12.22</v>
       </c>
-      <c r="S10" s="2" t="n">
+      <c r="S10" s="3" t="n">
         <v>8.74</v>
       </c>
-      <c r="T10" s="2" t="n">
+      <c r="T10" t="n">
         <v>8.449999999999999</v>
       </c>
-      <c r="U10" s="2" t="n">
+      <c r="U10" t="n">
         <v>16.97</v>
       </c>
-      <c r="V10" s="2" t="n">
+      <c r="V10" t="n">
         <v>0</v>
       </c>
-      <c r="W10" s="2" t="n">
+      <c r="W10" t="n">
         <v>2</v>
       </c>
-      <c r="X10" s="2" t="n">
+      <c r="X10" s="3" t="n">
         <v>23.42</v>
       </c>
-      <c r="Y10" s="2" t="n">
+      <c r="Y10" s="3" t="n">
         <v>29.68</v>
       </c>
-      <c r="Z10" s="2" t="n">
+      <c r="Z10" t="n">
         <v>7.32</v>
       </c>
       <c r="AA10" t="inlineStr">
@@ -8912,7 +8912,7 @@
           <t>Energy</t>
         </is>
       </c>
-      <c r="AB10" s="2" t="n">
+      <c r="AB10" t="n">
         <v>178501</v>
       </c>
       <c r="AC10" s="2" t="n">
@@ -8938,10 +8938,10 @@
           <t>Mar 2024</t>
         </is>
       </c>
-      <c r="D11" s="2" t="n">
+      <c r="D11" t="n">
         <v>9.9</v>
       </c>
-      <c r="E11" s="2" t="n">
+      <c r="E11" t="n">
         <v>86.15000000000001</v>
       </c>
       <c r="F11" s="2" t="n">
@@ -8956,55 +8956,55 @@
       <c r="I11" s="2" t="n">
         <v>47.27</v>
       </c>
-      <c r="J11" s="2" t="n">
+      <c r="J11" t="n">
         <v>1.44</v>
       </c>
       <c r="K11" s="2" t="n">
         <v>3095</v>
       </c>
-      <c r="L11" s="2" t="n">
+      <c r="L11" t="n">
         <v>4.84</v>
       </c>
-      <c r="M11" s="2" t="n">
+      <c r="M11" t="n">
         <v>187</v>
       </c>
-      <c r="N11" s="2" t="n">
+      <c r="N11" t="n">
         <v>442.48</v>
       </c>
-      <c r="O11" s="2" t="n">
+      <c r="O11" t="n">
         <v>75</v>
       </c>
-      <c r="P11" s="2" t="n">
+      <c r="P11" t="n">
         <v>606</v>
       </c>
-      <c r="Q11" s="2" t="n">
+      <c r="Q11" t="n">
         <v>4923</v>
       </c>
-      <c r="R11" s="2" t="n">
+      <c r="R11" s="3" t="n">
         <v>2.15</v>
       </c>
-      <c r="S11" s="2" t="n">
+      <c r="S11" s="3" t="n">
         <v>1.54</v>
       </c>
-      <c r="T11" s="2" t="n">
+      <c r="T11" t="n">
         <v>1.69</v>
       </c>
-      <c r="U11" s="2" t="n">
+      <c r="U11" t="n">
         <v>6.87</v>
       </c>
-      <c r="V11" s="2" t="n">
+      <c r="V11" t="n">
         <v>0</v>
       </c>
-      <c r="W11" s="2" t="n">
+      <c r="W11" t="n">
         <v>4</v>
       </c>
-      <c r="X11" s="2" t="n">
+      <c r="X11" s="3" t="n">
         <v>6.43</v>
       </c>
-      <c r="Y11" s="2" t="n">
+      <c r="Y11" s="3" t="n">
         <v>2.72</v>
       </c>
-      <c r="Z11" s="2" t="n">
+      <c r="Z11" t="n">
         <v>6.24</v>
       </c>
       <c r="AA11" t="inlineStr">
@@ -9012,7 +9012,7 @@
           <t>Consumer Discretionary</t>
         </is>
       </c>
-      <c r="AB11" s="2" t="n">
+      <c r="AB11" t="n">
         <v>37789</v>
       </c>
       <c r="AC11" s="2" t="n">
@@ -9038,10 +9038,10 @@
           <t>Mar 2024</t>
         </is>
       </c>
-      <c r="D12" s="2" t="n">
+      <c r="D12" t="n">
         <v>14.11</v>
       </c>
-      <c r="E12" s="2" t="n">
+      <c r="E12" t="n">
         <v>21.87</v>
       </c>
       <c r="F12" s="2" t="n">
@@ -9056,55 +9056,55 @@
       <c r="I12" s="2" t="n">
         <v>54.33</v>
       </c>
-      <c r="J12" s="2" t="n">
+      <c r="J12" t="n">
         <v>1.03</v>
       </c>
       <c r="K12" s="2" t="n">
         <v>955</v>
       </c>
-      <c r="L12" s="2" t="n">
+      <c r="L12" t="n">
         <v>14.29</v>
       </c>
-      <c r="M12" s="2" t="n">
+      <c r="M12" t="n">
         <v>34</v>
       </c>
-      <c r="N12" s="2" t="n">
+      <c r="N12" t="n">
         <v>164.84</v>
       </c>
-      <c r="O12" s="2" t="n">
+      <c r="O12" t="n">
         <v>47</v>
       </c>
-      <c r="P12" s="2" t="n">
+      <c r="P12" t="n">
         <v>382</v>
       </c>
-      <c r="Q12" s="2" t="n">
+      <c r="Q12" t="n">
         <v>2724</v>
       </c>
-      <c r="R12" s="2" t="n">
+      <c r="R12" s="3" t="n">
         <v>11.84</v>
       </c>
-      <c r="S12" s="2" t="n">
+      <c r="S12" s="3" t="n">
         <v>13.49</v>
       </c>
-      <c r="T12" s="2" t="n">
+      <c r="T12" t="n">
         <v>13.56</v>
       </c>
-      <c r="U12" s="2" t="n">
+      <c r="U12" t="n">
         <v>19.3</v>
       </c>
-      <c r="V12" s="2" t="n">
+      <c r="V12" t="n">
         <v>1</v>
       </c>
-      <c r="W12" s="2" t="n">
+      <c r="W12" t="n">
         <v>5</v>
       </c>
-      <c r="X12" s="2" t="n">
+      <c r="X12" s="3" t="n">
         <v>20.14</v>
       </c>
-      <c r="Y12" s="2" t="n">
+      <c r="Y12" s="3" t="n">
         <v>4.15</v>
       </c>
-      <c r="Z12" s="2" t="n">
+      <c r="Z12" t="n">
         <v>6.86</v>
       </c>
       <c r="AA12" t="inlineStr">
@@ -9112,7 +9112,7 @@
           <t>Materials</t>
         </is>
       </c>
-      <c r="AB12" s="2" t="n">
+      <c r="AB12" t="n">
         <v>12383</v>
       </c>
       <c r="AC12" s="2" t="n">
@@ -9138,16 +9138,16 @@
           <t>Mar 2024</t>
         </is>
       </c>
-      <c r="D13" s="2" t="n">
+      <c r="D13" t="n">
         <v>7.43</v>
       </c>
-      <c r="E13" s="2" t="n">
+      <c r="E13" t="n">
         <v>10.74</v>
       </c>
-      <c r="F13" s="2" t="n">
+      <c r="F13" s="3" t="n">
         <v>12.86</v>
       </c>
-      <c r="G13" s="2" t="n">
+      <c r="G13" s="3" t="n">
         <v>14.49</v>
       </c>
       <c r="H13" s="2" t="n">
@@ -9156,55 +9156,55 @@
       <c r="I13" s="2" t="n">
         <v>23.62</v>
       </c>
-      <c r="J13" s="2" t="n">
+      <c r="J13" t="n">
         <v>1.07</v>
       </c>
       <c r="K13" s="2" t="n">
         <v>4360</v>
       </c>
-      <c r="L13" s="2" t="n">
+      <c r="L13" t="n">
         <v>6.17</v>
       </c>
-      <c r="M13" s="2" t="n">
+      <c r="M13" t="n">
         <v>15</v>
       </c>
-      <c r="N13" s="2" t="n">
+      <c r="N13" t="n">
         <v>11.71</v>
       </c>
-      <c r="O13" s="2" t="n">
+      <c r="O13" t="n">
         <v>37</v>
       </c>
-      <c r="P13" s="2" t="n">
+      <c r="P13" t="n">
         <v>21794</v>
       </c>
-      <c r="Q13" s="2" t="n">
+      <c r="Q13" t="n">
         <v>12586</v>
       </c>
-      <c r="R13" s="2" t="n">
+      <c r="R13" s="3" t="n">
         <v>11.83</v>
       </c>
-      <c r="S13" s="2" t="n">
+      <c r="S13" s="3" t="n">
         <v>8.609999999999999</v>
       </c>
-      <c r="T13" s="2" t="n">
+      <c r="T13" t="n">
         <v>8.449999999999999</v>
       </c>
-      <c r="U13" s="2" t="n">
+      <c r="U13" t="n">
         <v>32.42</v>
       </c>
-      <c r="V13" s="2" t="n">
+      <c r="V13" t="n">
         <v>0</v>
       </c>
-      <c r="W13" s="2" t="n">
+      <c r="W13" t="n">
         <v>3</v>
       </c>
-      <c r="X13" s="2" t="n">
+      <c r="X13" s="3" t="n">
         <v>25.58</v>
       </c>
-      <c r="Y13" s="2" t="n">
+      <c r="Y13" s="3" t="n">
         <v>32.76</v>
       </c>
-      <c r="Z13" s="2" t="n">
+      <c r="Z13" t="n">
         <v>9.640000000000001</v>
       </c>
       <c r="AA13" t="inlineStr">
@@ -9212,7 +9212,7 @@
           <t>Energy</t>
         </is>
       </c>
-      <c r="AB13" s="2" t="n">
+      <c r="AB13" t="n">
         <v>133228</v>
       </c>
       <c r="AC13" s="2" t="n">
@@ -9238,10 +9238,10 @@
           <t>Mar 2024</t>
         </is>
       </c>
-      <c r="D14" s="2" t="n">
+      <c r="D14" t="n">
         <v>6.84</v>
       </c>
-      <c r="E14" s="2" t="n">
+      <c r="E14" t="n">
         <v>10.12</v>
       </c>
       <c r="F14" s="2" t="n">
@@ -9256,55 +9256,55 @@
       <c r="I14" s="2" t="n">
         <v>25.36</v>
       </c>
-      <c r="J14" s="2" t="n">
+      <c r="J14" t="n">
         <v>1.5</v>
       </c>
       <c r="K14" s="2" t="n">
         <v>335</v>
       </c>
-      <c r="L14" s="2" t="n">
+      <c r="L14" t="n">
         <v>8.699999999999999</v>
       </c>
-      <c r="M14" s="2" t="n">
+      <c r="M14" t="n">
         <v>20</v>
       </c>
-      <c r="N14" s="2" t="n">
+      <c r="N14" t="n">
         <v>118.21</v>
       </c>
-      <c r="O14" s="2" t="n">
+      <c r="O14" t="n">
         <v>44</v>
       </c>
-      <c r="P14" s="2" t="n">
+      <c r="P14" t="n">
         <v>303</v>
       </c>
-      <c r="Q14" s="2" t="n">
+      <c r="Q14" t="n">
         <v>1953</v>
       </c>
-      <c r="R14" s="2" t="n">
+      <c r="R14" s="3" t="n">
         <v>13.04</v>
       </c>
-      <c r="S14" s="2" t="n">
+      <c r="S14" s="3" t="n">
         <v>10.03</v>
       </c>
-      <c r="T14" s="2" t="n">
+      <c r="T14" t="n">
         <v>9</v>
       </c>
-      <c r="U14" s="2" t="n">
+      <c r="U14" t="n">
         <v>21.14</v>
       </c>
-      <c r="V14" s="2" t="n">
+      <c r="V14" t="n">
         <v>0</v>
       </c>
-      <c r="W14" s="2" t="n">
+      <c r="W14" t="n">
         <v>4</v>
       </c>
-      <c r="X14" s="2" t="n">
+      <c r="X14" s="3" t="n">
         <v>106.42</v>
       </c>
-      <c r="Y14" s="2" t="n">
+      <c r="Y14" s="3" t="n">
         <v>18</v>
       </c>
-      <c r="Z14" s="2" t="n">
+      <c r="Z14" t="n">
         <v>2.07</v>
       </c>
       <c r="AA14" t="inlineStr">
@@ -9312,7 +9312,7 @@
           <t>Industrials</t>
         </is>
       </c>
-      <c r="AB14" s="2" t="n">
+      <c r="AB14" t="n">
         <v>18590</v>
       </c>
       <c r="AC14" s="2" t="n">
@@ -9338,10 +9338,10 @@
           <t>Mar 2024</t>
         </is>
       </c>
-      <c r="D15" s="2" t="n">
+      <c r="D15" t="n">
         <v>14.6</v>
       </c>
-      <c r="E15" s="2" t="n">
+      <c r="E15" t="n">
         <v>19.35</v>
       </c>
       <c r="F15" s="2" t="n">
@@ -9356,55 +9356,55 @@
       <c r="I15" s="2" t="n">
         <v>23.24</v>
       </c>
-      <c r="J15" s="2" t="n">
+      <c r="J15" t="n">
         <v>0.82</v>
       </c>
       <c r="K15" s="2" t="n">
         <v>1042</v>
       </c>
-      <c r="L15" s="2" t="n">
+      <c r="L15" t="n">
         <v>7.83</v>
       </c>
-      <c r="M15" s="2" t="n">
+      <c r="M15" t="n">
         <v>10</v>
       </c>
-      <c r="N15" s="2" t="n">
+      <c r="N15" t="n">
         <v>55.74</v>
       </c>
-      <c r="O15" s="2" t="n">
+      <c r="O15" t="n">
         <v>53</v>
       </c>
-      <c r="P15" s="2" t="n">
+      <c r="P15" t="n">
         <v>1365</v>
       </c>
-      <c r="Q15" s="2" t="n">
+      <c r="Q15" t="n">
         <v>2013</v>
       </c>
-      <c r="R15" s="2" t="n">
+      <c r="R15" s="3" t="n">
         <v>7.81</v>
       </c>
-      <c r="S15" s="2" t="n">
+      <c r="S15" s="3" t="n">
         <v>4.6</v>
       </c>
-      <c r="T15" s="2" t="n">
+      <c r="T15" t="n">
         <v>4.56</v>
       </c>
-      <c r="U15" s="2" t="n">
+      <c r="U15" t="n">
         <v>9.06</v>
       </c>
-      <c r="V15" s="2" t="n">
+      <c r="V15" t="n">
         <v>0</v>
       </c>
-      <c r="W15" s="2" t="n">
+      <c r="W15" t="n">
         <v>4</v>
       </c>
-      <c r="X15" s="2" t="n">
+      <c r="X15" s="3" t="n">
         <v>228.76</v>
       </c>
-      <c r="Y15" s="2" t="n">
+      <c r="Y15" s="3" t="n">
         <v>41.04</v>
       </c>
-      <c r="Z15" s="2" t="n">
+      <c r="Z15" t="n">
         <v>2.32</v>
       </c>
       <c r="AA15" t="inlineStr">
@@ -9412,7 +9412,7 @@
           <t>Consumer Staples</t>
         </is>
       </c>
-      <c r="AB15" s="2" t="n">
+      <c r="AB15" t="n">
         <v>12404</v>
       </c>
       <c r="AC15" s="2" t="n">
@@ -9438,13 +9438,13 @@
           <t>Mar 2024</t>
         </is>
       </c>
-      <c r="D16" s="2" t="n">
+      <c r="D16" t="n">
         <v>4.61</v>
       </c>
-      <c r="E16" s="2" t="n">
+      <c r="E16" t="n">
         <v>8.67</v>
       </c>
-      <c r="F16" s="2" t="n">
+      <c r="F16" s="3" t="n">
         <v>8.99</v>
       </c>
       <c r="G16" s="2" t="n">
@@ -9453,58 +9453,58 @@
       <c r="H16" s="2" t="n">
         <v>0.1</v>
       </c>
-      <c r="I16" s="2" t="n">
+      <c r="I16" s="3" t="n">
         <v>13.86</v>
       </c>
-      <c r="J16" s="2" t="n">
+      <c r="J16" t="n">
         <v>1.21</v>
       </c>
       <c r="K16" s="2" t="n">
         <v>5058</v>
       </c>
-      <c r="L16" s="2" t="n">
+      <c r="L16" t="n">
         <v>2.53</v>
       </c>
-      <c r="M16" s="2" t="n">
+      <c r="M16" t="n">
         <v>24</v>
       </c>
-      <c r="N16" s="2" t="n">
+      <c r="N16" t="n">
         <v>60.47</v>
       </c>
-      <c r="O16" s="2" t="n">
+      <c r="O16" t="n">
         <v>150</v>
       </c>
-      <c r="P16" s="2" t="n">
+      <c r="P16" t="n">
         <v>2537</v>
       </c>
-      <c r="Q16" s="2" t="n">
+      <c r="Q16" t="n">
         <v>6376</v>
       </c>
-      <c r="R16" s="2" t="n">
+      <c r="R16" s="3" t="n">
         <v>8.4</v>
       </c>
       <c r="S16" s="3" t="n">
         <v>-10.99</v>
       </c>
-      <c r="T16" s="3" t="n">
+      <c r="T16" t="n">
         <v>-11.42</v>
       </c>
-      <c r="U16" s="2" t="n">
+      <c r="U16" t="n">
         <v>11.16</v>
       </c>
-      <c r="V16" s="2" t="n">
+      <c r="V16" t="n">
         <v>1</v>
       </c>
-      <c r="W16" s="2" t="n">
+      <c r="W16" t="n">
         <v>3</v>
       </c>
-      <c r="X16" s="2" t="n">
+      <c r="X16" s="3" t="n">
         <v>242.19</v>
       </c>
-      <c r="Y16" s="2" t="n">
+      <c r="Y16" s="3" t="n">
         <v>96.12</v>
       </c>
-      <c r="Z16" s="2" t="n">
+      <c r="Z16" t="n">
         <v>2.58</v>
       </c>
       <c r="AA16" t="inlineStr">
@@ -9512,13 +9512,13 @@
           <t>Information Technology</t>
         </is>
       </c>
-      <c r="AB16" s="2" t="n">
+      <c r="AB16" t="n">
         <v>51996</v>
       </c>
       <c r="AC16" s="2" t="n">
         <v>29.72</v>
       </c>
-      <c r="AD16" s="2" t="n">
+      <c r="AD16" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -9736,10 +9736,10 @@
           <t>Mar 2024</t>
         </is>
       </c>
-      <c r="D2" s="2" t="n">
+      <c r="D2" t="n">
         <v>29.28</v>
       </c>
-      <c r="E2" s="2" t="n">
+      <c r="E2" t="n">
         <v>37.02</v>
       </c>
       <c r="F2" s="2" t="n">
@@ -9754,55 +9754,55 @@
       <c r="I2" s="2" t="n">
         <v>362.96</v>
       </c>
-      <c r="J2" s="2" t="n">
+      <c r="J2" t="n">
         <v>0.77</v>
       </c>
       <c r="K2" s="2" t="n">
         <v>18742</v>
       </c>
-      <c r="L2" s="2" t="n">
+      <c r="L2" t="n">
         <v>2.21</v>
       </c>
-      <c r="M2" s="2" t="n">
+      <c r="M2" t="n">
         <v>16</v>
       </c>
-      <c r="N2" s="2" t="n">
+      <c r="N2" t="n">
         <v>59.7</v>
       </c>
-      <c r="O2" s="2" t="n">
+      <c r="O2" t="n">
         <v>84</v>
       </c>
-      <c r="P2" s="2" t="n">
+      <c r="P2" t="n">
         <v>303</v>
       </c>
-      <c r="Q2" s="2" t="n">
+      <c r="Q2" t="n">
         <v>17179</v>
       </c>
-      <c r="R2" s="2" t="n">
+      <c r="R2" s="3" t="n">
         <v>7.95</v>
       </c>
-      <c r="S2" s="2" t="n">
+      <c r="S2" s="3" t="n">
         <v>10.08</v>
       </c>
-      <c r="T2" s="2" t="n">
+      <c r="T2" t="n">
         <v>9.859999999999999</v>
       </c>
-      <c r="U2" s="2" t="n">
+      <c r="U2" t="n">
         <v>12.89</v>
       </c>
-      <c r="V2" s="2" t="n">
+      <c r="V2" t="n">
         <v>1</v>
       </c>
-      <c r="W2" s="2" t="n">
+      <c r="W2" t="n">
         <v>4</v>
       </c>
-      <c r="X2" s="2" t="n">
+      <c r="X2" s="3" t="n">
         <v>840.78</v>
       </c>
-      <c r="Y2" s="2" t="n">
+      <c r="Y2" s="3" t="n">
         <v>225.33</v>
       </c>
-      <c r="Z2" s="2" t="n">
+      <c r="Z2" t="n">
         <v>0.62</v>
       </c>
       <c r="AA2" t="inlineStr">
@@ -9810,7 +9810,7 @@
           <t>Consumer Staples</t>
         </is>
       </c>
-      <c r="AB2" s="2" t="n">
+      <c r="AB2" t="n">
         <v>70866</v>
       </c>
       <c r="AC2" s="2" t="n">
@@ -9836,10 +9836,10 @@
           <t>Mar 2024</t>
         </is>
       </c>
-      <c r="D3" s="2" t="n">
+      <c r="D3" t="n">
         <v>4.84</v>
       </c>
-      <c r="E3" s="2" t="n">
+      <c r="E3" t="n">
         <v>3.87</v>
       </c>
       <c r="F3" s="2" t="n">
@@ -9854,55 +9854,55 @@
       <c r="I3" s="2" t="n">
         <v>371.94</v>
       </c>
-      <c r="J3" s="2" t="n">
+      <c r="J3" t="n">
         <v>0.16</v>
       </c>
       <c r="K3" s="2" t="n">
         <v>853</v>
       </c>
-      <c r="L3" s="2" t="n">
+      <c r="L3" t="n">
         <v>2.99</v>
       </c>
-      <c r="M3" s="2" t="n">
+      <c r="M3" t="n">
         <v>66</v>
       </c>
-      <c r="N3" s="2" t="n">
+      <c r="N3" t="n">
         <v>13.08</v>
       </c>
-      <c r="O3" s="2" t="n">
+      <c r="O3" t="n">
         <v>15</v>
       </c>
-      <c r="P3" s="2" t="n">
+      <c r="P3" t="n">
         <v>0</v>
       </c>
-      <c r="Q3" s="2" t="n">
+      <c r="Q3" t="n">
         <v>26122</v>
       </c>
-      <c r="R3" s="2" t="n">
+      <c r="R3" s="3" t="n">
         <v>8.16</v>
       </c>
       <c r="S3" s="2" t="n">
         <v>73.18000000000001</v>
       </c>
-      <c r="T3" s="3" t="n">
+      <c r="T3" t="n">
         <v/>
       </c>
-      <c r="U3" s="2" t="n">
+      <c r="U3" t="n">
         <v>6.98</v>
       </c>
-      <c r="V3" s="2" t="n">
+      <c r="V3" t="n">
         <v>0</v>
       </c>
-      <c r="W3" s="2" t="n">
+      <c r="W3" t="n">
         <v>3</v>
       </c>
-      <c r="X3" s="2" t="n">
+      <c r="X3" s="3" t="n">
         <v>4.8</v>
       </c>
-      <c r="Y3" s="2" t="n">
+      <c r="Y3" s="3" t="n">
         <v>24.2</v>
       </c>
-      <c r="Z3" s="2" t="n">
+      <c r="Z3" t="n">
         <v>4.74</v>
       </c>
       <c r="AA3" t="inlineStr">
@@ -9910,7 +9910,7 @@
           <t>Financials</t>
         </is>
       </c>
-      <c r="AB3" s="2" t="n">
+      <c r="AB3" t="n">
         <v>845966</v>
       </c>
       <c r="AC3" s="2" t="n">
@@ -9936,10 +9936,10 @@
           <t>Mar 2024</t>
         </is>
       </c>
-      <c r="D4" s="2" t="n">
+      <c r="D4" t="n">
         <v>9.369999999999999</v>
       </c>
-      <c r="E4" s="2" t="n">
+      <c r="E4" t="n">
         <v>87.42</v>
       </c>
       <c r="F4" s="2" t="n">
@@ -9954,55 +9954,55 @@
       <c r="I4" s="2" t="n">
         <v>160.03</v>
       </c>
-      <c r="J4" s="2" t="n">
+      <c r="J4" t="n">
         <v>0.32</v>
       </c>
       <c r="K4" s="2" t="n">
         <v>486</v>
       </c>
-      <c r="L4" s="2" t="n">
+      <c r="L4" t="n">
         <v>9.380000000000001</v>
       </c>
-      <c r="M4" s="2" t="n">
+      <c r="M4" t="n">
         <v>39</v>
       </c>
-      <c r="N4" s="2" t="n">
+      <c r="N4" t="n">
         <v>24.76</v>
       </c>
-      <c r="O4" s="2" t="n">
+      <c r="O4" t="n">
         <v>28</v>
       </c>
-      <c r="P4" s="2" t="n">
+      <c r="P4" t="n">
         <v>35</v>
       </c>
-      <c r="Q4" s="2" t="n">
+      <c r="Q4" t="n">
         <v>2407</v>
       </c>
-      <c r="R4" s="2" t="n">
+      <c r="R4" s="3" t="n">
         <v>12.91</v>
       </c>
-      <c r="S4" s="2" t="n">
+      <c r="S4" s="3" t="n">
         <v>12.84</v>
       </c>
-      <c r="T4" s="2" t="n">
+      <c r="T4" t="n">
         <v>11.14</v>
       </c>
-      <c r="U4" s="2" t="n">
+      <c r="U4" t="n">
         <v>18.99</v>
       </c>
-      <c r="V4" s="2" t="n">
+      <c r="V4" t="n">
         <v>0</v>
       </c>
-      <c r="W4" s="2" t="n">
+      <c r="W4" t="n">
         <v>3</v>
       </c>
-      <c r="X4" s="2" t="n">
+      <c r="X4" s="3" t="n">
         <v>68.59999999999999</v>
       </c>
-      <c r="Y4" s="2" t="n">
+      <c r="Y4" s="3" t="n">
         <v>108.05</v>
       </c>
-      <c r="Z4" s="2" t="n">
+      <c r="Z4" t="n">
         <v>1.05</v>
       </c>
       <c r="AA4" t="inlineStr">
@@ -10010,7 +10010,7 @@
           <t>Financials</t>
         </is>
       </c>
-      <c r="AB4" s="2" t="n">
+      <c r="AB4" t="n">
         <v>20487</v>
       </c>
       <c r="AC4" s="2" t="n">
@@ -10036,10 +10036,10 @@
           <t>Mar 2024</t>
         </is>
       </c>
-      <c r="D5" s="2" t="n">
+      <c r="D5" t="n">
         <v>9.51</v>
       </c>
-      <c r="E5" s="2" t="n">
+      <c r="E5" t="n">
         <v>13.13</v>
       </c>
       <c r="F5" s="2" t="n">
@@ -10054,55 +10054,55 @@
       <c r="I5" s="2" t="n">
         <v>117.91</v>
       </c>
-      <c r="J5" s="2" t="n">
+      <c r="J5" t="n">
         <v>1.23</v>
       </c>
       <c r="K5" s="2" t="n">
         <v>4936</v>
       </c>
-      <c r="L5" s="2" t="n">
+      <c r="L5" t="n">
         <v>8.359999999999999</v>
       </c>
-      <c r="M5" s="2" t="n">
+      <c r="M5" t="n">
         <v>429</v>
       </c>
-      <c r="N5" s="2" t="n">
+      <c r="N5" t="n">
         <v>545.45</v>
       </c>
-      <c r="O5" s="2" t="n">
+      <c r="O5" t="n">
         <v>29</v>
       </c>
-      <c r="P5" s="2" t="n">
+      <c r="P5" t="n">
         <v>119</v>
       </c>
-      <c r="Q5" s="2" t="n">
+      <c r="Q5" t="n">
         <v>16801</v>
       </c>
-      <c r="R5" s="2" t="n">
+      <c r="R5" s="3" t="n">
         <v>10.51</v>
       </c>
-      <c r="S5" s="2" t="n">
+      <c r="S5" s="3" t="n">
         <v>12.01</v>
       </c>
-      <c r="T5" s="2" t="n">
+      <c r="T5" t="n">
         <v>11.14</v>
       </c>
-      <c r="U5" s="2" t="n">
+      <c r="U5" t="n">
         <v>26.32</v>
       </c>
-      <c r="V5" s="2" t="n">
+      <c r="V5" t="n">
         <v>1</v>
       </c>
-      <c r="W5" s="2" t="n">
+      <c r="W5" t="n">
         <v>4</v>
       </c>
-      <c r="X5" s="2" t="n">
+      <c r="X5" s="3" t="n">
         <v>11.71</v>
       </c>
-      <c r="Y5" s="2" t="n">
+      <c r="Y5" s="3" t="n">
         <v>9.210000000000001</v>
       </c>
-      <c r="Z5" s="2" t="n">
+      <c r="Z5" t="n">
         <v>0.58</v>
       </c>
       <c r="AA5" t="inlineStr">
@@ -10110,7 +10110,7 @@
           <t>Consumer Discretionary</t>
         </is>
       </c>
-      <c r="AB5" s="2" t="n">
+      <c r="AB5" t="n">
         <v>141858</v>
       </c>
       <c r="AC5" s="2" t="n">
@@ -10136,16 +10136,16 @@
           <t>Mar 2024</t>
         </is>
       </c>
-      <c r="D6" s="2" t="n">
+      <c r="D6" t="n">
         <v>1.43</v>
       </c>
-      <c r="E6" s="2" t="n">
+      <c r="E6" t="n">
         <v>0.19</v>
       </c>
-      <c r="F6" s="2" t="n">
+      <c r="F6" s="3" t="n">
         <v>12.7</v>
       </c>
-      <c r="G6" s="2" t="n">
+      <c r="G6" s="3" t="n">
         <v>1.65</v>
       </c>
       <c r="H6" s="2" t="n">
@@ -10154,55 +10154,55 @@
       <c r="I6" s="2" t="n">
         <v>240.33</v>
       </c>
-      <c r="J6" s="2" t="n">
+      <c r="J6" t="n">
         <v>0.33</v>
       </c>
       <c r="K6" s="3" t="n">
         <v>-2099</v>
       </c>
-      <c r="L6" s="2" t="n">
+      <c r="L6" t="n">
         <v>23.65</v>
       </c>
-      <c r="M6" s="2" t="n">
+      <c r="M6" t="n">
         <v>19</v>
       </c>
-      <c r="N6" s="2" t="n">
+      <c r="N6" t="n">
         <v>14.89</v>
       </c>
-      <c r="O6" s="2" t="n">
+      <c r="O6" t="n">
         <v>14</v>
       </c>
-      <c r="P6" s="2" t="n">
+      <c r="P6" t="n">
         <v>0</v>
       </c>
-      <c r="Q6" s="2" t="n">
+      <c r="Q6" t="n">
         <v>29122</v>
       </c>
       <c r="R6" s="2" t="n">
         <v>24.23</v>
       </c>
-      <c r="S6" s="2" t="n">
+      <c r="S6" s="3" t="n">
         <v>7.37</v>
       </c>
-      <c r="T6" s="2" t="n">
+      <c r="T6" t="n">
         <v>7.89</v>
       </c>
-      <c r="U6" s="2" t="n">
+      <c r="U6" t="n">
         <v>17.24</v>
       </c>
-      <c r="V6" s="2" t="n">
+      <c r="V6" t="n">
         <v>0</v>
       </c>
-      <c r="W6" s="2" t="n">
+      <c r="W6" t="n">
         <v>2</v>
       </c>
-      <c r="X6" s="2" t="n">
+      <c r="X6" s="3" t="n">
         <v>422.54</v>
       </c>
-      <c r="Y6" s="2" t="n">
+      <c r="Y6" s="3" t="n">
         <v>539.1799999999999</v>
       </c>
-      <c r="Z6" s="2" t="n">
+      <c r="Z6" t="n">
         <v>0.17</v>
       </c>
       <c r="AA6" t="inlineStr">
@@ -10210,7 +10210,7 @@
           <t>Financials</t>
         </is>
       </c>
-      <c r="AB6" s="2" t="n">
+      <c r="AB6" t="n">
         <v>131988</v>
       </c>
       <c r="AC6" s="2" t="n">
@@ -10236,10 +10236,10 @@
           <t>Mar 2024</t>
         </is>
       </c>
-      <c r="D7" s="2" t="n">
+      <c r="D7" t="n">
         <v>14.89</v>
       </c>
-      <c r="E7" s="2" t="n">
+      <c r="E7" t="n">
         <v>12.52</v>
       </c>
       <c r="F7" s="2" t="n">
@@ -10254,55 +10254,55 @@
       <c r="I7" s="2" t="n">
         <v>71.78</v>
       </c>
-      <c r="J7" s="2" t="n">
+      <c r="J7" t="n">
         <v>0.96</v>
       </c>
       <c r="K7" s="2" t="n">
         <v>1536</v>
       </c>
-      <c r="L7" s="2" t="n">
+      <c r="L7" t="n">
         <v>1.69</v>
       </c>
-      <c r="M7" s="2" t="n">
+      <c r="M7" t="n">
         <v>844</v>
       </c>
-      <c r="N7" s="2" t="n">
+      <c r="N7" t="n">
         <v>402.13</v>
       </c>
-      <c r="O7" s="2" t="n">
+      <c r="O7" t="n">
         <v>44</v>
       </c>
-      <c r="P7" s="2" t="n">
+      <c r="P7" t="n">
         <v>39</v>
       </c>
-      <c r="Q7" s="2" t="n">
+      <c r="Q7" t="n">
         <v>1253</v>
       </c>
-      <c r="R7" s="2" t="n">
+      <c r="R7" s="3" t="n">
         <v>6.72</v>
       </c>
-      <c r="S7" s="2" t="n">
+      <c r="S7" s="3" t="n">
         <v>9.279999999999999</v>
       </c>
-      <c r="T7" s="2" t="n">
+      <c r="T7" t="n">
         <v>9.26</v>
       </c>
-      <c r="U7" s="2" t="n">
+      <c r="U7" t="n">
         <v>19.84</v>
       </c>
-      <c r="V7" s="2" t="n">
+      <c r="V7" t="n">
         <v>1</v>
       </c>
-      <c r="W7" s="2" t="n">
+      <c r="W7" t="n">
         <v>4</v>
       </c>
-      <c r="X7" s="2" t="n">
+      <c r="X7" s="3" t="n">
         <v>4.11</v>
       </c>
-      <c r="Y7" s="2" t="n">
+      <c r="Y7" s="3" t="n">
         <v>8.619999999999999</v>
       </c>
-      <c r="Z7" s="2" t="n">
+      <c r="Z7" t="n">
         <v>1.27</v>
       </c>
       <c r="AA7" t="inlineStr">
@@ -10310,7 +10310,7 @@
           <t>Consumer Discretionary</t>
         </is>
       </c>
-      <c r="AB7" s="2" t="n">
+      <c r="AB7" t="n">
         <v>16727</v>
       </c>
       <c r="AC7" s="2" t="n">
